--- a/output/flipkart_sellers.xlsx
+++ b/output/flipkart_sellers.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD453"/>
+  <dimension ref="A1:AD519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="60" customWidth="1" min="28" max="28"/>
@@ -956,7 +956,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Ganeshaenterprisestore</t>
+          <t>GaneshaEnterpriseStore</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sneakers</t>
+          <t>Casual Shoes</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -997,17 +997,23 @@
         </is>
       </c>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
+      <c r="T4" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/echor-esgrpep-sneakers-men/p/itme9e8167e57aac?pid=SHOHHD2FNBTZ77BG</t>
+          <t>https://www.flipkart.com/echor-esmgod-white-gym-shoes-men-sneakers/p/itma21e408aa03a9?pid=SHOHMQP7BFFB5TWM</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>Sneakers</t>
+          <t>Casual Shoes</t>
         </is>
       </c>
       <c r="Y4" s="2" t="n"/>
@@ -1015,12 +1021,12 @@
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/echor-esgrpep-sneakers-men/p/itme9e8167e57aac?pid=SHOHHD2FNBTZ77BG</t>
+          <t>https://www.flipkart.com/echor-esmgod-white-gym-shoes-men-sneakers/p/itma21e408aa03a9?pid=SHOHMQP7BFFB5TWM</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>flipkart_product</t>
+          <t>state_json_sold_by</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1800,7 +1806,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bellmisports</t>
+          <t>BellmiSports</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -1821,7 +1827,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Thong Sandals</t>
+          <t>Slippers &amp; Flip Flops</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -1841,9 +1847,15 @@
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
+      <c r="T14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
           <t>https://www.flipkart.com/bellmi-men-slippers/p/itme5f2678d4d69f?pid=SFFHZFXJCHZMPYDR</t>
@@ -1851,7 +1863,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>Thong Sandals</t>
+          <t>Slippers &amp; Flip Flops</t>
         </is>
       </c>
       <c r="Y14" s="2" t="n"/>
@@ -1864,7 +1876,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>flipkart_product</t>
+          <t>state_json_sold_by</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -9876,7 +9888,7 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Shoetopi</t>
+          <t>SHOETOPI</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -9889,13 +9901,21 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>ENRICHMENT_PENDING</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="3" t="n"/>
       <c r="I124" s="2" t="n"/>
@@ -9907,33 +9927,53 @@
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="n"/>
       <c r="Q124" s="3" t="n"/>
-      <c r="R124" s="2" t="n"/>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="S124" s="2" t="n"/>
-      <c r="T124" s="3" t="n"/>
-      <c r="U124" s="3" t="n"/>
+      <c r="T124" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U124" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V124" s="3" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/shoetopia-jutis-women/p/itmc82116a3b3ae5?pid=SHOHZEJVSW3FZHA8</t>
+          <t>https://www.flipkart.com/shoetopia-girls-slip-jutis/p/itmac537c1c54c18?pid=KSSHB3ZYM9RMMGSR</t>
         </is>
       </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
-          <t>Women's Ethnic Shoes</t>
-        </is>
-      </c>
-      <c r="Y124" s="2" t="n"/>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>Ethnic Shoes</t>
+        </is>
+      </c>
       <c r="Z124" s="2" t="n"/>
       <c r="AA124" s="2" t="n"/>
-      <c r="AB124" s="2" t="n"/>
+      <c r="AB124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/shoetopia-girls-slip-jutis/p/itmac537c1c54c18?pid=KSSHB3ZYM9RMMGSR</t>
+        </is>
+      </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>fulfillment_label</t>
-        </is>
-      </c>
-      <c r="AD124" s="2" t="n"/>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD124" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -38857,6 +38897,5370 @@
         </is>
       </c>
     </row>
+    <row r="454" ht="22" customHeight="1">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Pranaambharatse</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="n"/>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D454" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="n"/>
+      <c r="H454" s="3" t="n"/>
+      <c r="I454" s="2" t="n"/>
+      <c r="J454" s="3" t="n"/>
+      <c r="K454" s="3" t="n"/>
+      <c r="L454" s="3" t="n"/>
+      <c r="M454" s="2" t="n"/>
+      <c r="N454" s="2" t="n"/>
+      <c r="O454" s="2" t="n"/>
+      <c r="P454" s="2" t="n"/>
+      <c r="Q454" s="3" t="n"/>
+      <c r="R454" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S454" s="2" t="n"/>
+      <c r="T454" s="3" t="n"/>
+      <c r="U454" s="3" t="n"/>
+      <c r="V454" s="3" t="n"/>
+      <c r="W454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/feetpanda-men-clogs/p/itm7f52d21eea7b3?pid=SNDHZGY55JH4C9TP</t>
+        </is>
+      </c>
+      <c r="X454" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y454" s="2" t="n"/>
+      <c r="Z454" s="2" t="n"/>
+      <c r="AA454" s="2" t="n"/>
+      <c r="AB454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/feetpanda-men-clogs/p/itm7f52d21eea7b3?pid=SNDHZGY55JH4C9TP</t>
+        </is>
+      </c>
+      <c r="AC454" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD454" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="1">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t>BRUTONFOOTWEAR</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="n"/>
+      <c r="C455" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D455" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E455" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="n"/>
+      <c r="H455" s="6" t="n"/>
+      <c r="I455" s="5" t="n"/>
+      <c r="J455" s="6" t="n"/>
+      <c r="K455" s="6" t="n"/>
+      <c r="L455" s="6" t="n"/>
+      <c r="M455" s="5" t="n"/>
+      <c r="N455" s="5" t="n"/>
+      <c r="O455" s="5" t="n"/>
+      <c r="P455" s="5" t="n"/>
+      <c r="Q455" s="6" t="n"/>
+      <c r="R455" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S455" s="5" t="n"/>
+      <c r="T455" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U455" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V455" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W455" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bruton-men-clogs/p/itm3c608372ba71e?pid=SNDH4C5UCHU76VFZ</t>
+        </is>
+      </c>
+      <c r="X455" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y455" s="5" t="n"/>
+      <c r="Z455" s="5" t="n"/>
+      <c r="AA455" s="5" t="n"/>
+      <c r="AB455" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bruton-men-clogs/p/itm3c608372ba71e?pid=SNDH4C5UCHU76VFZ</t>
+        </is>
+      </c>
+      <c r="AC455" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD455" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="1">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>SparxBrandStore</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="n"/>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D456" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="n"/>
+      <c r="H456" s="3" t="n"/>
+      <c r="I456" s="2" t="n"/>
+      <c r="J456" s="3" t="n"/>
+      <c r="K456" s="3" t="n"/>
+      <c r="L456" s="3" t="n"/>
+      <c r="M456" s="2" t="n"/>
+      <c r="N456" s="2" t="n"/>
+      <c r="O456" s="2" t="n"/>
+      <c r="P456" s="2" t="n"/>
+      <c r="Q456" s="3" t="n"/>
+      <c r="R456" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S456" s="2" t="n"/>
+      <c r="T456" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U456" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V456" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sparx-men-clogs/p/itm5262a4c148652?pid=SNDHN842GCWHPE6J</t>
+        </is>
+      </c>
+      <c r="X456" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y456" s="2" t="n"/>
+      <c r="Z456" s="2" t="n"/>
+      <c r="AA456" s="2" t="n"/>
+      <c r="AB456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sparx-men-clogs/p/itm5262a4c148652?pid=SNDHN842GCWHPE6J</t>
+        </is>
+      </c>
+      <c r="AC456" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD456" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="1">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>NithyaFootwearPrivateLimited</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="n"/>
+      <c r="C457" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D457" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="inlineStr">
+        <is>
+          <t>Public Limited Company</t>
+        </is>
+      </c>
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="n"/>
+      <c r="H457" s="6" t="n"/>
+      <c r="I457" s="5" t="n"/>
+      <c r="J457" s="6" t="n"/>
+      <c r="K457" s="6" t="n"/>
+      <c r="L457" s="6" t="n"/>
+      <c r="M457" s="5" t="n"/>
+      <c r="N457" s="5" t="n"/>
+      <c r="O457" s="5" t="n"/>
+      <c r="P457" s="5" t="n"/>
+      <c r="Q457" s="6" t="n"/>
+      <c r="R457" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S457" s="5" t="n"/>
+      <c r="T457" s="6" t="n"/>
+      <c r="U457" s="6" t="n"/>
+      <c r="V457" s="6" t="n"/>
+      <c r="W457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/adrenex-x-hoppa-men-clogs/p/itm5b2ceac681a06?pid=SNDHZQGJRF6EPQGK</t>
+        </is>
+      </c>
+      <c r="X457" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y457" s="5" t="n"/>
+      <c r="Z457" s="5" t="n"/>
+      <c r="AA457" s="5" t="n"/>
+      <c r="AB457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/adrenex-x-hoppa-men-clogs/p/itm5b2ceac681a06?pid=SNDHZQGJRF6EPQGK</t>
+        </is>
+      </c>
+      <c r="AC457" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD457" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Cherry09</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="n"/>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D458" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="n"/>
+      <c r="H458" s="3" t="n"/>
+      <c r="I458" s="2" t="n"/>
+      <c r="J458" s="3" t="n"/>
+      <c r="K458" s="3" t="n"/>
+      <c r="L458" s="3" t="n"/>
+      <c r="M458" s="2" t="n"/>
+      <c r="N458" s="2" t="n"/>
+      <c r="O458" s="2" t="n"/>
+      <c r="P458" s="2" t="n"/>
+      <c r="Q458" s="3" t="n"/>
+      <c r="R458" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S458" s="2" t="n"/>
+      <c r="T458" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U458" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V458" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/eastern-club-men-clogs/p/itmf8ffe13d76f69?pid=SNDHG82RTAVKKPZF</t>
+        </is>
+      </c>
+      <c r="X458" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y458" s="2" t="n"/>
+      <c r="Z458" s="2" t="n"/>
+      <c r="AA458" s="2" t="n"/>
+      <c r="AB458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/eastern-club-men-clogs/p/itmf8ffe13d76f69?pid=SNDHG82RTAVKKPZF</t>
+        </is>
+      </c>
+      <c r="AC458" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD458" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="22" customHeight="1">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t>KridhayStore</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="n"/>
+      <c r="C459" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D459" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="n"/>
+      <c r="H459" s="6" t="n"/>
+      <c r="I459" s="5" t="n"/>
+      <c r="J459" s="6" t="n"/>
+      <c r="K459" s="6" t="n"/>
+      <c r="L459" s="6" t="n"/>
+      <c r="M459" s="5" t="n"/>
+      <c r="N459" s="5" t="n"/>
+      <c r="O459" s="5" t="n"/>
+      <c r="P459" s="5" t="n"/>
+      <c r="Q459" s="6" t="n"/>
+      <c r="R459" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S459" s="5" t="n"/>
+      <c r="T459" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U459" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V459" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W459" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/killer-men-healthcare-clogs-ortho-support-slip-resistant-easy-clean-sandal/p/itm51db3cb99a676?pid=SNDHZHYMTJJMVD9V</t>
+        </is>
+      </c>
+      <c r="X459" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y459" s="5" t="n"/>
+      <c r="Z459" s="5" t="n"/>
+      <c r="AA459" s="5" t="n"/>
+      <c r="AB459" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/killer-men-healthcare-clogs-ortho-support-slip-resistant-easy-clean-sandal/p/itm51db3cb99a676?pid=SNDHZHYMTJJMVD9V</t>
+        </is>
+      </c>
+      <c r="AC459" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD459" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="1">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Aarav enterprizes</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="n"/>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D460" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="n"/>
+      <c r="H460" s="3" t="n"/>
+      <c r="I460" s="2" t="n"/>
+      <c r="J460" s="3" t="n"/>
+      <c r="K460" s="3" t="n"/>
+      <c r="L460" s="3" t="n"/>
+      <c r="M460" s="2" t="n"/>
+      <c r="N460" s="2" t="n"/>
+      <c r="O460" s="2" t="n"/>
+      <c r="P460" s="2" t="n"/>
+      <c r="Q460" s="3" t="n"/>
+      <c r="R460" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S460" s="2" t="n"/>
+      <c r="T460" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U460" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V460" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/corsac-unisex-clogs/p/itmdaf27e125531d?pid=SNDHHTASZGHXEDYF</t>
+        </is>
+      </c>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="n"/>
+      <c r="Z460" s="2" t="n"/>
+      <c r="AA460" s="2" t="n"/>
+      <c r="AB460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/corsac-unisex-clogs/p/itmdaf27e125531d?pid=SNDHHTASZGHXEDYF</t>
+        </is>
+      </c>
+      <c r="AC460" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD460" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="1">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>HikeStore</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="n"/>
+      <c r="C461" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D461" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E461" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="n"/>
+      <c r="H461" s="6" t="n"/>
+      <c r="I461" s="5" t="n"/>
+      <c r="J461" s="6" t="n"/>
+      <c r="K461" s="6" t="n"/>
+      <c r="L461" s="6" t="n"/>
+      <c r="M461" s="5" t="n"/>
+      <c r="N461" s="5" t="n"/>
+      <c r="O461" s="5" t="n"/>
+      <c r="P461" s="5" t="n"/>
+      <c r="Q461" s="6" t="n"/>
+      <c r="R461" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S461" s="5" t="n"/>
+      <c r="T461" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U461" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V461" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W461" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/svaar-men-clogs/p/itm0495b9de56657?pid=SNDGJQV5RH6XSBW6</t>
+        </is>
+      </c>
+      <c r="X461" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y461" s="5" t="n"/>
+      <c r="Z461" s="5" t="n"/>
+      <c r="AA461" s="5" t="n"/>
+      <c r="AB461" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/svaar-men-clogs/p/itm0495b9de56657?pid=SNDGJQV5RH6XSBW6</t>
+        </is>
+      </c>
+      <c r="AC461" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD461" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="1">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Pirchlifestyle</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="n"/>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D462" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="n"/>
+      <c r="H462" s="3" t="n"/>
+      <c r="I462" s="2" t="n"/>
+      <c r="J462" s="3" t="n"/>
+      <c r="K462" s="3" t="n"/>
+      <c r="L462" s="3" t="n"/>
+      <c r="M462" s="2" t="n"/>
+      <c r="N462" s="2" t="n"/>
+      <c r="O462" s="2" t="n"/>
+      <c r="P462" s="2" t="n"/>
+      <c r="Q462" s="3" t="n"/>
+      <c r="R462" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S462" s="2" t="n"/>
+      <c r="T462" s="3" t="n"/>
+      <c r="U462" s="3" t="n"/>
+      <c r="V462" s="3" t="n"/>
+      <c r="W462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pirch-men-clogs/p/itm3e169363f2089?pid=SNDHZ5PSP3BXMYUG</t>
+        </is>
+      </c>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="n"/>
+      <c r="Z462" s="2" t="n"/>
+      <c r="AA462" s="2" t="n"/>
+      <c r="AB462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pirch-men-clogs/p/itm3e169363f2089?pid=SNDHZ5PSP3BXMYUG</t>
+        </is>
+      </c>
+      <c r="AC462" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD462" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="1">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t>SOUKSHOE</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="n"/>
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D463" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E463" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="n"/>
+      <c r="H463" s="6" t="n"/>
+      <c r="I463" s="5" t="n"/>
+      <c r="J463" s="6" t="n"/>
+      <c r="K463" s="6" t="n"/>
+      <c r="L463" s="6" t="n"/>
+      <c r="M463" s="5" t="n"/>
+      <c r="N463" s="5" t="n"/>
+      <c r="O463" s="5" t="n"/>
+      <c r="P463" s="5" t="n"/>
+      <c r="Q463" s="6" t="n"/>
+      <c r="R463" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S463" s="5" t="n"/>
+      <c r="T463" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U463" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V463" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W463" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/souk-men-clogs/p/itm4ab8257bc5a94?pid=SNDHHV5DPDXA6QB2</t>
+        </is>
+      </c>
+      <c r="X463" s="5" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y463" s="5" t="n"/>
+      <c r="Z463" s="5" t="n"/>
+      <c r="AA463" s="5" t="n"/>
+      <c r="AB463" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/souk-men-clogs/p/itm4ab8257bc5a94?pid=SNDHHV5DPDXA6QB2</t>
+        </is>
+      </c>
+      <c r="AC463" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD463" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="1">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>PerfactFeet</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="n"/>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D464" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="n"/>
+      <c r="H464" s="3" t="n"/>
+      <c r="I464" s="2" t="n"/>
+      <c r="J464" s="3" t="n"/>
+      <c r="K464" s="3" t="n"/>
+      <c r="L464" s="3" t="n"/>
+      <c r="M464" s="2" t="n"/>
+      <c r="N464" s="2" t="n"/>
+      <c r="O464" s="2" t="n"/>
+      <c r="P464" s="2" t="n"/>
+      <c r="Q464" s="3" t="n"/>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="n"/>
+      <c r="T464" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U464" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V464" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/perfect-feet-men-sandals/p/itm08831933f96fb?pid=SNDHM47HGJZU4UHS</t>
+        </is>
+      </c>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>Clogs</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="n"/>
+      <c r="Z464" s="2" t="n"/>
+      <c r="AA464" s="2" t="n"/>
+      <c r="AB464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/perfect-feet-men-sandals/p/itm08831933f96fb?pid=SNDHM47HGJZU4UHS</t>
+        </is>
+      </c>
+      <c r="AC464" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD464" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="1">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t>IRAJANDCOMPANY</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="n"/>
+      <c r="C465" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D465" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F465" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="G465" s="5" t="n"/>
+      <c r="H465" s="6" t="n"/>
+      <c r="I465" s="5" t="n"/>
+      <c r="J465" s="6" t="n"/>
+      <c r="K465" s="6" t="n"/>
+      <c r="L465" s="6" t="n"/>
+      <c r="M465" s="5" t="n"/>
+      <c r="N465" s="5" t="n"/>
+      <c r="O465" s="5" t="n"/>
+      <c r="P465" s="5" t="n"/>
+      <c r="Q465" s="6" t="n"/>
+      <c r="R465" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S465" s="5" t="n"/>
+      <c r="T465" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U465" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V465" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W465" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kastava-premium-stylish-lightweight-slip-on-shoes-office-party-wear-loafers-men/p/itmb04c0e3015fa9?pid=SHOH7Z2DNSAHHCCV</t>
+        </is>
+      </c>
+      <c r="X465" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="Y465" s="5" t="n"/>
+      <c r="Z465" s="5" t="n"/>
+      <c r="AA465" s="5" t="n"/>
+      <c r="AB465" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kastava-premium-stylish-lightweight-slip-on-shoes-office-party-wear-loafers-men/p/itmb04c0e3015fa9?pid=SHOH7Z2DNSAHHCCV</t>
+        </is>
+      </c>
+      <c r="AC465" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD465" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="1">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Auvio</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="n"/>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D466" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="n"/>
+      <c r="H466" s="3" t="n"/>
+      <c r="I466" s="2" t="n"/>
+      <c r="J466" s="3" t="n"/>
+      <c r="K466" s="3" t="n"/>
+      <c r="L466" s="3" t="n"/>
+      <c r="M466" s="2" t="n"/>
+      <c r="N466" s="2" t="n"/>
+      <c r="O466" s="2" t="n"/>
+      <c r="P466" s="2" t="n"/>
+      <c r="Q466" s="3" t="n"/>
+      <c r="R466" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S466" s="2" t="n"/>
+      <c r="T466" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U466" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V466" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/birde-premium-comfortable-regular-wear-shoes-men-casual-senakers-high-tops/p/itm774f050523a15?pid=SHOGZEQGDDM9GP8N</t>
+        </is>
+      </c>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="n"/>
+      <c r="Z466" s="2" t="n"/>
+      <c r="AA466" s="2" t="n"/>
+      <c r="AB466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/birde-premium-comfortable-regular-wear-shoes-men-casual-senakers-high-tops/p/itm774f050523a15?pid=SHOGZEQGDDM9GP8N</t>
+        </is>
+      </c>
+      <c r="AC466" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD466" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="22" customHeight="1">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t>lejano</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="n"/>
+      <c r="C467" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D467" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="n"/>
+      <c r="H467" s="6" t="n"/>
+      <c r="I467" s="5" t="n"/>
+      <c r="J467" s="6" t="n"/>
+      <c r="K467" s="6" t="n"/>
+      <c r="L467" s="6" t="n"/>
+      <c r="M467" s="5" t="n"/>
+      <c r="N467" s="5" t="n"/>
+      <c r="O467" s="5" t="n"/>
+      <c r="P467" s="5" t="n"/>
+      <c r="Q467" s="6" t="n"/>
+      <c r="R467" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S467" s="5" t="n"/>
+      <c r="T467" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U467" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V467" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W467" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lejano-high-tops-men/p/itmc6f61b55d69a4?pid=SHOHF9RRFAHFY22M</t>
+        </is>
+      </c>
+      <c r="X467" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="Y467" s="5" t="n"/>
+      <c r="Z467" s="5" t="n"/>
+      <c r="AA467" s="5" t="n"/>
+      <c r="AB467" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lejano-high-tops-men/p/itmc6f61b55d69a4?pid=SHOHF9RRFAHFY22M</t>
+        </is>
+      </c>
+      <c r="AC467" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD467" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="1">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>COOPERWINGSFOOTWEAR</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="n"/>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D468" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="n"/>
+      <c r="H468" s="3" t="n"/>
+      <c r="I468" s="2" t="n"/>
+      <c r="J468" s="3" t="n"/>
+      <c r="K468" s="3" t="n"/>
+      <c r="L468" s="3" t="n"/>
+      <c r="M468" s="2" t="n"/>
+      <c r="N468" s="2" t="n"/>
+      <c r="O468" s="2" t="n"/>
+      <c r="P468" s="2" t="n"/>
+      <c r="Q468" s="3" t="n"/>
+      <c r="R468" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S468" s="2" t="n"/>
+      <c r="T468" s="3" t="n"/>
+      <c r="U468" s="3" t="n"/>
+      <c r="V468" s="3" t="n"/>
+      <c r="W468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cooperwings-running-shoes-men/p/itm74b6d0ca0af1d?pid=SHOHPGCTJJRT3M8F</t>
+        </is>
+      </c>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="n"/>
+      <c r="Z468" s="2" t="n"/>
+      <c r="AA468" s="2" t="n"/>
+      <c r="AB468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cooperwings-running-shoes-men/p/itm74b6d0ca0af1d?pid=SHOHPGCTJJRT3M8F</t>
+        </is>
+      </c>
+      <c r="AC468" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD468" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="1">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t>ULIKEFASHION</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="n"/>
+      <c r="C469" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D469" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="n"/>
+      <c r="H469" s="6" t="n"/>
+      <c r="I469" s="5" t="n"/>
+      <c r="J469" s="6" t="n"/>
+      <c r="K469" s="6" t="n"/>
+      <c r="L469" s="6" t="n"/>
+      <c r="M469" s="5" t="n"/>
+      <c r="N469" s="5" t="n"/>
+      <c r="O469" s="5" t="n"/>
+      <c r="P469" s="5" t="n"/>
+      <c r="Q469" s="6" t="n"/>
+      <c r="R469" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S469" s="5" t="n"/>
+      <c r="T469" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U469" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V469" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W469" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zorza-mens-running-shoes-cushioned-comfort-sole-outdoors-men/p/itmc34a2522571bb?pid=SHOHZGSC2EAHYGMC</t>
+        </is>
+      </c>
+      <c r="X469" s="5" t="inlineStr">
+        <is>
+          <t>Casual Shoes</t>
+        </is>
+      </c>
+      <c r="Y469" s="5" t="n"/>
+      <c r="Z469" s="5" t="n"/>
+      <c r="AA469" s="5" t="n"/>
+      <c r="AB469" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zorza-mens-running-shoes-cushioned-comfort-sole-outdoors-men/p/itmc34a2522571bb?pid=SHOHZGSC2EAHYGMC</t>
+        </is>
+      </c>
+      <c r="AC469" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD469" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="22" customHeight="1">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>SmTrands</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="n"/>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D470" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="n"/>
+      <c r="H470" s="3" t="n"/>
+      <c r="I470" s="2" t="n"/>
+      <c r="J470" s="3" t="n"/>
+      <c r="K470" s="3" t="n"/>
+      <c r="L470" s="3" t="n"/>
+      <c r="M470" s="2" t="n"/>
+      <c r="N470" s="2" t="n"/>
+      <c r="O470" s="2" t="n"/>
+      <c r="P470" s="2" t="n"/>
+      <c r="Q470" s="3" t="n"/>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="n"/>
+      <c r="T470" s="3" t="n"/>
+      <c r="U470" s="3" t="n"/>
+      <c r="V470" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/stride-up-new-design-lightweight-stylish-trendy-walking-shoes-men-sneakers/p/itm6a9e942057b32?pid=SHOHNWRGFCYZWFRH</t>
+        </is>
+      </c>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="n"/>
+      <c r="Z470" s="2" t="n"/>
+      <c r="AA470" s="2" t="n"/>
+      <c r="AB470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/stride-up-new-design-lightweight-stylish-trendy-walking-shoes-men-sneakers/p/itm6a9e942057b32?pid=SHOHNWRGFCYZWFRH</t>
+        </is>
+      </c>
+      <c r="AC470" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD470" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="22" customHeight="1">
+      <c r="A471" s="5" t="inlineStr">
+        <is>
+          <t>NobeliteFootwear</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="n"/>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D471" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="n"/>
+      <c r="H471" s="6" t="n"/>
+      <c r="I471" s="5" t="n"/>
+      <c r="J471" s="6" t="n"/>
+      <c r="K471" s="6" t="n"/>
+      <c r="L471" s="6" t="n"/>
+      <c r="M471" s="5" t="n"/>
+      <c r="N471" s="5" t="n"/>
+      <c r="O471" s="5" t="n"/>
+      <c r="P471" s="5" t="n"/>
+      <c r="Q471" s="6" t="n"/>
+      <c r="R471" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S471" s="5" t="n"/>
+      <c r="T471" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U471" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V471" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W471" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nobelite-premium-sports-gym-trending-stylish-running-shoes-men/p/itm97ef97f943d6c?pid=SHOH8PFQCTANHETW</t>
+        </is>
+      </c>
+      <c r="X471" s="5" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="Y471" s="5" t="n"/>
+      <c r="Z471" s="5" t="n"/>
+      <c r="AA471" s="5" t="n"/>
+      <c r="AB471" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nobelite-premium-sports-gym-trending-stylish-running-shoes-men/p/itm97ef97f943d6c?pid=SHOH8PFQCTANHETW</t>
+        </is>
+      </c>
+      <c r="AC471" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD471" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="22" customHeight="1">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>TAJFOOTWEARFACTORY</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="n"/>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D472" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="n"/>
+      <c r="H472" s="3" t="n"/>
+      <c r="I472" s="2" t="n"/>
+      <c r="J472" s="3" t="n"/>
+      <c r="K472" s="3" t="n"/>
+      <c r="L472" s="3" t="n"/>
+      <c r="M472" s="2" t="n"/>
+      <c r="N472" s="2" t="n"/>
+      <c r="O472" s="2" t="n"/>
+      <c r="P472" s="2" t="n"/>
+      <c r="Q472" s="3" t="n"/>
+      <c r="R472" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S472" s="2" t="n"/>
+      <c r="T472" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U472" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V472" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/taj-tajj-boot-07-102-boots-men/p/itm8f09751b12552?pid=SHOHHJ5K7GBTXVTK</t>
+        </is>
+      </c>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="n"/>
+      <c r="Z472" s="2" t="n"/>
+      <c r="AA472" s="2" t="n"/>
+      <c r="AB472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/taj-tajj-boot-07-102-boots-men/p/itm8f09751b12552?pid=SHOHHJ5K7GBTXVTK</t>
+        </is>
+      </c>
+      <c r="AC472" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD472" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="22" customHeight="1">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>LeosFitnesshoes</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="n"/>
+      <c r="C473" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="n"/>
+      <c r="H473" s="6" t="n"/>
+      <c r="I473" s="5" t="n"/>
+      <c r="J473" s="6" t="n"/>
+      <c r="K473" s="6" t="n"/>
+      <c r="L473" s="6" t="n"/>
+      <c r="M473" s="5" t="n"/>
+      <c r="N473" s="5" t="n"/>
+      <c r="O473" s="5" t="n"/>
+      <c r="P473" s="5" t="n"/>
+      <c r="Q473" s="6" t="n"/>
+      <c r="R473" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S473" s="5" t="n"/>
+      <c r="T473" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U473" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V473" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W473" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/leo-shoes-hiking-trekking-men/p/itmad8e9bdfa0907?pid=SHOG5F82AJJTBKKE</t>
+        </is>
+      </c>
+      <c r="X473" s="5" t="inlineStr">
+        <is>
+          <t>Sports Shoes</t>
+        </is>
+      </c>
+      <c r="Y473" s="5" t="n"/>
+      <c r="Z473" s="5" t="n"/>
+      <c r="AA473" s="5" t="n"/>
+      <c r="AB473" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/leo-shoes-hiking-trekking-men/p/itmad8e9bdfa0907?pid=SHOG5F82AJJTBKKE</t>
+        </is>
+      </c>
+      <c r="AC473" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD473" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="22" customHeight="1">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Vokline</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="n"/>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D474" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="n"/>
+      <c r="H474" s="3" t="n"/>
+      <c r="I474" s="2" t="n"/>
+      <c r="J474" s="3" t="n"/>
+      <c r="K474" s="3" t="n"/>
+      <c r="L474" s="3" t="n"/>
+      <c r="M474" s="2" t="n"/>
+      <c r="N474" s="2" t="n"/>
+      <c r="O474" s="2" t="n"/>
+      <c r="P474" s="2" t="n"/>
+      <c r="Q474" s="3" t="n"/>
+      <c r="R474" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S474" s="2" t="n"/>
+      <c r="T474" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U474" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V474" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/evok-men-mens-comfortable-trending-stylish-multicolor-embozing-flipflop-pack-2-slippers/p/itmf2648afbb603d?pid=SFFGEWKCRMA4XTMW</t>
+        </is>
+      </c>
+      <c r="X474" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="n"/>
+      <c r="Z474" s="2" t="n"/>
+      <c r="AA474" s="2" t="n"/>
+      <c r="AB474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/evok-men-mens-comfortable-trending-stylish-multicolor-embozing-flipflop-pack-2-slippers/p/itmf2648afbb603d?pid=SFFGEWKCRMA4XTMW</t>
+        </is>
+      </c>
+      <c r="AC474" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD474" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="22" customHeight="1">
+      <c r="A475" s="5" t="inlineStr">
+        <is>
+          <t>FOOTUPFOOTWEAR</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="n"/>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D475" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G475" s="5" t="n"/>
+      <c r="H475" s="6" t="n"/>
+      <c r="I475" s="5" t="n"/>
+      <c r="J475" s="6" t="n"/>
+      <c r="K475" s="6" t="n"/>
+      <c r="L475" s="6" t="n"/>
+      <c r="M475" s="5" t="n"/>
+      <c r="N475" s="5" t="n"/>
+      <c r="O475" s="5" t="n"/>
+      <c r="P475" s="5" t="n"/>
+      <c r="Q475" s="6" t="n"/>
+      <c r="R475" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S475" s="5" t="n"/>
+      <c r="T475" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U475" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V475" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/footup-men-super-soft-orthopedic-comfortable-lightweight-diabetic-combo-slippers/p/itm32f605e32145d?pid=SFFHGV5F6UAZNAMF</t>
+        </is>
+      </c>
+      <c r="X475" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y475" s="5" t="n"/>
+      <c r="Z475" s="5" t="n"/>
+      <c r="AA475" s="5" t="n"/>
+      <c r="AB475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/footup-men-super-soft-orthopedic-comfortable-lightweight-diabetic-combo-slippers/p/itm32f605e32145d?pid=SFFHGV5F6UAZNAMF</t>
+        </is>
+      </c>
+      <c r="AC475" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD475" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="22" customHeight="1">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>FOOTPRO</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="n"/>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D476" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="n"/>
+      <c r="H476" s="3" t="n"/>
+      <c r="I476" s="2" t="n"/>
+      <c r="J476" s="3" t="n"/>
+      <c r="K476" s="3" t="n"/>
+      <c r="L476" s="3" t="n"/>
+      <c r="M476" s="2" t="n"/>
+      <c r="N476" s="2" t="n"/>
+      <c r="O476" s="2" t="n"/>
+      <c r="P476" s="2" t="n"/>
+      <c r="Q476" s="3" t="n"/>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="n"/>
+      <c r="T476" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U476" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V476" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ribaxon-men-flip-flops/p/itm6c9e860de5c1b?pid=SFFHNKDC2EYMHCG5</t>
+        </is>
+      </c>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="n"/>
+      <c r="Z476" s="2" t="n"/>
+      <c r="AA476" s="2" t="n"/>
+      <c r="AB476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ribaxon-men-flip-flops/p/itm6c9e860de5c1b?pid=SFFHNKDC2EYMHCG5</t>
+        </is>
+      </c>
+      <c r="AC476" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD476" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="1">
+      <c r="A477" s="5" t="inlineStr">
+        <is>
+          <t>SUPER</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="n"/>
+      <c r="C477" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D477" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E477" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G477" s="5" t="n"/>
+      <c r="H477" s="6" t="n"/>
+      <c r="I477" s="5" t="n"/>
+      <c r="J477" s="6" t="n"/>
+      <c r="K477" s="6" t="n"/>
+      <c r="L477" s="6" t="n"/>
+      <c r="M477" s="5" t="n"/>
+      <c r="N477" s="5" t="n"/>
+      <c r="O477" s="5" t="n"/>
+      <c r="P477" s="5" t="n"/>
+      <c r="Q477" s="6" t="n"/>
+      <c r="R477" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S477" s="5" t="n"/>
+      <c r="T477" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U477" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V477" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bersache-men-slippers/p/itm9299d4d566795?pid=SFFHEZPSYGHRNZSV</t>
+        </is>
+      </c>
+      <c r="X477" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y477" s="5" t="n"/>
+      <c r="Z477" s="5" t="n"/>
+      <c r="AA477" s="5" t="n"/>
+      <c r="AB477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bersache-men-slippers/p/itm9299d4d566795?pid=SFFHEZPSYGHRNZSV</t>
+        </is>
+      </c>
+      <c r="AC477" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD477" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="1">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Alteksleeper</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="n"/>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D478" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="n"/>
+      <c r="H478" s="3" t="n"/>
+      <c r="I478" s="2" t="n"/>
+      <c r="J478" s="3" t="n"/>
+      <c r="K478" s="3" t="n"/>
+      <c r="L478" s="3" t="n"/>
+      <c r="M478" s="2" t="n"/>
+      <c r="N478" s="2" t="n"/>
+      <c r="O478" s="2" t="n"/>
+      <c r="P478" s="2" t="n"/>
+      <c r="Q478" s="3" t="n"/>
+      <c r="R478" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S478" s="2" t="n"/>
+      <c r="T478" s="3" t="n"/>
+      <c r="U478" s="3" t="n"/>
+      <c r="V478" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/altek-men-slippers/p/itmf1da538a66648?pid=SFFHG8CHFAURUCSV</t>
+        </is>
+      </c>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="n"/>
+      <c r="Z478" s="2" t="n"/>
+      <c r="AA478" s="2" t="n"/>
+      <c r="AB478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/altek-men-slippers/p/itmf1da538a66648?pid=SFFHG8CHFAURUCSV</t>
+        </is>
+      </c>
+      <c r="AC478" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD478" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="1">
+      <c r="A479" s="5" t="inlineStr">
+        <is>
+          <t>ArcatronMobility</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="n"/>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D479" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G479" s="5" t="n"/>
+      <c r="H479" s="6" t="n"/>
+      <c r="I479" s="5" t="n"/>
+      <c r="J479" s="6" t="n"/>
+      <c r="K479" s="6" t="n"/>
+      <c r="L479" s="6" t="n"/>
+      <c r="M479" s="5" t="n"/>
+      <c r="N479" s="5" t="n"/>
+      <c r="O479" s="5" t="n"/>
+      <c r="P479" s="5" t="n"/>
+      <c r="Q479" s="6" t="n"/>
+      <c r="R479" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S479" s="5" t="n"/>
+      <c r="T479" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U479" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V479" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/frido-unisex-cloud-comfort-arch-support-orthopedic-soft-home-chappal-anti-skid-sole-slippers/p/itm9230f3ef7facc?pid=SFFHMHSHK2SJ4XNX</t>
+        </is>
+      </c>
+      <c r="X479" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y479" s="5" t="n"/>
+      <c r="Z479" s="5" t="n"/>
+      <c r="AA479" s="5" t="n"/>
+      <c r="AB479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/frido-unisex-cloud-comfort-arch-support-orthopedic-soft-home-chappal-anti-skid-sole-slippers/p/itm9230f3ef7facc?pid=SFFHMHSHK2SJ4XNX</t>
+        </is>
+      </c>
+      <c r="AC479" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD479" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="1">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Acupressure</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="n"/>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D480" s="7" t="inlineStr">
+        <is>
+          <t>PARTIALLY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="n"/>
+      <c r="H480" s="3" t="n"/>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>health@favr.town</t>
+        </is>
+      </c>
+      <c r="J480" s="3" t="n"/>
+      <c r="K480" s="3" t="n"/>
+      <c r="L480" s="3" t="n"/>
+      <c r="M480" s="2" t="n"/>
+      <c r="N480" s="2" t="n"/>
+      <c r="O480" s="2" t="n"/>
+      <c r="P480" s="2" t="n"/>
+      <c r="Q480" s="3" t="n"/>
+      <c r="R480" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S480" s="2" t="inlineStr">
+        <is>
+          <t>https://acupressure.guide</t>
+        </is>
+      </c>
+      <c r="T480" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U480" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V480" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/unistar-men-acupressure-flip-flops-natural-leg-foot-massager-slippers-men-s-women-s/p/itm48e724fd75511?pid=SFFEYQPYEGGBD9MK</t>
+        </is>
+      </c>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="n"/>
+      <c r="Z480" s="2" t="n"/>
+      <c r="AA480" s="2" t="n"/>
+      <c r="AB480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/unistar-men-acupressure-flip-flops-natural-leg-foot-massager-slippers-men-s-women-s/p/itm48e724fd75511?pid=SFFEYQPYEGGBD9MK</t>
+        </is>
+      </c>
+      <c r="AC480" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD480" s="2" t="inlineStr">
+        <is>
+          <t>company_website</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="1">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>LittlePalz</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="n"/>
+      <c r="C481" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D481" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="G481" s="5" t="n"/>
+      <c r="H481" s="6" t="n"/>
+      <c r="I481" s="5" t="n"/>
+      <c r="J481" s="6" t="n"/>
+      <c r="K481" s="6" t="n"/>
+      <c r="L481" s="6" t="n"/>
+      <c r="M481" s="5" t="n"/>
+      <c r="N481" s="5" t="n"/>
+      <c r="O481" s="5" t="n"/>
+      <c r="P481" s="5" t="n"/>
+      <c r="Q481" s="6" t="n"/>
+      <c r="R481" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S481" s="5" t="n"/>
+      <c r="T481" s="6" t="n"/>
+      <c r="U481" s="6" t="n"/>
+      <c r="V481" s="6" t="n"/>
+      <c r="W481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/little-palz-girls-slip-mojaris/p/itm3a974d5816103?pid=KSSHZYJHYRN5BSTH</t>
+        </is>
+      </c>
+      <c r="X481" s="5" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="Y481" s="5" t="inlineStr">
+        <is>
+          <t>Ethnic Shoes</t>
+        </is>
+      </c>
+      <c r="Z481" s="5" t="n"/>
+      <c r="AA481" s="5" t="n"/>
+      <c r="AB481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/little-palz-girls-slip-mojaris/p/itm3a974d5816103?pid=KSSHZYJHYRN5BSTH</t>
+        </is>
+      </c>
+      <c r="AC481" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD481" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="22" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Mukundu</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="n"/>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D482" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="n"/>
+      <c r="H482" s="3" t="n"/>
+      <c r="I482" s="2" t="n"/>
+      <c r="J482" s="3" t="n"/>
+      <c r="K482" s="3" t="n"/>
+      <c r="L482" s="3" t="n"/>
+      <c r="M482" s="2" t="n"/>
+      <c r="N482" s="2" t="n"/>
+      <c r="O482" s="2" t="n"/>
+      <c r="P482" s="2" t="n"/>
+      <c r="Q482" s="3" t="n"/>
+      <c r="R482" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S482" s="2" t="n"/>
+      <c r="T482" s="3" t="n"/>
+      <c r="U482" s="3" t="n"/>
+      <c r="V482" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mukunda-footwear-girls-slip-jutis/p/itm38090e61e8e26?pid=KSSH3FTFE3UMKV7P</t>
+        </is>
+      </c>
+      <c r="X482" s="2" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="Y482" s="2" t="inlineStr">
+        <is>
+          <t>Ethnic Shoes</t>
+        </is>
+      </c>
+      <c r="Z482" s="2" t="n"/>
+      <c r="AA482" s="2" t="n"/>
+      <c r="AB482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mukunda-footwear-girls-slip-jutis/p/itm38090e61e8e26?pid=KSSH3FTFE3UMKV7P</t>
+        </is>
+      </c>
+      <c r="AC482" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD482" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="22" customHeight="1">
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>MBGINDUSTRIES</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="n"/>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E483" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="G483" s="5" t="n"/>
+      <c r="H483" s="6" t="n"/>
+      <c r="I483" s="5" t="n"/>
+      <c r="J483" s="6" t="n"/>
+      <c r="K483" s="6" t="n"/>
+      <c r="L483" s="6" t="n"/>
+      <c r="M483" s="5" t="n"/>
+      <c r="N483" s="5" t="n"/>
+      <c r="O483" s="5" t="n"/>
+      <c r="P483" s="5" t="n"/>
+      <c r="Q483" s="6" t="n"/>
+      <c r="R483" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S483" s="5" t="n"/>
+      <c r="T483" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U483" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V483" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/hitway-girls-slip-mojaris/p/itme070c805611d9?pid=KSSGZSSRZGGQGZ3Y</t>
+        </is>
+      </c>
+      <c r="X483" s="5" t="inlineStr">
+        <is>
+          <t>Girls' Footwear</t>
+        </is>
+      </c>
+      <c r="Y483" s="5" t="inlineStr">
+        <is>
+          <t>Ethnic Shoes</t>
+        </is>
+      </c>
+      <c r="Z483" s="5" t="n"/>
+      <c r="AA483" s="5" t="n"/>
+      <c r="AB483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/hitway-girls-slip-mojaris/p/itme070c805611d9?pid=KSSGZSSRZGGQGZ3Y</t>
+        </is>
+      </c>
+      <c r="AC483" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD483" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="22" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>ParagonFootwear</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="n"/>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D484" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="n"/>
+      <c r="H484" s="3" t="n"/>
+      <c r="I484" s="2" t="n"/>
+      <c r="J484" s="3" t="n"/>
+      <c r="K484" s="3" t="n"/>
+      <c r="L484" s="3" t="n"/>
+      <c r="M484" s="2" t="n"/>
+      <c r="N484" s="2" t="n"/>
+      <c r="O484" s="2" t="n"/>
+      <c r="P484" s="2" t="n"/>
+      <c r="Q484" s="3" t="n"/>
+      <c r="R484" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S484" s="2" t="n"/>
+      <c r="T484" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U484" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V484" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/paragon-men-slippers/p/itmd06e71eba374a?pid=SFFHP64QNZUST5GH</t>
+        </is>
+      </c>
+      <c r="X484" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y484" s="2" t="n"/>
+      <c r="Z484" s="2" t="n"/>
+      <c r="AA484" s="2" t="n"/>
+      <c r="AB484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/paragon-men-slippers/p/itmd06e71eba374a?pid=SFFHP64QNZUST5GH</t>
+        </is>
+      </c>
+      <c r="AC484" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD484" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="22" customHeight="1">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>CIBEK</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="n"/>
+      <c r="C485" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D485" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E485" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G485" s="5" t="n"/>
+      <c r="H485" s="6" t="n"/>
+      <c r="I485" s="5" t="n"/>
+      <c r="J485" s="6" t="n"/>
+      <c r="K485" s="6" t="n"/>
+      <c r="L485" s="6" t="n"/>
+      <c r="M485" s="5" t="n"/>
+      <c r="N485" s="5" t="n"/>
+      <c r="O485" s="5" t="n"/>
+      <c r="P485" s="5" t="n"/>
+      <c r="Q485" s="6" t="n"/>
+      <c r="R485" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S485" s="5" t="n"/>
+      <c r="T485" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U485" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V485" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cibek-women-slippers/p/itm0fb183e601776?pid=SFFHNTE4AKM7SHGQ</t>
+        </is>
+      </c>
+      <c r="X485" s="5" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y485" s="5" t="n"/>
+      <c r="Z485" s="5" t="n"/>
+      <c r="AA485" s="5" t="n"/>
+      <c r="AB485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cibek-women-slippers/p/itm0fb183e601776?pid=SFFHNTE4AKM7SHGQ</t>
+        </is>
+      </c>
+      <c r="AC485" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD485" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="22" customHeight="1">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>DivisaStore</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="n"/>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D486" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="n"/>
+      <c r="H486" s="3" t="n"/>
+      <c r="I486" s="2" t="n"/>
+      <c r="J486" s="3" t="n"/>
+      <c r="K486" s="3" t="n"/>
+      <c r="L486" s="3" t="n"/>
+      <c r="M486" s="2" t="n"/>
+      <c r="N486" s="2" t="n"/>
+      <c r="O486" s="2" t="n"/>
+      <c r="P486" s="2" t="n"/>
+      <c r="Q486" s="3" t="n"/>
+      <c r="R486" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S486" s="2" t="n"/>
+      <c r="T486" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U486" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V486" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/dr-ortho-men-accupressure-slippers/p/itmd2ca0a027f5d4?pid=SFFH9MB7UMYMH7RA</t>
+        </is>
+      </c>
+      <c r="X486" s="2" t="inlineStr">
+        <is>
+          <t>Slippers &amp; Flip Flops</t>
+        </is>
+      </c>
+      <c r="Y486" s="2" t="n"/>
+      <c r="Z486" s="2" t="n"/>
+      <c r="AA486" s="2" t="n"/>
+      <c r="AB486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/dr-ortho-men-accupressure-slippers/p/itmd2ca0a027f5d4?pid=SFFH9MB7UMYMH7RA</t>
+        </is>
+      </c>
+      <c r="AC486" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD486" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="22" customHeight="1">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>Puresole</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="n"/>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D487" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="G487" s="5" t="n"/>
+      <c r="H487" s="6" t="n"/>
+      <c r="I487" s="5" t="n"/>
+      <c r="J487" s="6" t="n"/>
+      <c r="K487" s="6" t="n"/>
+      <c r="L487" s="6" t="n"/>
+      <c r="M487" s="5" t="n"/>
+      <c r="N487" s="5" t="n"/>
+      <c r="O487" s="5" t="n"/>
+      <c r="P487" s="5" t="n"/>
+      <c r="Q487" s="6" t="n"/>
+      <c r="R487" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S487" s="5" t="n"/>
+      <c r="T487" s="6" t="n"/>
+      <c r="U487" s="6" t="n"/>
+      <c r="V487" s="6" t="n"/>
+      <c r="W487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/puresole-booties/p/itm0947cc086ee38?pid=BOOHJTYPSHYSZV5E</t>
+        </is>
+      </c>
+      <c r="X487" s="5" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="Y487" s="5" t="inlineStr">
+        <is>
+          <t>Baby Boys Footwear</t>
+        </is>
+      </c>
+      <c r="Z487" s="5" t="n"/>
+      <c r="AA487" s="5" t="n"/>
+      <c r="AB487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/puresole-booties/p/itm0947cc086ee38?pid=BOOHJTYPSHYSZV5E</t>
+        </is>
+      </c>
+      <c r="AC487" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD487" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="22" customHeight="1">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>RIDHI CREATION</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="n"/>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D488" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="n"/>
+      <c r="H488" s="3" t="n"/>
+      <c r="I488" s="2" t="n"/>
+      <c r="J488" s="3" t="n"/>
+      <c r="K488" s="3" t="n"/>
+      <c r="L488" s="3" t="n"/>
+      <c r="M488" s="2" t="n"/>
+      <c r="N488" s="2" t="n"/>
+      <c r="O488" s="2" t="n"/>
+      <c r="P488" s="2" t="n"/>
+      <c r="Q488" s="3" t="n"/>
+      <c r="R488" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S488" s="2" t="n"/>
+      <c r="T488" s="3" t="n"/>
+      <c r="U488" s="3" t="n"/>
+      <c r="V488" s="3" t="n"/>
+      <c r="W488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bullcraft-infant-soft-sole-booties-adorable-baby/p/itmea4b00576acbf?pid=BOOHPANVDHZQUY6Y</t>
+        </is>
+      </c>
+      <c r="X488" s="2" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="Y488" s="2" t="inlineStr">
+        <is>
+          <t>Baby Boys Footwear</t>
+        </is>
+      </c>
+      <c r="Z488" s="2" t="n"/>
+      <c r="AA488" s="2" t="n"/>
+      <c r="AB488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bullcraft-infant-soft-sole-booties-adorable-baby/p/itmea4b00576acbf?pid=BOOHPANVDHZQUY6Y</t>
+        </is>
+      </c>
+      <c r="AC488" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD488" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="22" customHeight="1">
+      <c r="A489" s="5" t="inlineStr">
+        <is>
+          <t>VBaby</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="n"/>
+      <c r="C489" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D489" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="G489" s="5" t="n"/>
+      <c r="H489" s="6" t="n"/>
+      <c r="I489" s="5" t="n"/>
+      <c r="J489" s="6" t="n"/>
+      <c r="K489" s="6" t="n"/>
+      <c r="L489" s="6" t="n"/>
+      <c r="M489" s="5" t="n"/>
+      <c r="N489" s="5" t="n"/>
+      <c r="O489" s="5" t="n"/>
+      <c r="P489" s="5" t="n"/>
+      <c r="Q489" s="6" t="n"/>
+      <c r="R489" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S489" s="5" t="n"/>
+      <c r="T489" s="6" t="n"/>
+      <c r="U489" s="6" t="n"/>
+      <c r="V489" s="6" t="n"/>
+      <c r="W489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vbaby-soft-step-dog-baby-shoes-winter-girl-boy-booties/p/itm2fe1db018220f?pid=BOOHJYCTZH3FAMWR</t>
+        </is>
+      </c>
+      <c r="X489" s="5" t="inlineStr">
+        <is>
+          <t>Infant Footwear</t>
+        </is>
+      </c>
+      <c r="Y489" s="5" t="inlineStr">
+        <is>
+          <t>Baby Boys Footwear</t>
+        </is>
+      </c>
+      <c r="Z489" s="5" t="n"/>
+      <c r="AA489" s="5" t="n"/>
+      <c r="AB489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vbaby-soft-step-dog-baby-shoes-winter-girl-boy-booties/p/itm2fe1db018220f?pid=BOOHJYCTZH3FAMWR</t>
+        </is>
+      </c>
+      <c r="AC489" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD489" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="22" customHeight="1">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>GOVINDEINTERPRISES</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="n"/>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D490" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="n"/>
+      <c r="H490" s="3" t="n"/>
+      <c r="I490" s="2" t="n"/>
+      <c r="J490" s="3" t="n"/>
+      <c r="K490" s="3" t="n"/>
+      <c r="L490" s="3" t="n"/>
+      <c r="M490" s="2" t="n"/>
+      <c r="N490" s="2" t="n"/>
+      <c r="O490" s="2" t="n"/>
+      <c r="P490" s="2" t="n"/>
+      <c r="Q490" s="3" t="n"/>
+      <c r="R490" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S490" s="2" t="n"/>
+      <c r="T490" s="3" t="n"/>
+      <c r="U490" s="3" t="n"/>
+      <c r="V490" s="3" t="n"/>
+      <c r="W490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/govind-booties/p/itm0a8cc11684c90?pid=BOOGNXJ6VHUZP6QM</t>
+        </is>
+      </c>
+      <c r="X490" s="2" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="Y490" s="2" t="n"/>
+      <c r="Z490" s="2" t="n"/>
+      <c r="AA490" s="2" t="n"/>
+      <c r="AB490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/govind-booties/p/itm0a8cc11684c90?pid=BOOGNXJ6VHUZP6QM</t>
+        </is>
+      </c>
+      <c r="AC490" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD490" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="22" customHeight="1">
+      <c r="A491" s="5" t="inlineStr">
+        <is>
+          <t>Trecify</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="n"/>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D491" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E491" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="G491" s="5" t="n"/>
+      <c r="H491" s="6" t="n"/>
+      <c r="I491" s="5" t="n"/>
+      <c r="J491" s="6" t="n"/>
+      <c r="K491" s="6" t="n"/>
+      <c r="L491" s="6" t="n"/>
+      <c r="M491" s="5" t="n"/>
+      <c r="N491" s="5" t="n"/>
+      <c r="O491" s="5" t="n"/>
+      <c r="P491" s="5" t="n"/>
+      <c r="Q491" s="6" t="n"/>
+      <c r="R491" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S491" s="5" t="n"/>
+      <c r="T491" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U491" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V491" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/trecify-booties/p/itm8eadce960d5d9?pid=BOOHJJEZPNNX66GM</t>
+        </is>
+      </c>
+      <c r="X491" s="5" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="Y491" s="5" t="n"/>
+      <c r="Z491" s="5" t="n"/>
+      <c r="AA491" s="5" t="n"/>
+      <c r="AB491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/trecify-booties/p/itm8eadce960d5d9?pid=BOOHJJEZPNNX66GM</t>
+        </is>
+      </c>
+      <c r="AC491" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD491" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="22" customHeight="1">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>KRISHNAM2025</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="n"/>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D492" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="n"/>
+      <c r="H492" s="3" t="n"/>
+      <c r="I492" s="2" t="n"/>
+      <c r="J492" s="3" t="n"/>
+      <c r="K492" s="3" t="n"/>
+      <c r="L492" s="3" t="n"/>
+      <c r="M492" s="2" t="n"/>
+      <c r="N492" s="2" t="n"/>
+      <c r="O492" s="2" t="n"/>
+      <c r="P492" s="2" t="n"/>
+      <c r="Q492" s="3" t="n"/>
+      <c r="R492" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S492" s="2" t="n"/>
+      <c r="T492" s="3" t="n"/>
+      <c r="U492" s="3" t="n"/>
+      <c r="V492" s="3" t="n"/>
+      <c r="W492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/angaakar-001-booties/p/itm893e7545787f4?pid=BOOHJNCDAAJS3X2V</t>
+        </is>
+      </c>
+      <c r="X492" s="2" t="inlineStr">
+        <is>
+          <t>Booties</t>
+        </is>
+      </c>
+      <c r="Y492" s="2" t="n"/>
+      <c r="Z492" s="2" t="n"/>
+      <c r="AA492" s="2" t="n"/>
+      <c r="AB492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/angaakar-001-booties/p/itm893e7545787f4?pid=BOOHJNCDAAJS3X2V</t>
+        </is>
+      </c>
+      <c r="AC492" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD492" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="22" customHeight="1">
+      <c r="A493" s="5" t="inlineStr">
+        <is>
+          <t>PrabhuEnterprises1</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="n"/>
+      <c r="C493" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D493" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E493" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G493" s="5" t="n"/>
+      <c r="H493" s="6" t="n"/>
+      <c r="I493" s="5" t="n"/>
+      <c r="J493" s="6" t="n"/>
+      <c r="K493" s="6" t="n"/>
+      <c r="L493" s="6" t="n"/>
+      <c r="M493" s="5" t="n"/>
+      <c r="N493" s="5" t="n"/>
+      <c r="O493" s="5" t="n"/>
+      <c r="P493" s="5" t="n"/>
+      <c r="Q493" s="6" t="n"/>
+      <c r="R493" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S493" s="5" t="n"/>
+      <c r="T493" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U493" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V493" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/inivaene-regular-men-black-jeans/p/itm6dbc688bd6cd7?pid=JEAHD8FHVVZYY6QY</t>
+        </is>
+      </c>
+      <c r="X493" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y493" s="5" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z493" s="5" t="n"/>
+      <c r="AA493" s="5" t="n"/>
+      <c r="AB493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/inivaene-regular-men-black-jeans/p/itm6dbc688bd6cd7?pid=JEAHD8FHVVZYY6QY</t>
+        </is>
+      </c>
+      <c r="AC493" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD493" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="22" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>4FLIES</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="n"/>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D494" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="n"/>
+      <c r="H494" s="3" t="n"/>
+      <c r="I494" s="2" t="n"/>
+      <c r="J494" s="3" t="n"/>
+      <c r="K494" s="3" t="n"/>
+      <c r="L494" s="3" t="n"/>
+      <c r="M494" s="2" t="n"/>
+      <c r="N494" s="2" t="n"/>
+      <c r="O494" s="2" t="n"/>
+      <c r="P494" s="2" t="n"/>
+      <c r="Q494" s="3" t="n"/>
+      <c r="R494" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S494" s="2" t="n"/>
+      <c r="T494" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U494" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V494" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/3butterflies-skinny-women-black-jeans/p/itmea250cf972f91?pid=JEAHE29ZMMYFQGPZ</t>
+        </is>
+      </c>
+      <c r="X494" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y494" s="2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z494" s="2" t="n"/>
+      <c r="AA494" s="2" t="n"/>
+      <c r="AB494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/3butterflies-skinny-women-black-jeans/p/itmea250cf972f91?pid=JEAHE29ZMMYFQGPZ</t>
+        </is>
+      </c>
+      <c r="AC494" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD494" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="22" customHeight="1">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>SBTSTORE</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="n"/>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D495" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G495" s="5" t="n"/>
+      <c r="H495" s="6" t="n"/>
+      <c r="I495" s="5" t="n"/>
+      <c r="J495" s="6" t="n"/>
+      <c r="K495" s="6" t="n"/>
+      <c r="L495" s="6" t="n"/>
+      <c r="M495" s="5" t="n"/>
+      <c r="N495" s="5" t="n"/>
+      <c r="O495" s="5" t="n"/>
+      <c r="P495" s="5" t="n"/>
+      <c r="Q495" s="6" t="n"/>
+      <c r="R495" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S495" s="5" t="n"/>
+      <c r="T495" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U495" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V495" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tyffyn-wide-leg-women-blue-jeans/p/itm8f63f4958145d?pid=JEAHNHR2JWWNU3JW</t>
+        </is>
+      </c>
+      <c r="X495" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y495" s="5" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z495" s="5" t="n"/>
+      <c r="AA495" s="5" t="n"/>
+      <c r="AB495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tyffyn-wide-leg-women-blue-jeans/p/itm8f63f4958145d?pid=JEAHNHR2JWWNU3JW</t>
+        </is>
+      </c>
+      <c r="AC495" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD495" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="22" customHeight="1">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>MARUTISTORE</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="n"/>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D496" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="n"/>
+      <c r="H496" s="3" t="n"/>
+      <c r="I496" s="2" t="n"/>
+      <c r="J496" s="3" t="n"/>
+      <c r="K496" s="3" t="n"/>
+      <c r="L496" s="3" t="n"/>
+      <c r="M496" s="2" t="n"/>
+      <c r="N496" s="2" t="n"/>
+      <c r="O496" s="2" t="n"/>
+      <c r="P496" s="2" t="n"/>
+      <c r="Q496" s="3" t="n"/>
+      <c r="R496" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S496" s="2" t="n"/>
+      <c r="T496" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U496" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V496" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/moudlin-regular-men-light-blue-jeans/p/itm6008d8782af65?pid=JEAHFCTGMBZEYGGY</t>
+        </is>
+      </c>
+      <c r="X496" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y496" s="2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z496" s="2" t="n"/>
+      <c r="AA496" s="2" t="n"/>
+      <c r="AB496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/moudlin-regular-men-light-blue-jeans/p/itm6008d8782af65?pid=JEAHFCTGMBZEYGGY</t>
+        </is>
+      </c>
+      <c r="AC496" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD496" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="22" customHeight="1">
+      <c r="A497" s="5" t="inlineStr">
+        <is>
+          <t>ZARISTAAA</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="n"/>
+      <c r="C497" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D497" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G497" s="5" t="n"/>
+      <c r="H497" s="6" t="n"/>
+      <c r="I497" s="5" t="n"/>
+      <c r="J497" s="6" t="n"/>
+      <c r="K497" s="6" t="n"/>
+      <c r="L497" s="6" t="n"/>
+      <c r="M497" s="5" t="n"/>
+      <c r="N497" s="5" t="n"/>
+      <c r="O497" s="5" t="n"/>
+      <c r="P497" s="5" t="n"/>
+      <c r="Q497" s="6" t="n"/>
+      <c r="R497" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S497" s="5" t="n"/>
+      <c r="T497" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U497" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V497" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zaristaa-flared-women-light-blue-jeans/p/itm1d3d11b18b4f5?pid=JEAHNWS7VHAVUZFS</t>
+        </is>
+      </c>
+      <c r="X497" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y497" s="5" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z497" s="5" t="n"/>
+      <c r="AA497" s="5" t="n"/>
+      <c r="AB497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zaristaa-flared-women-light-blue-jeans/p/itm1d3d11b18b4f5?pid=JEAHNWS7VHAVUZFS</t>
+        </is>
+      </c>
+      <c r="AC497" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD497" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="22" customHeight="1">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>3butterflies</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="n"/>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D498" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="n"/>
+      <c r="H498" s="3" t="n"/>
+      <c r="I498" s="2" t="n"/>
+      <c r="J498" s="3" t="n"/>
+      <c r="K498" s="3" t="n"/>
+      <c r="L498" s="3" t="n"/>
+      <c r="M498" s="2" t="n"/>
+      <c r="N498" s="2" t="n"/>
+      <c r="O498" s="2" t="n"/>
+      <c r="P498" s="2" t="n"/>
+      <c r="Q498" s="3" t="n"/>
+      <c r="R498" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S498" s="2" t="n"/>
+      <c r="T498" s="3" t="n"/>
+      <c r="U498" s="3" t="n"/>
+      <c r="V498" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/3butterflies-flared-women-dark-blue-jeans/p/itmf9de44f542c6f?pid=JEAHMAZVZ5APFHRD</t>
+        </is>
+      </c>
+      <c r="X498" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y498" s="2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z498" s="2" t="n"/>
+      <c r="AA498" s="2" t="n"/>
+      <c r="AB498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/3butterflies-flared-women-dark-blue-jeans/p/itmf9de44f542c6f?pid=JEAHMAZVZ5APFHRD</t>
+        </is>
+      </c>
+      <c r="AC498" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD498" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="22" customHeight="1">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>MRFASHION</t>
+        </is>
+      </c>
+      <c r="B499" s="5" t="n"/>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D499" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E499" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G499" s="5" t="n"/>
+      <c r="H499" s="6" t="n"/>
+      <c r="I499" s="5" t="n"/>
+      <c r="J499" s="6" t="n"/>
+      <c r="K499" s="6" t="n"/>
+      <c r="L499" s="6" t="n"/>
+      <c r="M499" s="5" t="n"/>
+      <c r="N499" s="5" t="n"/>
+      <c r="O499" s="5" t="n"/>
+      <c r="P499" s="5" t="n"/>
+      <c r="Q499" s="6" t="n"/>
+      <c r="R499" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S499" s="5" t="n"/>
+      <c r="T499" s="6" t="n"/>
+      <c r="U499" s="6" t="n"/>
+      <c r="V499" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W499" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/wearo-jeans-regular-men-black/p/itme0706cc7a068f?pid=JEAHC4B7GSYHZA9H</t>
+        </is>
+      </c>
+      <c r="X499" s="5" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y499" s="5" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z499" s="5" t="n"/>
+      <c r="AA499" s="5" t="n"/>
+      <c r="AB499" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/wearo-jeans-regular-men-black/p/itme0706cc7a068f?pid=JEAHC4B7GSYHZA9H</t>
+        </is>
+      </c>
+      <c r="AC499" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD499" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="22" customHeight="1">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>KARANFASHIONHUB</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="n"/>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D500" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="n"/>
+      <c r="H500" s="3" t="n"/>
+      <c r="I500" s="2" t="n"/>
+      <c r="J500" s="3" t="n"/>
+      <c r="K500" s="3" t="n"/>
+      <c r="L500" s="3" t="n"/>
+      <c r="M500" s="2" t="n"/>
+      <c r="N500" s="2" t="n"/>
+      <c r="O500" s="2" t="n"/>
+      <c r="P500" s="2" t="n"/>
+      <c r="Q500" s="3" t="n"/>
+      <c r="R500" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S500" s="2" t="n"/>
+      <c r="T500" s="3" t="n"/>
+      <c r="U500" s="3" t="n"/>
+      <c r="V500" s="3" t="n"/>
+      <c r="W500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metronaut-wide-leg-women-light-blue-jeans/p/itm7703ee2ae732d?pid=JEAHPF9V89BUFH27</t>
+        </is>
+      </c>
+      <c r="X500" s="2" t="inlineStr">
+        <is>
+          <t>Bottom Wear</t>
+        </is>
+      </c>
+      <c r="Y500" s="2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="Z500" s="2" t="n"/>
+      <c r="AA500" s="2" t="n"/>
+      <c r="AB500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metronaut-wide-leg-women-light-blue-jeans/p/itm7703ee2ae732d?pid=JEAHPF9V89BUFH27</t>
+        </is>
+      </c>
+      <c r="AC500" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD500" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="5" t="inlineStr">
+        <is>
+          <t>Pesado</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="n"/>
+      <c r="C501" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D501" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G501" s="5" t="n"/>
+      <c r="H501" s="6" t="n"/>
+      <c r="I501" s="5" t="n"/>
+      <c r="J501" s="6" t="n"/>
+      <c r="K501" s="6" t="n"/>
+      <c r="L501" s="6" t="n"/>
+      <c r="M501" s="5" t="n"/>
+      <c r="N501" s="5" t="n"/>
+      <c r="O501" s="5" t="n"/>
+      <c r="P501" s="5" t="n"/>
+      <c r="Q501" s="6" t="n"/>
+      <c r="R501" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S501" s="5" t="n"/>
+      <c r="T501" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U501" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V501" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W501" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pesado-slim-fit-men-green-trousers/p/itm19e9c1b481b56?pid=TROGMKA9T6GWAMFF</t>
+        </is>
+      </c>
+      <c r="X501" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y501" s="5" t="n"/>
+      <c r="Z501" s="5" t="n"/>
+      <c r="AA501" s="5" t="n"/>
+      <c r="AB501" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pesado-slim-fit-men-green-trousers/p/itm19e9c1b481b56?pid=TROGMKA9T6GWAMFF</t>
+        </is>
+      </c>
+      <c r="AC501" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD501" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="22" customHeight="1">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>AKAYAAPPARELS</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="n"/>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D502" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="n"/>
+      <c r="H502" s="3" t="n"/>
+      <c r="I502" s="2" t="n"/>
+      <c r="J502" s="3" t="n"/>
+      <c r="K502" s="3" t="n"/>
+      <c r="L502" s="3" t="n"/>
+      <c r="M502" s="2" t="n"/>
+      <c r="N502" s="2" t="n"/>
+      <c r="O502" s="2" t="n"/>
+      <c r="P502" s="2" t="n"/>
+      <c r="Q502" s="3" t="n"/>
+      <c r="R502" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S502" s="2" t="n"/>
+      <c r="T502" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U502" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V502" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itme0c404571a277?pid=TROHZGH5AHHZQHNK</t>
+        </is>
+      </c>
+      <c r="X502" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y502" s="2" t="n"/>
+      <c r="Z502" s="2" t="n"/>
+      <c r="AA502" s="2" t="n"/>
+      <c r="AB502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itme0c404571a277?pid=TROHZGH5AHHZQHNK</t>
+        </is>
+      </c>
+      <c r="AC502" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD502" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="22" customHeight="1">
+      <c r="A503" s="5" t="inlineStr">
+        <is>
+          <t>OSWAL NETWORK PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="n"/>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D503" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E503" s="5" t="inlineStr">
+        <is>
+          <t>Private Limited Company</t>
+        </is>
+      </c>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G503" s="5" t="n"/>
+      <c r="H503" s="6" t="n"/>
+      <c r="I503" s="5" t="n"/>
+      <c r="J503" s="6" t="n"/>
+      <c r="K503" s="6" t="n"/>
+      <c r="L503" s="6" t="n"/>
+      <c r="M503" s="5" t="n"/>
+      <c r="N503" s="5" t="n"/>
+      <c r="O503" s="5" t="n"/>
+      <c r="P503" s="5" t="n"/>
+      <c r="Q503" s="6" t="n"/>
+      <c r="R503" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S503" s="5" t="n"/>
+      <c r="T503" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U503" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V503" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W503" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ad-av-regular-fit-men-black-trousers/p/itmfgpmyczzn5hyz?pid=TROFGPJWAHPHH97B</t>
+        </is>
+      </c>
+      <c r="X503" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y503" s="5" t="n"/>
+      <c r="Z503" s="5" t="n"/>
+      <c r="AA503" s="5" t="n"/>
+      <c r="AB503" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ad-av-regular-fit-men-black-trousers/p/itmfgpmyczzn5hyz?pid=TROFGPJWAHPHH97B</t>
+        </is>
+      </c>
+      <c r="AC503" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD503" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="22" customHeight="1">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>ManakStore</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="n"/>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D504" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="n"/>
+      <c r="H504" s="3" t="n"/>
+      <c r="I504" s="2" t="n"/>
+      <c r="J504" s="3" t="n"/>
+      <c r="K504" s="3" t="n"/>
+      <c r="L504" s="3" t="n"/>
+      <c r="M504" s="2" t="n"/>
+      <c r="N504" s="2" t="n"/>
+      <c r="O504" s="2" t="n"/>
+      <c r="P504" s="2" t="n"/>
+      <c r="Q504" s="3" t="n"/>
+      <c r="R504" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S504" s="2" t="n"/>
+      <c r="T504" s="3" t="n"/>
+      <c r="U504" s="3" t="n"/>
+      <c r="V504" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-cream-trousers/p/itm8b337c68d0e34?pid=TROHZGH9JJY4YSWH</t>
+        </is>
+      </c>
+      <c r="X504" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y504" s="2" t="n"/>
+      <c r="Z504" s="2" t="n"/>
+      <c r="AA504" s="2" t="n"/>
+      <c r="AB504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-cream-trousers/p/itm8b337c68d0e34?pid=TROHZGH9JJY4YSWH</t>
+        </is>
+      </c>
+      <c r="AC504" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD504" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="22" customHeight="1">
+      <c r="A505" s="5" t="inlineStr">
+        <is>
+          <t>GralinHollie</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="n"/>
+      <c r="C505" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D505" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E505" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G505" s="5" t="n"/>
+      <c r="H505" s="6" t="n"/>
+      <c r="I505" s="5" t="n"/>
+      <c r="J505" s="6" t="n"/>
+      <c r="K505" s="6" t="n"/>
+      <c r="L505" s="6" t="n"/>
+      <c r="M505" s="5" t="n"/>
+      <c r="N505" s="5" t="n"/>
+      <c r="O505" s="5" t="n"/>
+      <c r="P505" s="5" t="n"/>
+      <c r="Q505" s="6" t="n"/>
+      <c r="R505" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S505" s="5" t="n"/>
+      <c r="T505" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U505" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V505" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W505" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gralin-hollie-slim-fit-men-black-trousers/p/itm590295fd43789?pid=TROHHAEBZE8SAZWT</t>
+        </is>
+      </c>
+      <c r="X505" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y505" s="5" t="n"/>
+      <c r="Z505" s="5" t="n"/>
+      <c r="AA505" s="5" t="n"/>
+      <c r="AB505" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gralin-hollie-slim-fit-men-black-trousers/p/itm590295fd43789?pid=TROHHAEBZE8SAZWT</t>
+        </is>
+      </c>
+      <c r="AC505" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD505" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="22" customHeight="1">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>MarcNTailor</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="n"/>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D506" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="n"/>
+      <c r="H506" s="3" t="n"/>
+      <c r="I506" s="2" t="n"/>
+      <c r="J506" s="3" t="n"/>
+      <c r="K506" s="3" t="n"/>
+      <c r="L506" s="3" t="n"/>
+      <c r="M506" s="2" t="n"/>
+      <c r="N506" s="2" t="n"/>
+      <c r="O506" s="2" t="n"/>
+      <c r="P506" s="2" t="n"/>
+      <c r="Q506" s="3" t="n"/>
+      <c r="R506" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S506" s="2" t="n"/>
+      <c r="T506" s="3" t="n"/>
+      <c r="U506" s="3" t="n"/>
+      <c r="V506" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/marcntailor-tapered-men-white-trousers/p/itmbc5d15bd3eb6a?pid=TROHAY4YXDHTTGNH</t>
+        </is>
+      </c>
+      <c r="X506" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y506" s="2" t="n"/>
+      <c r="Z506" s="2" t="n"/>
+      <c r="AA506" s="2" t="n"/>
+      <c r="AB506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/marcntailor-tapered-men-white-trousers/p/itmbc5d15bd3eb6a?pid=TROHAY4YXDHTTGNH</t>
+        </is>
+      </c>
+      <c r="AC506" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD506" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="22" customHeight="1">
+      <c r="A507" s="5" t="inlineStr">
+        <is>
+          <t>KATELACREATION</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="n"/>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D507" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E507" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G507" s="5" t="n"/>
+      <c r="H507" s="6" t="n"/>
+      <c r="I507" s="5" t="n"/>
+      <c r="J507" s="6" t="n"/>
+      <c r="K507" s="6" t="n"/>
+      <c r="L507" s="6" t="n"/>
+      <c r="M507" s="5" t="n"/>
+      <c r="N507" s="5" t="n"/>
+      <c r="O507" s="5" t="n"/>
+      <c r="P507" s="5" t="n"/>
+      <c r="Q507" s="6" t="n"/>
+      <c r="R507" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S507" s="5" t="n"/>
+      <c r="T507" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U507" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V507" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W507" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fubar-regular-fit-men-black-trousers/p/itmfac6bee203897?pid=TROH7X3AYBNFRXSF</t>
+        </is>
+      </c>
+      <c r="X507" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y507" s="5" t="n"/>
+      <c r="Z507" s="5" t="n"/>
+      <c r="AA507" s="5" t="n"/>
+      <c r="AB507" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fubar-regular-fit-men-black-trousers/p/itmfac6bee203897?pid=TROH7X3AYBNFRXSF</t>
+        </is>
+      </c>
+      <c r="AC507" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD507" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="22" customHeight="1">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>AUSTENSTITCHERY</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="n"/>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D508" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="n"/>
+      <c r="H508" s="3" t="n"/>
+      <c r="I508" s="2" t="n"/>
+      <c r="J508" s="3" t="n"/>
+      <c r="K508" s="3" t="n"/>
+      <c r="L508" s="3" t="n"/>
+      <c r="M508" s="2" t="n"/>
+      <c r="N508" s="2" t="n"/>
+      <c r="O508" s="2" t="n"/>
+      <c r="P508" s="2" t="n"/>
+      <c r="Q508" s="3" t="n"/>
+      <c r="R508" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S508" s="2" t="n"/>
+      <c r="T508" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U508" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V508" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itm6b1479a914291?pid=TROHZGH5S4XMFPTG</t>
+        </is>
+      </c>
+      <c r="X508" s="2" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y508" s="2" t="n"/>
+      <c r="Z508" s="2" t="n"/>
+      <c r="AA508" s="2" t="n"/>
+      <c r="AB508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itm6b1479a914291?pid=TROHZGH5S4XMFPTG</t>
+        </is>
+      </c>
+      <c r="AC508" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD508" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>1stShreeJiEnterprises</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="n"/>
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D509" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="n"/>
+      <c r="H509" s="6" t="n"/>
+      <c r="I509" s="5" t="n"/>
+      <c r="J509" s="6" t="n"/>
+      <c r="K509" s="6" t="n"/>
+      <c r="L509" s="6" t="n"/>
+      <c r="M509" s="5" t="n"/>
+      <c r="N509" s="5" t="n"/>
+      <c r="O509" s="5" t="n"/>
+      <c r="P509" s="5" t="n"/>
+      <c r="Q509" s="6" t="n"/>
+      <c r="R509" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S509" s="5" t="n"/>
+      <c r="T509" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U509" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V509" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W509" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itmd4419e16a70a1?pid=TROHZGH53TTYZMCU</t>
+        </is>
+      </c>
+      <c r="X509" s="5" t="inlineStr">
+        <is>
+          <t>Formal Trousers</t>
+        </is>
+      </c>
+      <c r="Y509" s="5" t="n"/>
+      <c r="Z509" s="5" t="n"/>
+      <c r="AA509" s="5" t="n"/>
+      <c r="AB509" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itmd4419e16a70a1?pid=TROHZGH53TTYZMCU</t>
+        </is>
+      </c>
+      <c r="AC509" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD509" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>KAJARU_V</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="n"/>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D510" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="n"/>
+      <c r="H510" s="3" t="n"/>
+      <c r="I510" s="2" t="n"/>
+      <c r="J510" s="3" t="n"/>
+      <c r="K510" s="3" t="n"/>
+      <c r="L510" s="3" t="n"/>
+      <c r="M510" s="2" t="n"/>
+      <c r="N510" s="2" t="n"/>
+      <c r="O510" s="2" t="n"/>
+      <c r="P510" s="2" t="n"/>
+      <c r="Q510" s="3" t="n"/>
+      <c r="R510" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S510" s="2" t="n"/>
+      <c r="T510" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U510" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V510" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kajaru-solid-men-beige-cargo-shorts/p/itm4d39a6d094b50?pid=SRTHEPQT8XSEHNSB</t>
+        </is>
+      </c>
+      <c r="X510" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y510" s="2" t="n"/>
+      <c r="Z510" s="2" t="n"/>
+      <c r="AA510" s="2" t="n"/>
+      <c r="AB510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kajaru-solid-men-beige-cargo-shorts/p/itm4d39a6d094b50?pid=SRTHEPQT8XSEHNSB</t>
+        </is>
+      </c>
+      <c r="AC510" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD510" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="22" customHeight="1">
+      <c r="A511" s="5" t="inlineStr">
+        <is>
+          <t>PITZZ ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="n"/>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D511" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E511" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G511" s="5" t="n"/>
+      <c r="H511" s="6" t="n"/>
+      <c r="I511" s="5" t="n"/>
+      <c r="J511" s="6" t="n"/>
+      <c r="K511" s="6" t="n"/>
+      <c r="L511" s="6" t="n"/>
+      <c r="M511" s="5" t="n"/>
+      <c r="N511" s="5" t="n"/>
+      <c r="O511" s="5" t="n"/>
+      <c r="P511" s="5" t="n"/>
+      <c r="Q511" s="6" t="n"/>
+      <c r="R511" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S511" s="5" t="n"/>
+      <c r="T511" s="6" t="n"/>
+      <c r="U511" s="6" t="n"/>
+      <c r="V511" s="6" t="n"/>
+      <c r="W511" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pitzz-printed-men-grey-cargo-shorts/p/itm0a148475230c6?pid=SRTHPHCSHCHFKMPK</t>
+        </is>
+      </c>
+      <c r="X511" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y511" s="5" t="n"/>
+      <c r="Z511" s="5" t="n"/>
+      <c r="AA511" s="5" t="n"/>
+      <c r="AB511" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pitzz-printed-men-grey-cargo-shorts/p/itm0a148475230c6?pid=SRTHPHCSHCHFKMPK</t>
+        </is>
+      </c>
+      <c r="AC511" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD511" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="22" customHeight="1">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>RADHE_CREATION_</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="n"/>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D512" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="n"/>
+      <c r="H512" s="3" t="n"/>
+      <c r="I512" s="2" t="n"/>
+      <c r="J512" s="3" t="n"/>
+      <c r="K512" s="3" t="n"/>
+      <c r="L512" s="3" t="n"/>
+      <c r="M512" s="2" t="n"/>
+      <c r="N512" s="2" t="n"/>
+      <c r="O512" s="2" t="n"/>
+      <c r="P512" s="2" t="n"/>
+      <c r="Q512" s="3" t="n"/>
+      <c r="R512" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S512" s="2" t="n"/>
+      <c r="T512" s="3" t="n"/>
+      <c r="U512" s="3" t="n"/>
+      <c r="V512" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/glam-elegance-solid-men-grey-cargo-shorts/p/itm2bf1c92520515?pid=SRTHPHJUXBZDZZBK</t>
+        </is>
+      </c>
+      <c r="X512" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y512" s="2" t="n"/>
+      <c r="Z512" s="2" t="n"/>
+      <c r="AA512" s="2" t="n"/>
+      <c r="AB512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/glam-elegance-solid-men-grey-cargo-shorts/p/itm2bf1c92520515?pid=SRTHPHJUXBZDZZBK</t>
+        </is>
+      </c>
+      <c r="AC512" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD512" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="22" customHeight="1">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>Minicuddle</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="n"/>
+      <c r="C513" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D513" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E513" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G513" s="5" t="n"/>
+      <c r="H513" s="6" t="n"/>
+      <c r="I513" s="5" t="n"/>
+      <c r="J513" s="6" t="n"/>
+      <c r="K513" s="6" t="n"/>
+      <c r="L513" s="6" t="n"/>
+      <c r="M513" s="5" t="n"/>
+      <c r="N513" s="5" t="n"/>
+      <c r="O513" s="5" t="n"/>
+      <c r="P513" s="5" t="n"/>
+      <c r="Q513" s="6" t="n"/>
+      <c r="R513" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S513" s="5" t="n"/>
+      <c r="T513" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U513" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V513" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W513" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/uwald-creation-solid-men-multicolor-cargo-shorts/p/itmc6719bba07dd9?pid=SRTHJJYVTBSPKJNV</t>
+        </is>
+      </c>
+      <c r="X513" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y513" s="5" t="n"/>
+      <c r="Z513" s="5" t="n"/>
+      <c r="AA513" s="5" t="n"/>
+      <c r="AB513" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/uwald-creation-solid-men-multicolor-cargo-shorts/p/itmc6719bba07dd9?pid=SRTHJJYVTBSPKJNV</t>
+        </is>
+      </c>
+      <c r="AC513" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD513" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="22" customHeight="1">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>JYOTPOOJA</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="n"/>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D514" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="n"/>
+      <c r="H514" s="3" t="n"/>
+      <c r="I514" s="2" t="n"/>
+      <c r="J514" s="3" t="n"/>
+      <c r="K514" s="3" t="n"/>
+      <c r="L514" s="3" t="n"/>
+      <c r="M514" s="2" t="n"/>
+      <c r="N514" s="2" t="n"/>
+      <c r="O514" s="2" t="n"/>
+      <c r="P514" s="2" t="n"/>
+      <c r="Q514" s="3" t="n"/>
+      <c r="R514" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S514" s="2" t="n"/>
+      <c r="T514" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U514" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V514" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vertali-industries-printed-men-green-cargo-shorts/p/itm869e20d707c77?pid=SRTHPQ2ZWCGZSP6A</t>
+        </is>
+      </c>
+      <c r="X514" s="2" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y514" s="2" t="n"/>
+      <c r="Z514" s="2" t="n"/>
+      <c r="AA514" s="2" t="n"/>
+      <c r="AB514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vertali-industries-printed-men-green-cargo-shorts/p/itm869e20d707c77?pid=SRTHPQ2ZWCGZSP6A</t>
+        </is>
+      </c>
+      <c r="AC514" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD514" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="22" customHeight="1">
+      <c r="A515" s="5" t="inlineStr">
+        <is>
+          <t>RiddhamCollection</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="n"/>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D515" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E515" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="G515" s="5" t="n"/>
+      <c r="H515" s="6" t="n"/>
+      <c r="I515" s="5" t="n"/>
+      <c r="J515" s="6" t="n"/>
+      <c r="K515" s="6" t="n"/>
+      <c r="L515" s="6" t="n"/>
+      <c r="M515" s="5" t="n"/>
+      <c r="N515" s="5" t="n"/>
+      <c r="O515" s="5" t="n"/>
+      <c r="P515" s="5" t="n"/>
+      <c r="Q515" s="6" t="n"/>
+      <c r="R515" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S515" s="5" t="n"/>
+      <c r="T515" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U515" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V515" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W515" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fragment-short-boys-girls-casual-solid-cotton-blend/p/itmb0b79c0d89e93?pid=KSHHFHCRBAJBHMBH</t>
+        </is>
+      </c>
+      <c r="X515" s="5" t="inlineStr">
+        <is>
+          <t>Cargo Shorts</t>
+        </is>
+      </c>
+      <c r="Y515" s="5" t="n"/>
+      <c r="Z515" s="5" t="n"/>
+      <c r="AA515" s="5" t="n"/>
+      <c r="AB515" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fragment-short-boys-girls-casual-solid-cotton-blend/p/itmb0b79c0d89e93?pid=KSHHFHCRBAJBHMBH</t>
+        </is>
+      </c>
+      <c r="AC515" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD515" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="22" customHeight="1">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Munnz</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="n"/>
+      <c r="C516" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D516" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="n"/>
+      <c r="H516" s="3" t="n"/>
+      <c r="I516" s="2" t="n"/>
+      <c r="J516" s="3" t="n"/>
+      <c r="K516" s="3" t="n"/>
+      <c r="L516" s="3" t="n"/>
+      <c r="M516" s="2" t="n"/>
+      <c r="N516" s="2" t="n"/>
+      <c r="O516" s="2" t="n"/>
+      <c r="P516" s="2" t="n"/>
+      <c r="Q516" s="3" t="n"/>
+      <c r="R516" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S516" s="2" t="n"/>
+      <c r="T516" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U516" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V516" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
+        </is>
+      </c>
+      <c r="X516" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y516" s="2" t="n"/>
+      <c r="Z516" s="2" t="n"/>
+      <c r="AA516" s="2" t="n"/>
+      <c r="AB516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
+        </is>
+      </c>
+      <c r="AC516" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD516" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="22" customHeight="1">
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>RIZIMCLOTHING</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="n"/>
+      <c r="C517" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D517" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E517" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G517" s="5" t="n"/>
+      <c r="H517" s="6" t="n"/>
+      <c r="I517" s="5" t="n"/>
+      <c r="J517" s="6" t="n"/>
+      <c r="K517" s="6" t="n"/>
+      <c r="L517" s="6" t="n"/>
+      <c r="M517" s="5" t="n"/>
+      <c r="N517" s="5" t="n"/>
+      <c r="O517" s="5" t="n"/>
+      <c r="P517" s="5" t="n"/>
+      <c r="Q517" s="6" t="n"/>
+      <c r="R517" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S517" s="5" t="n"/>
+      <c r="T517" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U517" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V517" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W517" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/chhote-nawab-solid-women-three-fourths/p/itm6b173939d6fdf?pid=TFHHEGJURRPNZHME</t>
+        </is>
+      </c>
+      <c r="X517" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y517" s="5" t="n"/>
+      <c r="Z517" s="5" t="n"/>
+      <c r="AA517" s="5" t="n"/>
+      <c r="AB517" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/chhote-nawab-solid-women-three-fourths/p/itm6b173939d6fdf?pid=TFHHEGJURRPNZHME</t>
+        </is>
+      </c>
+      <c r="AC517" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD517" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="22" customHeight="1">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>BHAVAY</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="n"/>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D518" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="n"/>
+      <c r="H518" s="3" t="n"/>
+      <c r="I518" s="2" t="n"/>
+      <c r="J518" s="3" t="n"/>
+      <c r="K518" s="3" t="n"/>
+      <c r="L518" s="3" t="n"/>
+      <c r="M518" s="2" t="n"/>
+      <c r="N518" s="2" t="n"/>
+      <c r="O518" s="2" t="n"/>
+      <c r="P518" s="2" t="n"/>
+      <c r="Q518" s="3" t="n"/>
+      <c r="R518" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S518" s="2" t="n"/>
+      <c r="T518" s="3" t="n"/>
+      <c r="U518" s="3" t="n"/>
+      <c r="V518" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/proxima-striped-men-three-fourths/p/itm7961f4cd42893?pid=TFHG9ZVZM3KFC2AX</t>
+        </is>
+      </c>
+      <c r="X518" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y518" s="2" t="n"/>
+      <c r="Z518" s="2" t="n"/>
+      <c r="AA518" s="2" t="n"/>
+      <c r="AB518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/proxima-striped-men-three-fourths/p/itm7961f4cd42893?pid=TFHG9ZVZM3KFC2AX</t>
+        </is>
+      </c>
+      <c r="AC518" s="2" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD518" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="22" customHeight="1">
+      <c r="A519" s="5" t="inlineStr">
+        <is>
+          <t>BIKROM GARMENTS</t>
+        </is>
+      </c>
+      <c r="B519" s="5" t="n"/>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D519" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E519" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G519" s="5" t="n"/>
+      <c r="H519" s="6" t="n"/>
+      <c r="I519" s="5" t="n"/>
+      <c r="J519" s="6" t="n"/>
+      <c r="K519" s="6" t="n"/>
+      <c r="L519" s="6" t="n"/>
+      <c r="M519" s="5" t="n"/>
+      <c r="N519" s="5" t="n"/>
+      <c r="O519" s="5" t="n"/>
+      <c r="P519" s="5" t="n"/>
+      <c r="Q519" s="6" t="n"/>
+      <c r="R519" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S519" s="5" t="n"/>
+      <c r="T519" s="6" t="n"/>
+      <c r="U519" s="6" t="n"/>
+      <c r="V519" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W519" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
+        </is>
+      </c>
+      <c r="X519" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y519" s="5" t="n"/>
+      <c r="Z519" s="5" t="n"/>
+      <c r="AA519" s="5" t="n"/>
+      <c r="AB519" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
+        </is>
+      </c>
+      <c r="AC519" s="5" t="inlineStr">
+        <is>
+          <t>state_json_sold_by</t>
+        </is>
+      </c>
+      <c r="AD519" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/flipkart_sellers.xlsx
+++ b/output/flipkart_sellers.xlsx
@@ -544,8 +544,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD519"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AD453"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -571,7 +571,7 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="60" customWidth="1" min="28" max="28"/>
@@ -755,15 +755,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Electronics &gt; Audio &gt; Headphones &gt; Wireless Earbuds</t>
+          <t>Electronics &gt; Audio</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Purvi Sheth Non</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
+          <t>of boAt Lifestyle</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>8699608602</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>careers@imaginemarketingindia.com</t>
@@ -821,7 +825,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Electronics &gt; Audio &gt; Headphones &gt; Wireless Earbuds</t>
+          <t>Electronics &gt; Audio</t>
         </is>
       </c>
       <c r="Y2" s="2" t="n"/>
@@ -839,7 +843,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>public_search, company_website</t>
+          <t>targeted_search, company_website</t>
         </is>
       </c>
     </row>
@@ -956,7 +960,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GaneshaEnterpriseStore</t>
+          <t>Ganeshaenterprisestore</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -977,7 +981,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Casual Shoes</t>
+          <t>Sneakers</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -997,23 +1001,17 @@
         </is>
       </c>
       <c r="S4" s="2" t="n"/>
-      <c r="T4" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/echor-esmgod-white-gym-shoes-men-sneakers/p/itma21e408aa03a9?pid=SHOHMQP7BFFB5TWM</t>
+          <t>https://www.flipkart.com/echor-esgrpep-sneakers-men/p/itme9e8167e57aac?pid=SHOHHD2FNBTZ77BG</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>Casual Shoes</t>
+          <t>Sneakers</t>
         </is>
       </c>
       <c r="Y4" s="2" t="n"/>
@@ -1021,12 +1019,12 @@
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/echor-esmgod-white-gym-shoes-men-sneakers/p/itma21e408aa03a9?pid=SHOHMQP7BFFB5TWM</t>
+          <t>https://www.flipkart.com/echor-esgrpep-sneakers-men/p/itme9e8167e57aac?pid=SHOHHD2FNBTZ77BG</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>state_json_sold_by</t>
+          <t>flipkart_product</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1806,7 +1804,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BellmiSports</t>
+          <t>Bellmisports</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -1827,7 +1825,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Slippers &amp; Flip Flops</t>
+          <t>Thong Sandals</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -1847,15 +1845,9 @@
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
       <c r="W14" s="2" t="inlineStr">
         <is>
           <t>https://www.flipkart.com/bellmi-men-slippers/p/itme5f2678d4d69f?pid=SFFHZFXJCHZMPYDR</t>
@@ -1863,7 +1855,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>Slippers &amp; Flip Flops</t>
+          <t>Thong Sandals</t>
         </is>
       </c>
       <c r="Y14" s="2" t="n"/>
@@ -1876,7 +1868,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>state_json_sold_by</t>
+          <t>flipkart_product</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -9888,34 +9880,26 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>Shoetopi</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>SHOETOPI</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>SHOETOPI</t>
-        </is>
-      </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>ENRICHMENT_PENDING</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="3" t="n"/>
       <c r="I124" s="2" t="n"/>
@@ -9927,53 +9911,33 @@
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="n"/>
       <c r="Q124" s="3" t="n"/>
-      <c r="R124" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="R124" s="2" t="n"/>
       <c r="S124" s="2" t="n"/>
-      <c r="T124" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U124" s="3" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="T124" s="3" t="n"/>
+      <c r="U124" s="3" t="n"/>
       <c r="V124" s="3" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/shoetopia-girls-slip-jutis/p/itmac537c1c54c18?pid=KSSHB3ZYM9RMMGSR</t>
+          <t>https://www.flipkart.com/shoetopia-jutis-women/p/itmc82116a3b3ae5?pid=SHOHZEJVSW3FZHA8</t>
         </is>
       </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="Y124" s="2" t="inlineStr">
-        <is>
-          <t>Ethnic Shoes</t>
-        </is>
-      </c>
+          <t>Women's Ethnic Shoes</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="n"/>
       <c r="Z124" s="2" t="n"/>
       <c r="AA124" s="2" t="n"/>
-      <c r="AB124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/shoetopia-girls-slip-jutis/p/itmac537c1c54c18?pid=KSSHB3ZYM9RMMGSR</t>
-        </is>
-      </c>
+      <c r="AB124" s="2" t="n"/>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD124" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD124" s="2" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -38897,5370 +38861,6 @@
         </is>
       </c>
     </row>
-    <row r="454" ht="22" customHeight="1">
-      <c r="A454" s="2" t="inlineStr">
-        <is>
-          <t>Pranaambharatse</t>
-        </is>
-      </c>
-      <c r="B454" s="2" t="n"/>
-      <c r="C454" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D454" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F454" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G454" s="2" t="n"/>
-      <c r="H454" s="3" t="n"/>
-      <c r="I454" s="2" t="n"/>
-      <c r="J454" s="3" t="n"/>
-      <c r="K454" s="3" t="n"/>
-      <c r="L454" s="3" t="n"/>
-      <c r="M454" s="2" t="n"/>
-      <c r="N454" s="2" t="n"/>
-      <c r="O454" s="2" t="n"/>
-      <c r="P454" s="2" t="n"/>
-      <c r="Q454" s="3" t="n"/>
-      <c r="R454" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S454" s="2" t="n"/>
-      <c r="T454" s="3" t="n"/>
-      <c r="U454" s="3" t="n"/>
-      <c r="V454" s="3" t="n"/>
-      <c r="W454" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/feetpanda-men-clogs/p/itm7f52d21eea7b3?pid=SNDHZGY55JH4C9TP</t>
-        </is>
-      </c>
-      <c r="X454" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y454" s="2" t="n"/>
-      <c r="Z454" s="2" t="n"/>
-      <c r="AA454" s="2" t="n"/>
-      <c r="AB454" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/feetpanda-men-clogs/p/itm7f52d21eea7b3?pid=SNDHZGY55JH4C9TP</t>
-        </is>
-      </c>
-      <c r="AC454" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD454" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="1">
-      <c r="A455" s="5" t="inlineStr">
-        <is>
-          <t>BRUTONFOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B455" s="5" t="n"/>
-      <c r="C455" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D455" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E455" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F455" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G455" s="5" t="n"/>
-      <c r="H455" s="6" t="n"/>
-      <c r="I455" s="5" t="n"/>
-      <c r="J455" s="6" t="n"/>
-      <c r="K455" s="6" t="n"/>
-      <c r="L455" s="6" t="n"/>
-      <c r="M455" s="5" t="n"/>
-      <c r="N455" s="5" t="n"/>
-      <c r="O455" s="5" t="n"/>
-      <c r="P455" s="5" t="n"/>
-      <c r="Q455" s="6" t="n"/>
-      <c r="R455" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S455" s="5" t="n"/>
-      <c r="T455" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U455" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V455" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W455" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bruton-men-clogs/p/itm3c608372ba71e?pid=SNDH4C5UCHU76VFZ</t>
-        </is>
-      </c>
-      <c r="X455" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y455" s="5" t="n"/>
-      <c r="Z455" s="5" t="n"/>
-      <c r="AA455" s="5" t="n"/>
-      <c r="AB455" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bruton-men-clogs/p/itm3c608372ba71e?pid=SNDH4C5UCHU76VFZ</t>
-        </is>
-      </c>
-      <c r="AC455" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD455" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="1">
-      <c r="A456" s="2" t="inlineStr">
-        <is>
-          <t>SparxBrandStore</t>
-        </is>
-      </c>
-      <c r="B456" s="2" t="n"/>
-      <c r="C456" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D456" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E456" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F456" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G456" s="2" t="n"/>
-      <c r="H456" s="3" t="n"/>
-      <c r="I456" s="2" t="n"/>
-      <c r="J456" s="3" t="n"/>
-      <c r="K456" s="3" t="n"/>
-      <c r="L456" s="3" t="n"/>
-      <c r="M456" s="2" t="n"/>
-      <c r="N456" s="2" t="n"/>
-      <c r="O456" s="2" t="n"/>
-      <c r="P456" s="2" t="n"/>
-      <c r="Q456" s="3" t="n"/>
-      <c r="R456" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S456" s="2" t="n"/>
-      <c r="T456" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U456" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V456" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W456" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/sparx-men-clogs/p/itm5262a4c148652?pid=SNDHN842GCWHPE6J</t>
-        </is>
-      </c>
-      <c r="X456" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y456" s="2" t="n"/>
-      <c r="Z456" s="2" t="n"/>
-      <c r="AA456" s="2" t="n"/>
-      <c r="AB456" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/sparx-men-clogs/p/itm5262a4c148652?pid=SNDHN842GCWHPE6J</t>
-        </is>
-      </c>
-      <c r="AC456" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD456" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="457" ht="22" customHeight="1">
-      <c r="A457" s="5" t="inlineStr">
-        <is>
-          <t>NithyaFootwearPrivateLimited</t>
-        </is>
-      </c>
-      <c r="B457" s="5" t="n"/>
-      <c r="C457" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D457" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E457" s="5" t="inlineStr">
-        <is>
-          <t>Public Limited Company</t>
-        </is>
-      </c>
-      <c r="F457" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G457" s="5" t="n"/>
-      <c r="H457" s="6" t="n"/>
-      <c r="I457" s="5" t="n"/>
-      <c r="J457" s="6" t="n"/>
-      <c r="K457" s="6" t="n"/>
-      <c r="L457" s="6" t="n"/>
-      <c r="M457" s="5" t="n"/>
-      <c r="N457" s="5" t="n"/>
-      <c r="O457" s="5" t="n"/>
-      <c r="P457" s="5" t="n"/>
-      <c r="Q457" s="6" t="n"/>
-      <c r="R457" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S457" s="5" t="n"/>
-      <c r="T457" s="6" t="n"/>
-      <c r="U457" s="6" t="n"/>
-      <c r="V457" s="6" t="n"/>
-      <c r="W457" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/adrenex-x-hoppa-men-clogs/p/itm5b2ceac681a06?pid=SNDHZQGJRF6EPQGK</t>
-        </is>
-      </c>
-      <c r="X457" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y457" s="5" t="n"/>
-      <c r="Z457" s="5" t="n"/>
-      <c r="AA457" s="5" t="n"/>
-      <c r="AB457" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/adrenex-x-hoppa-men-clogs/p/itm5b2ceac681a06?pid=SNDHZQGJRF6EPQGK</t>
-        </is>
-      </c>
-      <c r="AC457" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD457" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="458" ht="22" customHeight="1">
-      <c r="A458" s="2" t="inlineStr">
-        <is>
-          <t>Cherry09</t>
-        </is>
-      </c>
-      <c r="B458" s="2" t="n"/>
-      <c r="C458" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D458" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E458" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F458" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G458" s="2" t="n"/>
-      <c r="H458" s="3" t="n"/>
-      <c r="I458" s="2" t="n"/>
-      <c r="J458" s="3" t="n"/>
-      <c r="K458" s="3" t="n"/>
-      <c r="L458" s="3" t="n"/>
-      <c r="M458" s="2" t="n"/>
-      <c r="N458" s="2" t="n"/>
-      <c r="O458" s="2" t="n"/>
-      <c r="P458" s="2" t="n"/>
-      <c r="Q458" s="3" t="n"/>
-      <c r="R458" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S458" s="2" t="n"/>
-      <c r="T458" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U458" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V458" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W458" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/eastern-club-men-clogs/p/itmf8ffe13d76f69?pid=SNDHG82RTAVKKPZF</t>
-        </is>
-      </c>
-      <c r="X458" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y458" s="2" t="n"/>
-      <c r="Z458" s="2" t="n"/>
-      <c r="AA458" s="2" t="n"/>
-      <c r="AB458" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/eastern-club-men-clogs/p/itmf8ffe13d76f69?pid=SNDHG82RTAVKKPZF</t>
-        </is>
-      </c>
-      <c r="AC458" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD458" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="459" ht="22" customHeight="1">
-      <c r="A459" s="5" t="inlineStr">
-        <is>
-          <t>KridhayStore</t>
-        </is>
-      </c>
-      <c r="B459" s="5" t="n"/>
-      <c r="C459" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D459" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E459" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F459" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G459" s="5" t="n"/>
-      <c r="H459" s="6" t="n"/>
-      <c r="I459" s="5" t="n"/>
-      <c r="J459" s="6" t="n"/>
-      <c r="K459" s="6" t="n"/>
-      <c r="L459" s="6" t="n"/>
-      <c r="M459" s="5" t="n"/>
-      <c r="N459" s="5" t="n"/>
-      <c r="O459" s="5" t="n"/>
-      <c r="P459" s="5" t="n"/>
-      <c r="Q459" s="6" t="n"/>
-      <c r="R459" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S459" s="5" t="n"/>
-      <c r="T459" s="6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U459" s="6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V459" s="6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W459" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/killer-men-healthcare-clogs-ortho-support-slip-resistant-easy-clean-sandal/p/itm51db3cb99a676?pid=SNDHZHYMTJJMVD9V</t>
-        </is>
-      </c>
-      <c r="X459" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y459" s="5" t="n"/>
-      <c r="Z459" s="5" t="n"/>
-      <c r="AA459" s="5" t="n"/>
-      <c r="AB459" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/killer-men-healthcare-clogs-ortho-support-slip-resistant-easy-clean-sandal/p/itm51db3cb99a676?pid=SNDHZHYMTJJMVD9V</t>
-        </is>
-      </c>
-      <c r="AC459" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD459" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="460" ht="22" customHeight="1">
-      <c r="A460" s="2" t="inlineStr">
-        <is>
-          <t>Aarav enterprizes</t>
-        </is>
-      </c>
-      <c r="B460" s="2" t="n"/>
-      <c r="C460" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D460" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F460" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="n"/>
-      <c r="H460" s="3" t="n"/>
-      <c r="I460" s="2" t="n"/>
-      <c r="J460" s="3" t="n"/>
-      <c r="K460" s="3" t="n"/>
-      <c r="L460" s="3" t="n"/>
-      <c r="M460" s="2" t="n"/>
-      <c r="N460" s="2" t="n"/>
-      <c r="O460" s="2" t="n"/>
-      <c r="P460" s="2" t="n"/>
-      <c r="Q460" s="3" t="n"/>
-      <c r="R460" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S460" s="2" t="n"/>
-      <c r="T460" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U460" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V460" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W460" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/corsac-unisex-clogs/p/itmdaf27e125531d?pid=SNDHHTASZGHXEDYF</t>
-        </is>
-      </c>
-      <c r="X460" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y460" s="2" t="n"/>
-      <c r="Z460" s="2" t="n"/>
-      <c r="AA460" s="2" t="n"/>
-      <c r="AB460" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/corsac-unisex-clogs/p/itmdaf27e125531d?pid=SNDHHTASZGHXEDYF</t>
-        </is>
-      </c>
-      <c r="AC460" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD460" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="461" ht="22" customHeight="1">
-      <c r="A461" s="5" t="inlineStr">
-        <is>
-          <t>HikeStore</t>
-        </is>
-      </c>
-      <c r="B461" s="5" t="n"/>
-      <c r="C461" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D461" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E461" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F461" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G461" s="5" t="n"/>
-      <c r="H461" s="6" t="n"/>
-      <c r="I461" s="5" t="n"/>
-      <c r="J461" s="6" t="n"/>
-      <c r="K461" s="6" t="n"/>
-      <c r="L461" s="6" t="n"/>
-      <c r="M461" s="5" t="n"/>
-      <c r="N461" s="5" t="n"/>
-      <c r="O461" s="5" t="n"/>
-      <c r="P461" s="5" t="n"/>
-      <c r="Q461" s="6" t="n"/>
-      <c r="R461" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S461" s="5" t="n"/>
-      <c r="T461" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U461" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V461" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W461" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/svaar-men-clogs/p/itm0495b9de56657?pid=SNDGJQV5RH6XSBW6</t>
-        </is>
-      </c>
-      <c r="X461" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y461" s="5" t="n"/>
-      <c r="Z461" s="5" t="n"/>
-      <c r="AA461" s="5" t="n"/>
-      <c r="AB461" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/svaar-men-clogs/p/itm0495b9de56657?pid=SNDGJQV5RH6XSBW6</t>
-        </is>
-      </c>
-      <c r="AC461" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD461" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="1">
-      <c r="A462" s="2" t="inlineStr">
-        <is>
-          <t>Pirchlifestyle</t>
-        </is>
-      </c>
-      <c r="B462" s="2" t="n"/>
-      <c r="C462" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D462" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E462" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F462" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G462" s="2" t="n"/>
-      <c r="H462" s="3" t="n"/>
-      <c r="I462" s="2" t="n"/>
-      <c r="J462" s="3" t="n"/>
-      <c r="K462" s="3" t="n"/>
-      <c r="L462" s="3" t="n"/>
-      <c r="M462" s="2" t="n"/>
-      <c r="N462" s="2" t="n"/>
-      <c r="O462" s="2" t="n"/>
-      <c r="P462" s="2" t="n"/>
-      <c r="Q462" s="3" t="n"/>
-      <c r="R462" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S462" s="2" t="n"/>
-      <c r="T462" s="3" t="n"/>
-      <c r="U462" s="3" t="n"/>
-      <c r="V462" s="3" t="n"/>
-      <c r="W462" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pirch-men-clogs/p/itm3e169363f2089?pid=SNDHZ5PSP3BXMYUG</t>
-        </is>
-      </c>
-      <c r="X462" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y462" s="2" t="n"/>
-      <c r="Z462" s="2" t="n"/>
-      <c r="AA462" s="2" t="n"/>
-      <c r="AB462" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pirch-men-clogs/p/itm3e169363f2089?pid=SNDHZ5PSP3BXMYUG</t>
-        </is>
-      </c>
-      <c r="AC462" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD462" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="1">
-      <c r="A463" s="5" t="inlineStr">
-        <is>
-          <t>SOUKSHOE</t>
-        </is>
-      </c>
-      <c r="B463" s="5" t="n"/>
-      <c r="C463" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D463" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E463" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F463" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G463" s="5" t="n"/>
-      <c r="H463" s="6" t="n"/>
-      <c r="I463" s="5" t="n"/>
-      <c r="J463" s="6" t="n"/>
-      <c r="K463" s="6" t="n"/>
-      <c r="L463" s="6" t="n"/>
-      <c r="M463" s="5" t="n"/>
-      <c r="N463" s="5" t="n"/>
-      <c r="O463" s="5" t="n"/>
-      <c r="P463" s="5" t="n"/>
-      <c r="Q463" s="6" t="n"/>
-      <c r="R463" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S463" s="5" t="n"/>
-      <c r="T463" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U463" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V463" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W463" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/souk-men-clogs/p/itm4ab8257bc5a94?pid=SNDHHV5DPDXA6QB2</t>
-        </is>
-      </c>
-      <c r="X463" s="5" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y463" s="5" t="n"/>
-      <c r="Z463" s="5" t="n"/>
-      <c r="AA463" s="5" t="n"/>
-      <c r="AB463" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/souk-men-clogs/p/itm4ab8257bc5a94?pid=SNDHHV5DPDXA6QB2</t>
-        </is>
-      </c>
-      <c r="AC463" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD463" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="1">
-      <c r="A464" s="2" t="inlineStr">
-        <is>
-          <t>PerfactFeet</t>
-        </is>
-      </c>
-      <c r="B464" s="2" t="n"/>
-      <c r="C464" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D464" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E464" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F464" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="G464" s="2" t="n"/>
-      <c r="H464" s="3" t="n"/>
-      <c r="I464" s="2" t="n"/>
-      <c r="J464" s="3" t="n"/>
-      <c r="K464" s="3" t="n"/>
-      <c r="L464" s="3" t="n"/>
-      <c r="M464" s="2" t="n"/>
-      <c r="N464" s="2" t="n"/>
-      <c r="O464" s="2" t="n"/>
-      <c r="P464" s="2" t="n"/>
-      <c r="Q464" s="3" t="n"/>
-      <c r="R464" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S464" s="2" t="n"/>
-      <c r="T464" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U464" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V464" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W464" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/perfect-feet-men-sandals/p/itm08831933f96fb?pid=SNDHM47HGJZU4UHS</t>
-        </is>
-      </c>
-      <c r="X464" s="2" t="inlineStr">
-        <is>
-          <t>Clogs</t>
-        </is>
-      </c>
-      <c r="Y464" s="2" t="n"/>
-      <c r="Z464" s="2" t="n"/>
-      <c r="AA464" s="2" t="n"/>
-      <c r="AB464" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/perfect-feet-men-sandals/p/itm08831933f96fb?pid=SNDHM47HGJZU4UHS</t>
-        </is>
-      </c>
-      <c r="AC464" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD464" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="465" ht="22" customHeight="1">
-      <c r="A465" s="5" t="inlineStr">
-        <is>
-          <t>IRAJANDCOMPANY</t>
-        </is>
-      </c>
-      <c r="B465" s="5" t="n"/>
-      <c r="C465" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D465" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E465" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F465" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="G465" s="5" t="n"/>
-      <c r="H465" s="6" t="n"/>
-      <c r="I465" s="5" t="n"/>
-      <c r="J465" s="6" t="n"/>
-      <c r="K465" s="6" t="n"/>
-      <c r="L465" s="6" t="n"/>
-      <c r="M465" s="5" t="n"/>
-      <c r="N465" s="5" t="n"/>
-      <c r="O465" s="5" t="n"/>
-      <c r="P465" s="5" t="n"/>
-      <c r="Q465" s="6" t="n"/>
-      <c r="R465" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S465" s="5" t="n"/>
-      <c r="T465" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U465" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V465" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W465" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/kastava-premium-stylish-lightweight-slip-on-shoes-office-party-wear-loafers-men/p/itmb04c0e3015fa9?pid=SHOH7Z2DNSAHHCCV</t>
-        </is>
-      </c>
-      <c r="X465" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="Y465" s="5" t="n"/>
-      <c r="Z465" s="5" t="n"/>
-      <c r="AA465" s="5" t="n"/>
-      <c r="AB465" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/kastava-premium-stylish-lightweight-slip-on-shoes-office-party-wear-loafers-men/p/itmb04c0e3015fa9?pid=SHOH7Z2DNSAHHCCV</t>
-        </is>
-      </c>
-      <c r="AC465" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD465" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="466" ht="22" customHeight="1">
-      <c r="A466" s="2" t="inlineStr">
-        <is>
-          <t>Auvio</t>
-        </is>
-      </c>
-      <c r="B466" s="2" t="n"/>
-      <c r="C466" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D466" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F466" s="2" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="G466" s="2" t="n"/>
-      <c r="H466" s="3" t="n"/>
-      <c r="I466" s="2" t="n"/>
-      <c r="J466" s="3" t="n"/>
-      <c r="K466" s="3" t="n"/>
-      <c r="L466" s="3" t="n"/>
-      <c r="M466" s="2" t="n"/>
-      <c r="N466" s="2" t="n"/>
-      <c r="O466" s="2" t="n"/>
-      <c r="P466" s="2" t="n"/>
-      <c r="Q466" s="3" t="n"/>
-      <c r="R466" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S466" s="2" t="n"/>
-      <c r="T466" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U466" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V466" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W466" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/birde-premium-comfortable-regular-wear-shoes-men-casual-senakers-high-tops/p/itm774f050523a15?pid=SHOGZEQGDDM9GP8N</t>
-        </is>
-      </c>
-      <c r="X466" s="2" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="Y466" s="2" t="n"/>
-      <c r="Z466" s="2" t="n"/>
-      <c r="AA466" s="2" t="n"/>
-      <c r="AB466" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/birde-premium-comfortable-regular-wear-shoes-men-casual-senakers-high-tops/p/itm774f050523a15?pid=SHOGZEQGDDM9GP8N</t>
-        </is>
-      </c>
-      <c r="AC466" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD466" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="467" ht="22" customHeight="1">
-      <c r="A467" s="5" t="inlineStr">
-        <is>
-          <t>lejano</t>
-        </is>
-      </c>
-      <c r="B467" s="5" t="n"/>
-      <c r="C467" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D467" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E467" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F467" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="G467" s="5" t="n"/>
-      <c r="H467" s="6" t="n"/>
-      <c r="I467" s="5" t="n"/>
-      <c r="J467" s="6" t="n"/>
-      <c r="K467" s="6" t="n"/>
-      <c r="L467" s="6" t="n"/>
-      <c r="M467" s="5" t="n"/>
-      <c r="N467" s="5" t="n"/>
-      <c r="O467" s="5" t="n"/>
-      <c r="P467" s="5" t="n"/>
-      <c r="Q467" s="6" t="n"/>
-      <c r="R467" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S467" s="5" t="n"/>
-      <c r="T467" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U467" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V467" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W467" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/lejano-high-tops-men/p/itmc6f61b55d69a4?pid=SHOHF9RRFAHFY22M</t>
-        </is>
-      </c>
-      <c r="X467" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="Y467" s="5" t="n"/>
-      <c r="Z467" s="5" t="n"/>
-      <c r="AA467" s="5" t="n"/>
-      <c r="AB467" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/lejano-high-tops-men/p/itmc6f61b55d69a4?pid=SHOHF9RRFAHFY22M</t>
-        </is>
-      </c>
-      <c r="AC467" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD467" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="468" ht="22" customHeight="1">
-      <c r="A468" s="2" t="inlineStr">
-        <is>
-          <t>COOPERWINGSFOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B468" s="2" t="n"/>
-      <c r="C468" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D468" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E468" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F468" s="2" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="G468" s="2" t="n"/>
-      <c r="H468" s="3" t="n"/>
-      <c r="I468" s="2" t="n"/>
-      <c r="J468" s="3" t="n"/>
-      <c r="K468" s="3" t="n"/>
-      <c r="L468" s="3" t="n"/>
-      <c r="M468" s="2" t="n"/>
-      <c r="N468" s="2" t="n"/>
-      <c r="O468" s="2" t="n"/>
-      <c r="P468" s="2" t="n"/>
-      <c r="Q468" s="3" t="n"/>
-      <c r="R468" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S468" s="2" t="n"/>
-      <c r="T468" s="3" t="n"/>
-      <c r="U468" s="3" t="n"/>
-      <c r="V468" s="3" t="n"/>
-      <c r="W468" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/cooperwings-running-shoes-men/p/itm74b6d0ca0af1d?pid=SHOHPGCTJJRT3M8F</t>
-        </is>
-      </c>
-      <c r="X468" s="2" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="Y468" s="2" t="n"/>
-      <c r="Z468" s="2" t="n"/>
-      <c r="AA468" s="2" t="n"/>
-      <c r="AB468" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/cooperwings-running-shoes-men/p/itm74b6d0ca0af1d?pid=SHOHPGCTJJRT3M8F</t>
-        </is>
-      </c>
-      <c r="AC468" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD468" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="469" ht="22" customHeight="1">
-      <c r="A469" s="5" t="inlineStr">
-        <is>
-          <t>ULIKEFASHION</t>
-        </is>
-      </c>
-      <c r="B469" s="5" t="n"/>
-      <c r="C469" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D469" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E469" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F469" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="G469" s="5" t="n"/>
-      <c r="H469" s="6" t="n"/>
-      <c r="I469" s="5" t="n"/>
-      <c r="J469" s="6" t="n"/>
-      <c r="K469" s="6" t="n"/>
-      <c r="L469" s="6" t="n"/>
-      <c r="M469" s="5" t="n"/>
-      <c r="N469" s="5" t="n"/>
-      <c r="O469" s="5" t="n"/>
-      <c r="P469" s="5" t="n"/>
-      <c r="Q469" s="6" t="n"/>
-      <c r="R469" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S469" s="5" t="n"/>
-      <c r="T469" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U469" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V469" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W469" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/zorza-mens-running-shoes-cushioned-comfort-sole-outdoors-men/p/itmc34a2522571bb?pid=SHOHZGSC2EAHYGMC</t>
-        </is>
-      </c>
-      <c r="X469" s="5" t="inlineStr">
-        <is>
-          <t>Casual Shoes</t>
-        </is>
-      </c>
-      <c r="Y469" s="5" t="n"/>
-      <c r="Z469" s="5" t="n"/>
-      <c r="AA469" s="5" t="n"/>
-      <c r="AB469" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/zorza-mens-running-shoes-cushioned-comfort-sole-outdoors-men/p/itmc34a2522571bb?pid=SHOHZGSC2EAHYGMC</t>
-        </is>
-      </c>
-      <c r="AC469" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD469" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="470" ht="22" customHeight="1">
-      <c r="A470" s="2" t="inlineStr">
-        <is>
-          <t>SmTrands</t>
-        </is>
-      </c>
-      <c r="B470" s="2" t="n"/>
-      <c r="C470" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D470" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F470" s="2" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="G470" s="2" t="n"/>
-      <c r="H470" s="3" t="n"/>
-      <c r="I470" s="2" t="n"/>
-      <c r="J470" s="3" t="n"/>
-      <c r="K470" s="3" t="n"/>
-      <c r="L470" s="3" t="n"/>
-      <c r="M470" s="2" t="n"/>
-      <c r="N470" s="2" t="n"/>
-      <c r="O470" s="2" t="n"/>
-      <c r="P470" s="2" t="n"/>
-      <c r="Q470" s="3" t="n"/>
-      <c r="R470" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S470" s="2" t="n"/>
-      <c r="T470" s="3" t="n"/>
-      <c r="U470" s="3" t="n"/>
-      <c r="V470" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W470" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/stride-up-new-design-lightweight-stylish-trendy-walking-shoes-men-sneakers/p/itm6a9e942057b32?pid=SHOHNWRGFCYZWFRH</t>
-        </is>
-      </c>
-      <c r="X470" s="2" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="Y470" s="2" t="n"/>
-      <c r="Z470" s="2" t="n"/>
-      <c r="AA470" s="2" t="n"/>
-      <c r="AB470" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/stride-up-new-design-lightweight-stylish-trendy-walking-shoes-men-sneakers/p/itm6a9e942057b32?pid=SHOHNWRGFCYZWFRH</t>
-        </is>
-      </c>
-      <c r="AC470" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD470" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="471" ht="22" customHeight="1">
-      <c r="A471" s="5" t="inlineStr">
-        <is>
-          <t>NobeliteFootwear</t>
-        </is>
-      </c>
-      <c r="B471" s="5" t="n"/>
-      <c r="C471" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D471" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E471" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F471" s="5" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="G471" s="5" t="n"/>
-      <c r="H471" s="6" t="n"/>
-      <c r="I471" s="5" t="n"/>
-      <c r="J471" s="6" t="n"/>
-      <c r="K471" s="6" t="n"/>
-      <c r="L471" s="6" t="n"/>
-      <c r="M471" s="5" t="n"/>
-      <c r="N471" s="5" t="n"/>
-      <c r="O471" s="5" t="n"/>
-      <c r="P471" s="5" t="n"/>
-      <c r="Q471" s="6" t="n"/>
-      <c r="R471" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S471" s="5" t="n"/>
-      <c r="T471" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U471" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V471" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W471" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/nobelite-premium-sports-gym-trending-stylish-running-shoes-men/p/itm97ef97f943d6c?pid=SHOH8PFQCTANHETW</t>
-        </is>
-      </c>
-      <c r="X471" s="5" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="Y471" s="5" t="n"/>
-      <c r="Z471" s="5" t="n"/>
-      <c r="AA471" s="5" t="n"/>
-      <c r="AB471" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/nobelite-premium-sports-gym-trending-stylish-running-shoes-men/p/itm97ef97f943d6c?pid=SHOH8PFQCTANHETW</t>
-        </is>
-      </c>
-      <c r="AC471" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD471" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="472" ht="22" customHeight="1">
-      <c r="A472" s="2" t="inlineStr">
-        <is>
-          <t>TAJFOOTWEARFACTORY</t>
-        </is>
-      </c>
-      <c r="B472" s="2" t="n"/>
-      <c r="C472" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D472" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E472" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F472" s="2" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="G472" s="2" t="n"/>
-      <c r="H472" s="3" t="n"/>
-      <c r="I472" s="2" t="n"/>
-      <c r="J472" s="3" t="n"/>
-      <c r="K472" s="3" t="n"/>
-      <c r="L472" s="3" t="n"/>
-      <c r="M472" s="2" t="n"/>
-      <c r="N472" s="2" t="n"/>
-      <c r="O472" s="2" t="n"/>
-      <c r="P472" s="2" t="n"/>
-      <c r="Q472" s="3" t="n"/>
-      <c r="R472" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S472" s="2" t="n"/>
-      <c r="T472" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U472" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V472" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W472" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/taj-tajj-boot-07-102-boots-men/p/itm8f09751b12552?pid=SHOHHJ5K7GBTXVTK</t>
-        </is>
-      </c>
-      <c r="X472" s="2" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="Y472" s="2" t="n"/>
-      <c r="Z472" s="2" t="n"/>
-      <c r="AA472" s="2" t="n"/>
-      <c r="AB472" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/taj-tajj-boot-07-102-boots-men/p/itm8f09751b12552?pid=SHOHHJ5K7GBTXVTK</t>
-        </is>
-      </c>
-      <c r="AC472" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD472" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="473" ht="22" customHeight="1">
-      <c r="A473" s="5" t="inlineStr">
-        <is>
-          <t>LeosFitnesshoes</t>
-        </is>
-      </c>
-      <c r="B473" s="5" t="n"/>
-      <c r="C473" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D473" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E473" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F473" s="5" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="G473" s="5" t="n"/>
-      <c r="H473" s="6" t="n"/>
-      <c r="I473" s="5" t="n"/>
-      <c r="J473" s="6" t="n"/>
-      <c r="K473" s="6" t="n"/>
-      <c r="L473" s="6" t="n"/>
-      <c r="M473" s="5" t="n"/>
-      <c r="N473" s="5" t="n"/>
-      <c r="O473" s="5" t="n"/>
-      <c r="P473" s="5" t="n"/>
-      <c r="Q473" s="6" t="n"/>
-      <c r="R473" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S473" s="5" t="n"/>
-      <c r="T473" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U473" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V473" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W473" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/leo-shoes-hiking-trekking-men/p/itmad8e9bdfa0907?pid=SHOG5F82AJJTBKKE</t>
-        </is>
-      </c>
-      <c r="X473" s="5" t="inlineStr">
-        <is>
-          <t>Sports Shoes</t>
-        </is>
-      </c>
-      <c r="Y473" s="5" t="n"/>
-      <c r="Z473" s="5" t="n"/>
-      <c r="AA473" s="5" t="n"/>
-      <c r="AB473" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/leo-shoes-hiking-trekking-men/p/itmad8e9bdfa0907?pid=SHOG5F82AJJTBKKE</t>
-        </is>
-      </c>
-      <c r="AC473" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD473" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="474" ht="22" customHeight="1">
-      <c r="A474" s="2" t="inlineStr">
-        <is>
-          <t>Vokline</t>
-        </is>
-      </c>
-      <c r="B474" s="2" t="n"/>
-      <c r="C474" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D474" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E474" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F474" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G474" s="2" t="n"/>
-      <c r="H474" s="3" t="n"/>
-      <c r="I474" s="2" t="n"/>
-      <c r="J474" s="3" t="n"/>
-      <c r="K474" s="3" t="n"/>
-      <c r="L474" s="3" t="n"/>
-      <c r="M474" s="2" t="n"/>
-      <c r="N474" s="2" t="n"/>
-      <c r="O474" s="2" t="n"/>
-      <c r="P474" s="2" t="n"/>
-      <c r="Q474" s="3" t="n"/>
-      <c r="R474" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S474" s="2" t="n"/>
-      <c r="T474" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U474" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V474" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W474" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/evok-men-mens-comfortable-trending-stylish-multicolor-embozing-flipflop-pack-2-slippers/p/itmf2648afbb603d?pid=SFFGEWKCRMA4XTMW</t>
-        </is>
-      </c>
-      <c r="X474" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y474" s="2" t="n"/>
-      <c r="Z474" s="2" t="n"/>
-      <c r="AA474" s="2" t="n"/>
-      <c r="AB474" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/evok-men-mens-comfortable-trending-stylish-multicolor-embozing-flipflop-pack-2-slippers/p/itmf2648afbb603d?pid=SFFGEWKCRMA4XTMW</t>
-        </is>
-      </c>
-      <c r="AC474" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD474" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="475" ht="22" customHeight="1">
-      <c r="A475" s="5" t="inlineStr">
-        <is>
-          <t>FOOTUPFOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B475" s="5" t="n"/>
-      <c r="C475" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D475" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E475" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F475" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G475" s="5" t="n"/>
-      <c r="H475" s="6" t="n"/>
-      <c r="I475" s="5" t="n"/>
-      <c r="J475" s="6" t="n"/>
-      <c r="K475" s="6" t="n"/>
-      <c r="L475" s="6" t="n"/>
-      <c r="M475" s="5" t="n"/>
-      <c r="N475" s="5" t="n"/>
-      <c r="O475" s="5" t="n"/>
-      <c r="P475" s="5" t="n"/>
-      <c r="Q475" s="6" t="n"/>
-      <c r="R475" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S475" s="5" t="n"/>
-      <c r="T475" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U475" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V475" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W475" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/footup-men-super-soft-orthopedic-comfortable-lightweight-diabetic-combo-slippers/p/itm32f605e32145d?pid=SFFHGV5F6UAZNAMF</t>
-        </is>
-      </c>
-      <c r="X475" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y475" s="5" t="n"/>
-      <c r="Z475" s="5" t="n"/>
-      <c r="AA475" s="5" t="n"/>
-      <c r="AB475" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/footup-men-super-soft-orthopedic-comfortable-lightweight-diabetic-combo-slippers/p/itm32f605e32145d?pid=SFFHGV5F6UAZNAMF</t>
-        </is>
-      </c>
-      <c r="AC475" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD475" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="1">
-      <c r="A476" s="2" t="inlineStr">
-        <is>
-          <t>FOOTPRO</t>
-        </is>
-      </c>
-      <c r="B476" s="2" t="n"/>
-      <c r="C476" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D476" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E476" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F476" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G476" s="2" t="n"/>
-      <c r="H476" s="3" t="n"/>
-      <c r="I476" s="2" t="n"/>
-      <c r="J476" s="3" t="n"/>
-      <c r="K476" s="3" t="n"/>
-      <c r="L476" s="3" t="n"/>
-      <c r="M476" s="2" t="n"/>
-      <c r="N476" s="2" t="n"/>
-      <c r="O476" s="2" t="n"/>
-      <c r="P476" s="2" t="n"/>
-      <c r="Q476" s="3" t="n"/>
-      <c r="R476" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S476" s="2" t="n"/>
-      <c r="T476" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U476" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V476" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W476" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/ribaxon-men-flip-flops/p/itm6c9e860de5c1b?pid=SFFHNKDC2EYMHCG5</t>
-        </is>
-      </c>
-      <c r="X476" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y476" s="2" t="n"/>
-      <c r="Z476" s="2" t="n"/>
-      <c r="AA476" s="2" t="n"/>
-      <c r="AB476" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/ribaxon-men-flip-flops/p/itm6c9e860de5c1b?pid=SFFHNKDC2EYMHCG5</t>
-        </is>
-      </c>
-      <c r="AC476" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD476" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="1">
-      <c r="A477" s="5" t="inlineStr">
-        <is>
-          <t>SUPER</t>
-        </is>
-      </c>
-      <c r="B477" s="5" t="n"/>
-      <c r="C477" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D477" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E477" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F477" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G477" s="5" t="n"/>
-      <c r="H477" s="6" t="n"/>
-      <c r="I477" s="5" t="n"/>
-      <c r="J477" s="6" t="n"/>
-      <c r="K477" s="6" t="n"/>
-      <c r="L477" s="6" t="n"/>
-      <c r="M477" s="5" t="n"/>
-      <c r="N477" s="5" t="n"/>
-      <c r="O477" s="5" t="n"/>
-      <c r="P477" s="5" t="n"/>
-      <c r="Q477" s="6" t="n"/>
-      <c r="R477" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S477" s="5" t="n"/>
-      <c r="T477" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U477" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V477" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W477" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bersache-men-slippers/p/itm9299d4d566795?pid=SFFHEZPSYGHRNZSV</t>
-        </is>
-      </c>
-      <c r="X477" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y477" s="5" t="n"/>
-      <c r="Z477" s="5" t="n"/>
-      <c r="AA477" s="5" t="n"/>
-      <c r="AB477" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bersache-men-slippers/p/itm9299d4d566795?pid=SFFHEZPSYGHRNZSV</t>
-        </is>
-      </c>
-      <c r="AC477" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD477" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="1">
-      <c r="A478" s="2" t="inlineStr">
-        <is>
-          <t>Alteksleeper</t>
-        </is>
-      </c>
-      <c r="B478" s="2" t="n"/>
-      <c r="C478" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D478" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E478" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F478" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G478" s="2" t="n"/>
-      <c r="H478" s="3" t="n"/>
-      <c r="I478" s="2" t="n"/>
-      <c r="J478" s="3" t="n"/>
-      <c r="K478" s="3" t="n"/>
-      <c r="L478" s="3" t="n"/>
-      <c r="M478" s="2" t="n"/>
-      <c r="N478" s="2" t="n"/>
-      <c r="O478" s="2" t="n"/>
-      <c r="P478" s="2" t="n"/>
-      <c r="Q478" s="3" t="n"/>
-      <c r="R478" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S478" s="2" t="n"/>
-      <c r="T478" s="3" t="n"/>
-      <c r="U478" s="3" t="n"/>
-      <c r="V478" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W478" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/altek-men-slippers/p/itmf1da538a66648?pid=SFFHG8CHFAURUCSV</t>
-        </is>
-      </c>
-      <c r="X478" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y478" s="2" t="n"/>
-      <c r="Z478" s="2" t="n"/>
-      <c r="AA478" s="2" t="n"/>
-      <c r="AB478" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/altek-men-slippers/p/itmf1da538a66648?pid=SFFHG8CHFAURUCSV</t>
-        </is>
-      </c>
-      <c r="AC478" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD478" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="479" ht="22" customHeight="1">
-      <c r="A479" s="5" t="inlineStr">
-        <is>
-          <t>ArcatronMobility</t>
-        </is>
-      </c>
-      <c r="B479" s="5" t="n"/>
-      <c r="C479" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D479" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E479" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F479" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G479" s="5" t="n"/>
-      <c r="H479" s="6" t="n"/>
-      <c r="I479" s="5" t="n"/>
-      <c r="J479" s="6" t="n"/>
-      <c r="K479" s="6" t="n"/>
-      <c r="L479" s="6" t="n"/>
-      <c r="M479" s="5" t="n"/>
-      <c r="N479" s="5" t="n"/>
-      <c r="O479" s="5" t="n"/>
-      <c r="P479" s="5" t="n"/>
-      <c r="Q479" s="6" t="n"/>
-      <c r="R479" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S479" s="5" t="n"/>
-      <c r="T479" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U479" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V479" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W479" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/frido-unisex-cloud-comfort-arch-support-orthopedic-soft-home-chappal-anti-skid-sole-slippers/p/itm9230f3ef7facc?pid=SFFHMHSHK2SJ4XNX</t>
-        </is>
-      </c>
-      <c r="X479" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y479" s="5" t="n"/>
-      <c r="Z479" s="5" t="n"/>
-      <c r="AA479" s="5" t="n"/>
-      <c r="AB479" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/frido-unisex-cloud-comfort-arch-support-orthopedic-soft-home-chappal-anti-skid-sole-slippers/p/itm9230f3ef7facc?pid=SFFHMHSHK2SJ4XNX</t>
-        </is>
-      </c>
-      <c r="AC479" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD479" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="1">
-      <c r="A480" s="2" t="inlineStr">
-        <is>
-          <t>Acupressure</t>
-        </is>
-      </c>
-      <c r="B480" s="2" t="n"/>
-      <c r="C480" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D480" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
-        </is>
-      </c>
-      <c r="E480" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F480" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G480" s="2" t="n"/>
-      <c r="H480" s="3" t="n"/>
-      <c r="I480" s="2" t="inlineStr">
-        <is>
-          <t>health@favr.town</t>
-        </is>
-      </c>
-      <c r="J480" s="3" t="n"/>
-      <c r="K480" s="3" t="n"/>
-      <c r="L480" s="3" t="n"/>
-      <c r="M480" s="2" t="n"/>
-      <c r="N480" s="2" t="n"/>
-      <c r="O480" s="2" t="n"/>
-      <c r="P480" s="2" t="n"/>
-      <c r="Q480" s="3" t="n"/>
-      <c r="R480" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S480" s="2" t="inlineStr">
-        <is>
-          <t>https://acupressure.guide</t>
-        </is>
-      </c>
-      <c r="T480" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U480" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V480" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W480" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/unistar-men-acupressure-flip-flops-natural-leg-foot-massager-slippers-men-s-women-s/p/itm48e724fd75511?pid=SFFEYQPYEGGBD9MK</t>
-        </is>
-      </c>
-      <c r="X480" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y480" s="2" t="n"/>
-      <c r="Z480" s="2" t="n"/>
-      <c r="AA480" s="2" t="n"/>
-      <c r="AB480" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/unistar-men-acupressure-flip-flops-natural-leg-foot-massager-slippers-men-s-women-s/p/itm48e724fd75511?pid=SFFEYQPYEGGBD9MK</t>
-        </is>
-      </c>
-      <c r="AC480" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD480" s="2" t="inlineStr">
-        <is>
-          <t>company_website</t>
-        </is>
-      </c>
-    </row>
-    <row r="481" ht="22" customHeight="1">
-      <c r="A481" s="5" t="inlineStr">
-        <is>
-          <t>LittlePalz</t>
-        </is>
-      </c>
-      <c r="B481" s="5" t="n"/>
-      <c r="C481" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D481" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E481" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F481" s="5" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="G481" s="5" t="n"/>
-      <c r="H481" s="6" t="n"/>
-      <c r="I481" s="5" t="n"/>
-      <c r="J481" s="6" t="n"/>
-      <c r="K481" s="6" t="n"/>
-      <c r="L481" s="6" t="n"/>
-      <c r="M481" s="5" t="n"/>
-      <c r="N481" s="5" t="n"/>
-      <c r="O481" s="5" t="n"/>
-      <c r="P481" s="5" t="n"/>
-      <c r="Q481" s="6" t="n"/>
-      <c r="R481" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S481" s="5" t="n"/>
-      <c r="T481" s="6" t="n"/>
-      <c r="U481" s="6" t="n"/>
-      <c r="V481" s="6" t="n"/>
-      <c r="W481" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/little-palz-girls-slip-mojaris/p/itm3a974d5816103?pid=KSSHZYJHYRN5BSTH</t>
-        </is>
-      </c>
-      <c r="X481" s="5" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="Y481" s="5" t="inlineStr">
-        <is>
-          <t>Ethnic Shoes</t>
-        </is>
-      </c>
-      <c r="Z481" s="5" t="n"/>
-      <c r="AA481" s="5" t="n"/>
-      <c r="AB481" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/little-palz-girls-slip-mojaris/p/itm3a974d5816103?pid=KSSHZYJHYRN5BSTH</t>
-        </is>
-      </c>
-      <c r="AC481" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD481" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="482" ht="22" customHeight="1">
-      <c r="A482" s="2" t="inlineStr">
-        <is>
-          <t>Mukundu</t>
-        </is>
-      </c>
-      <c r="B482" s="2" t="n"/>
-      <c r="C482" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D482" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E482" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F482" s="2" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="G482" s="2" t="n"/>
-      <c r="H482" s="3" t="n"/>
-      <c r="I482" s="2" t="n"/>
-      <c r="J482" s="3" t="n"/>
-      <c r="K482" s="3" t="n"/>
-      <c r="L482" s="3" t="n"/>
-      <c r="M482" s="2" t="n"/>
-      <c r="N482" s="2" t="n"/>
-      <c r="O482" s="2" t="n"/>
-      <c r="P482" s="2" t="n"/>
-      <c r="Q482" s="3" t="n"/>
-      <c r="R482" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S482" s="2" t="n"/>
-      <c r="T482" s="3" t="n"/>
-      <c r="U482" s="3" t="n"/>
-      <c r="V482" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W482" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/mukunda-footwear-girls-slip-jutis/p/itm38090e61e8e26?pid=KSSH3FTFE3UMKV7P</t>
-        </is>
-      </c>
-      <c r="X482" s="2" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="Y482" s="2" t="inlineStr">
-        <is>
-          <t>Ethnic Shoes</t>
-        </is>
-      </c>
-      <c r="Z482" s="2" t="n"/>
-      <c r="AA482" s="2" t="n"/>
-      <c r="AB482" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/mukunda-footwear-girls-slip-jutis/p/itm38090e61e8e26?pid=KSSH3FTFE3UMKV7P</t>
-        </is>
-      </c>
-      <c r="AC482" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD482" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="483" ht="22" customHeight="1">
-      <c r="A483" s="5" t="inlineStr">
-        <is>
-          <t>MBGINDUSTRIES</t>
-        </is>
-      </c>
-      <c r="B483" s="5" t="n"/>
-      <c r="C483" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D483" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E483" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F483" s="5" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="G483" s="5" t="n"/>
-      <c r="H483" s="6" t="n"/>
-      <c r="I483" s="5" t="n"/>
-      <c r="J483" s="6" t="n"/>
-      <c r="K483" s="6" t="n"/>
-      <c r="L483" s="6" t="n"/>
-      <c r="M483" s="5" t="n"/>
-      <c r="N483" s="5" t="n"/>
-      <c r="O483" s="5" t="n"/>
-      <c r="P483" s="5" t="n"/>
-      <c r="Q483" s="6" t="n"/>
-      <c r="R483" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S483" s="5" t="n"/>
-      <c r="T483" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U483" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V483" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W483" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/hitway-girls-slip-mojaris/p/itme070c805611d9?pid=KSSGZSSRZGGQGZ3Y</t>
-        </is>
-      </c>
-      <c r="X483" s="5" t="inlineStr">
-        <is>
-          <t>Girls' Footwear</t>
-        </is>
-      </c>
-      <c r="Y483" s="5" t="inlineStr">
-        <is>
-          <t>Ethnic Shoes</t>
-        </is>
-      </c>
-      <c r="Z483" s="5" t="n"/>
-      <c r="AA483" s="5" t="n"/>
-      <c r="AB483" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/hitway-girls-slip-mojaris/p/itme070c805611d9?pid=KSSGZSSRZGGQGZ3Y</t>
-        </is>
-      </c>
-      <c r="AC483" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD483" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="484" ht="22" customHeight="1">
-      <c r="A484" s="2" t="inlineStr">
-        <is>
-          <t>ParagonFootwear</t>
-        </is>
-      </c>
-      <c r="B484" s="2" t="n"/>
-      <c r="C484" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D484" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F484" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G484" s="2" t="n"/>
-      <c r="H484" s="3" t="n"/>
-      <c r="I484" s="2" t="n"/>
-      <c r="J484" s="3" t="n"/>
-      <c r="K484" s="3" t="n"/>
-      <c r="L484" s="3" t="n"/>
-      <c r="M484" s="2" t="n"/>
-      <c r="N484" s="2" t="n"/>
-      <c r="O484" s="2" t="n"/>
-      <c r="P484" s="2" t="n"/>
-      <c r="Q484" s="3" t="n"/>
-      <c r="R484" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S484" s="2" t="n"/>
-      <c r="T484" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U484" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V484" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W484" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/paragon-men-slippers/p/itmd06e71eba374a?pid=SFFHP64QNZUST5GH</t>
-        </is>
-      </c>
-      <c r="X484" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y484" s="2" t="n"/>
-      <c r="Z484" s="2" t="n"/>
-      <c r="AA484" s="2" t="n"/>
-      <c r="AB484" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/paragon-men-slippers/p/itmd06e71eba374a?pid=SFFHP64QNZUST5GH</t>
-        </is>
-      </c>
-      <c r="AC484" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD484" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="485" ht="22" customHeight="1">
-      <c r="A485" s="5" t="inlineStr">
-        <is>
-          <t>CIBEK</t>
-        </is>
-      </c>
-      <c r="B485" s="5" t="n"/>
-      <c r="C485" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D485" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E485" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F485" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G485" s="5" t="n"/>
-      <c r="H485" s="6" t="n"/>
-      <c r="I485" s="5" t="n"/>
-      <c r="J485" s="6" t="n"/>
-      <c r="K485" s="6" t="n"/>
-      <c r="L485" s="6" t="n"/>
-      <c r="M485" s="5" t="n"/>
-      <c r="N485" s="5" t="n"/>
-      <c r="O485" s="5" t="n"/>
-      <c r="P485" s="5" t="n"/>
-      <c r="Q485" s="6" t="n"/>
-      <c r="R485" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S485" s="5" t="n"/>
-      <c r="T485" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U485" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V485" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W485" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/cibek-women-slippers/p/itm0fb183e601776?pid=SFFHNTE4AKM7SHGQ</t>
-        </is>
-      </c>
-      <c r="X485" s="5" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y485" s="5" t="n"/>
-      <c r="Z485" s="5" t="n"/>
-      <c r="AA485" s="5" t="n"/>
-      <c r="AB485" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/cibek-women-slippers/p/itm0fb183e601776?pid=SFFHNTE4AKM7SHGQ</t>
-        </is>
-      </c>
-      <c r="AC485" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD485" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="486" ht="22" customHeight="1">
-      <c r="A486" s="2" t="inlineStr">
-        <is>
-          <t>DivisaStore</t>
-        </is>
-      </c>
-      <c r="B486" s="2" t="n"/>
-      <c r="C486" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D486" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E486" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F486" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="G486" s="2" t="n"/>
-      <c r="H486" s="3" t="n"/>
-      <c r="I486" s="2" t="n"/>
-      <c r="J486" s="3" t="n"/>
-      <c r="K486" s="3" t="n"/>
-      <c r="L486" s="3" t="n"/>
-      <c r="M486" s="2" t="n"/>
-      <c r="N486" s="2" t="n"/>
-      <c r="O486" s="2" t="n"/>
-      <c r="P486" s="2" t="n"/>
-      <c r="Q486" s="3" t="n"/>
-      <c r="R486" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S486" s="2" t="n"/>
-      <c r="T486" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U486" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V486" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W486" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/dr-ortho-men-accupressure-slippers/p/itmd2ca0a027f5d4?pid=SFFH9MB7UMYMH7RA</t>
-        </is>
-      </c>
-      <c r="X486" s="2" t="inlineStr">
-        <is>
-          <t>Slippers &amp; Flip Flops</t>
-        </is>
-      </c>
-      <c r="Y486" s="2" t="n"/>
-      <c r="Z486" s="2" t="n"/>
-      <c r="AA486" s="2" t="n"/>
-      <c r="AB486" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/dr-ortho-men-accupressure-slippers/p/itmd2ca0a027f5d4?pid=SFFH9MB7UMYMH7RA</t>
-        </is>
-      </c>
-      <c r="AC486" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD486" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="487" ht="22" customHeight="1">
-      <c r="A487" s="5" t="inlineStr">
-        <is>
-          <t>Puresole</t>
-        </is>
-      </c>
-      <c r="B487" s="5" t="n"/>
-      <c r="C487" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D487" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E487" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F487" s="5" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="G487" s="5" t="n"/>
-      <c r="H487" s="6" t="n"/>
-      <c r="I487" s="5" t="n"/>
-      <c r="J487" s="6" t="n"/>
-      <c r="K487" s="6" t="n"/>
-      <c r="L487" s="6" t="n"/>
-      <c r="M487" s="5" t="n"/>
-      <c r="N487" s="5" t="n"/>
-      <c r="O487" s="5" t="n"/>
-      <c r="P487" s="5" t="n"/>
-      <c r="Q487" s="6" t="n"/>
-      <c r="R487" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S487" s="5" t="n"/>
-      <c r="T487" s="6" t="n"/>
-      <c r="U487" s="6" t="n"/>
-      <c r="V487" s="6" t="n"/>
-      <c r="W487" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/puresole-booties/p/itm0947cc086ee38?pid=BOOHJTYPSHYSZV5E</t>
-        </is>
-      </c>
-      <c r="X487" s="5" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="Y487" s="5" t="inlineStr">
-        <is>
-          <t>Baby Boys Footwear</t>
-        </is>
-      </c>
-      <c r="Z487" s="5" t="n"/>
-      <c r="AA487" s="5" t="n"/>
-      <c r="AB487" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/puresole-booties/p/itm0947cc086ee38?pid=BOOHJTYPSHYSZV5E</t>
-        </is>
-      </c>
-      <c r="AC487" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD487" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="488" ht="22" customHeight="1">
-      <c r="A488" s="2" t="inlineStr">
-        <is>
-          <t>RIDHI CREATION</t>
-        </is>
-      </c>
-      <c r="B488" s="2" t="n"/>
-      <c r="C488" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D488" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E488" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F488" s="2" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="G488" s="2" t="n"/>
-      <c r="H488" s="3" t="n"/>
-      <c r="I488" s="2" t="n"/>
-      <c r="J488" s="3" t="n"/>
-      <c r="K488" s="3" t="n"/>
-      <c r="L488" s="3" t="n"/>
-      <c r="M488" s="2" t="n"/>
-      <c r="N488" s="2" t="n"/>
-      <c r="O488" s="2" t="n"/>
-      <c r="P488" s="2" t="n"/>
-      <c r="Q488" s="3" t="n"/>
-      <c r="R488" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S488" s="2" t="n"/>
-      <c r="T488" s="3" t="n"/>
-      <c r="U488" s="3" t="n"/>
-      <c r="V488" s="3" t="n"/>
-      <c r="W488" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bullcraft-infant-soft-sole-booties-adorable-baby/p/itmea4b00576acbf?pid=BOOHPANVDHZQUY6Y</t>
-        </is>
-      </c>
-      <c r="X488" s="2" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="Y488" s="2" t="inlineStr">
-        <is>
-          <t>Baby Boys Footwear</t>
-        </is>
-      </c>
-      <c r="Z488" s="2" t="n"/>
-      <c r="AA488" s="2" t="n"/>
-      <c r="AB488" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bullcraft-infant-soft-sole-booties-adorable-baby/p/itmea4b00576acbf?pid=BOOHPANVDHZQUY6Y</t>
-        </is>
-      </c>
-      <c r="AC488" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD488" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="489" ht="22" customHeight="1">
-      <c r="A489" s="5" t="inlineStr">
-        <is>
-          <t>VBaby</t>
-        </is>
-      </c>
-      <c r="B489" s="5" t="n"/>
-      <c r="C489" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D489" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E489" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F489" s="5" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="G489" s="5" t="n"/>
-      <c r="H489" s="6" t="n"/>
-      <c r="I489" s="5" t="n"/>
-      <c r="J489" s="6" t="n"/>
-      <c r="K489" s="6" t="n"/>
-      <c r="L489" s="6" t="n"/>
-      <c r="M489" s="5" t="n"/>
-      <c r="N489" s="5" t="n"/>
-      <c r="O489" s="5" t="n"/>
-      <c r="P489" s="5" t="n"/>
-      <c r="Q489" s="6" t="n"/>
-      <c r="R489" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S489" s="5" t="n"/>
-      <c r="T489" s="6" t="n"/>
-      <c r="U489" s="6" t="n"/>
-      <c r="V489" s="6" t="n"/>
-      <c r="W489" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/vbaby-soft-step-dog-baby-shoes-winter-girl-boy-booties/p/itm2fe1db018220f?pid=BOOHJYCTZH3FAMWR</t>
-        </is>
-      </c>
-      <c r="X489" s="5" t="inlineStr">
-        <is>
-          <t>Infant Footwear</t>
-        </is>
-      </c>
-      <c r="Y489" s="5" t="inlineStr">
-        <is>
-          <t>Baby Boys Footwear</t>
-        </is>
-      </c>
-      <c r="Z489" s="5" t="n"/>
-      <c r="AA489" s="5" t="n"/>
-      <c r="AB489" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/vbaby-soft-step-dog-baby-shoes-winter-girl-boy-booties/p/itm2fe1db018220f?pid=BOOHJYCTZH3FAMWR</t>
-        </is>
-      </c>
-      <c r="AC489" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD489" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="490" ht="22" customHeight="1">
-      <c r="A490" s="2" t="inlineStr">
-        <is>
-          <t>GOVINDEINTERPRISES</t>
-        </is>
-      </c>
-      <c r="B490" s="2" t="n"/>
-      <c r="C490" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D490" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F490" s="2" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="G490" s="2" t="n"/>
-      <c r="H490" s="3" t="n"/>
-      <c r="I490" s="2" t="n"/>
-      <c r="J490" s="3" t="n"/>
-      <c r="K490" s="3" t="n"/>
-      <c r="L490" s="3" t="n"/>
-      <c r="M490" s="2" t="n"/>
-      <c r="N490" s="2" t="n"/>
-      <c r="O490" s="2" t="n"/>
-      <c r="P490" s="2" t="n"/>
-      <c r="Q490" s="3" t="n"/>
-      <c r="R490" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S490" s="2" t="n"/>
-      <c r="T490" s="3" t="n"/>
-      <c r="U490" s="3" t="n"/>
-      <c r="V490" s="3" t="n"/>
-      <c r="W490" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/govind-booties/p/itm0a8cc11684c90?pid=BOOGNXJ6VHUZP6QM</t>
-        </is>
-      </c>
-      <c r="X490" s="2" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="Y490" s="2" t="n"/>
-      <c r="Z490" s="2" t="n"/>
-      <c r="AA490" s="2" t="n"/>
-      <c r="AB490" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/govind-booties/p/itm0a8cc11684c90?pid=BOOGNXJ6VHUZP6QM</t>
-        </is>
-      </c>
-      <c r="AC490" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD490" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="491" ht="22" customHeight="1">
-      <c r="A491" s="5" t="inlineStr">
-        <is>
-          <t>Trecify</t>
-        </is>
-      </c>
-      <c r="B491" s="5" t="n"/>
-      <c r="C491" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D491" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E491" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F491" s="5" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="G491" s="5" t="n"/>
-      <c r="H491" s="6" t="n"/>
-      <c r="I491" s="5" t="n"/>
-      <c r="J491" s="6" t="n"/>
-      <c r="K491" s="6" t="n"/>
-      <c r="L491" s="6" t="n"/>
-      <c r="M491" s="5" t="n"/>
-      <c r="N491" s="5" t="n"/>
-      <c r="O491" s="5" t="n"/>
-      <c r="P491" s="5" t="n"/>
-      <c r="Q491" s="6" t="n"/>
-      <c r="R491" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S491" s="5" t="n"/>
-      <c r="T491" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U491" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V491" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W491" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/trecify-booties/p/itm8eadce960d5d9?pid=BOOHJJEZPNNX66GM</t>
-        </is>
-      </c>
-      <c r="X491" s="5" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="Y491" s="5" t="n"/>
-      <c r="Z491" s="5" t="n"/>
-      <c r="AA491" s="5" t="n"/>
-      <c r="AB491" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/trecify-booties/p/itm8eadce960d5d9?pid=BOOHJJEZPNNX66GM</t>
-        </is>
-      </c>
-      <c r="AC491" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD491" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="492" ht="22" customHeight="1">
-      <c r="A492" s="2" t="inlineStr">
-        <is>
-          <t>KRISHNAM2025</t>
-        </is>
-      </c>
-      <c r="B492" s="2" t="n"/>
-      <c r="C492" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D492" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E492" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F492" s="2" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="G492" s="2" t="n"/>
-      <c r="H492" s="3" t="n"/>
-      <c r="I492" s="2" t="n"/>
-      <c r="J492" s="3" t="n"/>
-      <c r="K492" s="3" t="n"/>
-      <c r="L492" s="3" t="n"/>
-      <c r="M492" s="2" t="n"/>
-      <c r="N492" s="2" t="n"/>
-      <c r="O492" s="2" t="n"/>
-      <c r="P492" s="2" t="n"/>
-      <c r="Q492" s="3" t="n"/>
-      <c r="R492" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S492" s="2" t="n"/>
-      <c r="T492" s="3" t="n"/>
-      <c r="U492" s="3" t="n"/>
-      <c r="V492" s="3" t="n"/>
-      <c r="W492" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/angaakar-001-booties/p/itm893e7545787f4?pid=BOOHJNCDAAJS3X2V</t>
-        </is>
-      </c>
-      <c r="X492" s="2" t="inlineStr">
-        <is>
-          <t>Booties</t>
-        </is>
-      </c>
-      <c r="Y492" s="2" t="n"/>
-      <c r="Z492" s="2" t="n"/>
-      <c r="AA492" s="2" t="n"/>
-      <c r="AB492" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/angaakar-001-booties/p/itm893e7545787f4?pid=BOOHJNCDAAJS3X2V</t>
-        </is>
-      </c>
-      <c r="AC492" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD492" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="493" ht="22" customHeight="1">
-      <c r="A493" s="5" t="inlineStr">
-        <is>
-          <t>PrabhuEnterprises1</t>
-        </is>
-      </c>
-      <c r="B493" s="5" t="n"/>
-      <c r="C493" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D493" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E493" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F493" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G493" s="5" t="n"/>
-      <c r="H493" s="6" t="n"/>
-      <c r="I493" s="5" t="n"/>
-      <c r="J493" s="6" t="n"/>
-      <c r="K493" s="6" t="n"/>
-      <c r="L493" s="6" t="n"/>
-      <c r="M493" s="5" t="n"/>
-      <c r="N493" s="5" t="n"/>
-      <c r="O493" s="5" t="n"/>
-      <c r="P493" s="5" t="n"/>
-      <c r="Q493" s="6" t="n"/>
-      <c r="R493" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S493" s="5" t="n"/>
-      <c r="T493" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U493" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V493" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W493" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/inivaene-regular-men-black-jeans/p/itm6dbc688bd6cd7?pid=JEAHD8FHVVZYY6QY</t>
-        </is>
-      </c>
-      <c r="X493" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y493" s="5" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z493" s="5" t="n"/>
-      <c r="AA493" s="5" t="n"/>
-      <c r="AB493" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/inivaene-regular-men-black-jeans/p/itm6dbc688bd6cd7?pid=JEAHD8FHVVZYY6QY</t>
-        </is>
-      </c>
-      <c r="AC493" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD493" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="494" ht="22" customHeight="1">
-      <c r="A494" s="2" t="inlineStr">
-        <is>
-          <t>4FLIES</t>
-        </is>
-      </c>
-      <c r="B494" s="2" t="n"/>
-      <c r="C494" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D494" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F494" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="n"/>
-      <c r="H494" s="3" t="n"/>
-      <c r="I494" s="2" t="n"/>
-      <c r="J494" s="3" t="n"/>
-      <c r="K494" s="3" t="n"/>
-      <c r="L494" s="3" t="n"/>
-      <c r="M494" s="2" t="n"/>
-      <c r="N494" s="2" t="n"/>
-      <c r="O494" s="2" t="n"/>
-      <c r="P494" s="2" t="n"/>
-      <c r="Q494" s="3" t="n"/>
-      <c r="R494" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S494" s="2" t="n"/>
-      <c r="T494" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U494" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V494" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W494" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/3butterflies-skinny-women-black-jeans/p/itmea250cf972f91?pid=JEAHE29ZMMYFQGPZ</t>
-        </is>
-      </c>
-      <c r="X494" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y494" s="2" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z494" s="2" t="n"/>
-      <c r="AA494" s="2" t="n"/>
-      <c r="AB494" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/3butterflies-skinny-women-black-jeans/p/itmea250cf972f91?pid=JEAHE29ZMMYFQGPZ</t>
-        </is>
-      </c>
-      <c r="AC494" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD494" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="495" ht="22" customHeight="1">
-      <c r="A495" s="5" t="inlineStr">
-        <is>
-          <t>SBTSTORE</t>
-        </is>
-      </c>
-      <c r="B495" s="5" t="n"/>
-      <c r="C495" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D495" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E495" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F495" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G495" s="5" t="n"/>
-      <c r="H495" s="6" t="n"/>
-      <c r="I495" s="5" t="n"/>
-      <c r="J495" s="6" t="n"/>
-      <c r="K495" s="6" t="n"/>
-      <c r="L495" s="6" t="n"/>
-      <c r="M495" s="5" t="n"/>
-      <c r="N495" s="5" t="n"/>
-      <c r="O495" s="5" t="n"/>
-      <c r="P495" s="5" t="n"/>
-      <c r="Q495" s="6" t="n"/>
-      <c r="R495" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S495" s="5" t="n"/>
-      <c r="T495" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U495" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V495" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W495" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/tyffyn-wide-leg-women-blue-jeans/p/itm8f63f4958145d?pid=JEAHNHR2JWWNU3JW</t>
-        </is>
-      </c>
-      <c r="X495" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y495" s="5" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z495" s="5" t="n"/>
-      <c r="AA495" s="5" t="n"/>
-      <c r="AB495" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/tyffyn-wide-leg-women-blue-jeans/p/itm8f63f4958145d?pid=JEAHNHR2JWWNU3JW</t>
-        </is>
-      </c>
-      <c r="AC495" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD495" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="496" ht="22" customHeight="1">
-      <c r="A496" s="2" t="inlineStr">
-        <is>
-          <t>MARUTISTORE</t>
-        </is>
-      </c>
-      <c r="B496" s="2" t="n"/>
-      <c r="C496" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D496" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F496" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G496" s="2" t="n"/>
-      <c r="H496" s="3" t="n"/>
-      <c r="I496" s="2" t="n"/>
-      <c r="J496" s="3" t="n"/>
-      <c r="K496" s="3" t="n"/>
-      <c r="L496" s="3" t="n"/>
-      <c r="M496" s="2" t="n"/>
-      <c r="N496" s="2" t="n"/>
-      <c r="O496" s="2" t="n"/>
-      <c r="P496" s="2" t="n"/>
-      <c r="Q496" s="3" t="n"/>
-      <c r="R496" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S496" s="2" t="n"/>
-      <c r="T496" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U496" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V496" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W496" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/moudlin-regular-men-light-blue-jeans/p/itm6008d8782af65?pid=JEAHFCTGMBZEYGGY</t>
-        </is>
-      </c>
-      <c r="X496" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y496" s="2" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z496" s="2" t="n"/>
-      <c r="AA496" s="2" t="n"/>
-      <c r="AB496" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/moudlin-regular-men-light-blue-jeans/p/itm6008d8782af65?pid=JEAHFCTGMBZEYGGY</t>
-        </is>
-      </c>
-      <c r="AC496" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD496" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="497" ht="22" customHeight="1">
-      <c r="A497" s="5" t="inlineStr">
-        <is>
-          <t>ZARISTAAA</t>
-        </is>
-      </c>
-      <c r="B497" s="5" t="n"/>
-      <c r="C497" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D497" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E497" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F497" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G497" s="5" t="n"/>
-      <c r="H497" s="6" t="n"/>
-      <c r="I497" s="5" t="n"/>
-      <c r="J497" s="6" t="n"/>
-      <c r="K497" s="6" t="n"/>
-      <c r="L497" s="6" t="n"/>
-      <c r="M497" s="5" t="n"/>
-      <c r="N497" s="5" t="n"/>
-      <c r="O497" s="5" t="n"/>
-      <c r="P497" s="5" t="n"/>
-      <c r="Q497" s="6" t="n"/>
-      <c r="R497" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S497" s="5" t="n"/>
-      <c r="T497" s="6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U497" s="6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V497" s="6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W497" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/zaristaa-flared-women-light-blue-jeans/p/itm1d3d11b18b4f5?pid=JEAHNWS7VHAVUZFS</t>
-        </is>
-      </c>
-      <c r="X497" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y497" s="5" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z497" s="5" t="n"/>
-      <c r="AA497" s="5" t="n"/>
-      <c r="AB497" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/zaristaa-flared-women-light-blue-jeans/p/itm1d3d11b18b4f5?pid=JEAHNWS7VHAVUZFS</t>
-        </is>
-      </c>
-      <c r="AC497" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD497" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="498" ht="22" customHeight="1">
-      <c r="A498" s="2" t="inlineStr">
-        <is>
-          <t>3butterflies</t>
-        </is>
-      </c>
-      <c r="B498" s="2" t="n"/>
-      <c r="C498" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D498" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E498" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F498" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G498" s="2" t="n"/>
-      <c r="H498" s="3" t="n"/>
-      <c r="I498" s="2" t="n"/>
-      <c r="J498" s="3" t="n"/>
-      <c r="K498" s="3" t="n"/>
-      <c r="L498" s="3" t="n"/>
-      <c r="M498" s="2" t="n"/>
-      <c r="N498" s="2" t="n"/>
-      <c r="O498" s="2" t="n"/>
-      <c r="P498" s="2" t="n"/>
-      <c r="Q498" s="3" t="n"/>
-      <c r="R498" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S498" s="2" t="n"/>
-      <c r="T498" s="3" t="n"/>
-      <c r="U498" s="3" t="n"/>
-      <c r="V498" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W498" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/3butterflies-flared-women-dark-blue-jeans/p/itmf9de44f542c6f?pid=JEAHMAZVZ5APFHRD</t>
-        </is>
-      </c>
-      <c r="X498" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y498" s="2" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z498" s="2" t="n"/>
-      <c r="AA498" s="2" t="n"/>
-      <c r="AB498" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/3butterflies-flared-women-dark-blue-jeans/p/itmf9de44f542c6f?pid=JEAHMAZVZ5APFHRD</t>
-        </is>
-      </c>
-      <c r="AC498" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD498" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="499" ht="22" customHeight="1">
-      <c r="A499" s="5" t="inlineStr">
-        <is>
-          <t>MRFASHION</t>
-        </is>
-      </c>
-      <c r="B499" s="5" t="n"/>
-      <c r="C499" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D499" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E499" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F499" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G499" s="5" t="n"/>
-      <c r="H499" s="6" t="n"/>
-      <c r="I499" s="5" t="n"/>
-      <c r="J499" s="6" t="n"/>
-      <c r="K499" s="6" t="n"/>
-      <c r="L499" s="6" t="n"/>
-      <c r="M499" s="5" t="n"/>
-      <c r="N499" s="5" t="n"/>
-      <c r="O499" s="5" t="n"/>
-      <c r="P499" s="5" t="n"/>
-      <c r="Q499" s="6" t="n"/>
-      <c r="R499" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S499" s="5" t="n"/>
-      <c r="T499" s="6" t="n"/>
-      <c r="U499" s="6" t="n"/>
-      <c r="V499" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W499" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/wearo-jeans-regular-men-black/p/itme0706cc7a068f?pid=JEAHC4B7GSYHZA9H</t>
-        </is>
-      </c>
-      <c r="X499" s="5" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y499" s="5" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z499" s="5" t="n"/>
-      <c r="AA499" s="5" t="n"/>
-      <c r="AB499" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/wearo-jeans-regular-men-black/p/itme0706cc7a068f?pid=JEAHC4B7GSYHZA9H</t>
-        </is>
-      </c>
-      <c r="AC499" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD499" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="500" ht="22" customHeight="1">
-      <c r="A500" s="2" t="inlineStr">
-        <is>
-          <t>KARANFASHIONHUB</t>
-        </is>
-      </c>
-      <c r="B500" s="2" t="n"/>
-      <c r="C500" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D500" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E500" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F500" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="G500" s="2" t="n"/>
-      <c r="H500" s="3" t="n"/>
-      <c r="I500" s="2" t="n"/>
-      <c r="J500" s="3" t="n"/>
-      <c r="K500" s="3" t="n"/>
-      <c r="L500" s="3" t="n"/>
-      <c r="M500" s="2" t="n"/>
-      <c r="N500" s="2" t="n"/>
-      <c r="O500" s="2" t="n"/>
-      <c r="P500" s="2" t="n"/>
-      <c r="Q500" s="3" t="n"/>
-      <c r="R500" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S500" s="2" t="n"/>
-      <c r="T500" s="3" t="n"/>
-      <c r="U500" s="3" t="n"/>
-      <c r="V500" s="3" t="n"/>
-      <c r="W500" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/metronaut-wide-leg-women-light-blue-jeans/p/itm7703ee2ae732d?pid=JEAHPF9V89BUFH27</t>
-        </is>
-      </c>
-      <c r="X500" s="2" t="inlineStr">
-        <is>
-          <t>Bottom Wear</t>
-        </is>
-      </c>
-      <c r="Y500" s="2" t="inlineStr">
-        <is>
-          <t>Jeans</t>
-        </is>
-      </c>
-      <c r="Z500" s="2" t="n"/>
-      <c r="AA500" s="2" t="n"/>
-      <c r="AB500" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/metronaut-wide-leg-women-light-blue-jeans/p/itm7703ee2ae732d?pid=JEAHPF9V89BUFH27</t>
-        </is>
-      </c>
-      <c r="AC500" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD500" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="501" ht="22" customHeight="1">
-      <c r="A501" s="5" t="inlineStr">
-        <is>
-          <t>Pesado</t>
-        </is>
-      </c>
-      <c r="B501" s="5" t="n"/>
-      <c r="C501" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D501" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E501" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F501" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G501" s="5" t="n"/>
-      <c r="H501" s="6" t="n"/>
-      <c r="I501" s="5" t="n"/>
-      <c r="J501" s="6" t="n"/>
-      <c r="K501" s="6" t="n"/>
-      <c r="L501" s="6" t="n"/>
-      <c r="M501" s="5" t="n"/>
-      <c r="N501" s="5" t="n"/>
-      <c r="O501" s="5" t="n"/>
-      <c r="P501" s="5" t="n"/>
-      <c r="Q501" s="6" t="n"/>
-      <c r="R501" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S501" s="5" t="n"/>
-      <c r="T501" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U501" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V501" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W501" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pesado-slim-fit-men-green-trousers/p/itm19e9c1b481b56?pid=TROGMKA9T6GWAMFF</t>
-        </is>
-      </c>
-      <c r="X501" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y501" s="5" t="n"/>
-      <c r="Z501" s="5" t="n"/>
-      <c r="AA501" s="5" t="n"/>
-      <c r="AB501" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pesado-slim-fit-men-green-trousers/p/itm19e9c1b481b56?pid=TROGMKA9T6GWAMFF</t>
-        </is>
-      </c>
-      <c r="AC501" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD501" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="502" ht="22" customHeight="1">
-      <c r="A502" s="2" t="inlineStr">
-        <is>
-          <t>AKAYAAPPARELS</t>
-        </is>
-      </c>
-      <c r="B502" s="2" t="n"/>
-      <c r="C502" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D502" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F502" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G502" s="2" t="n"/>
-      <c r="H502" s="3" t="n"/>
-      <c r="I502" s="2" t="n"/>
-      <c r="J502" s="3" t="n"/>
-      <c r="K502" s="3" t="n"/>
-      <c r="L502" s="3" t="n"/>
-      <c r="M502" s="2" t="n"/>
-      <c r="N502" s="2" t="n"/>
-      <c r="O502" s="2" t="n"/>
-      <c r="P502" s="2" t="n"/>
-      <c r="Q502" s="3" t="n"/>
-      <c r="R502" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S502" s="2" t="n"/>
-      <c r="T502" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U502" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V502" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W502" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itme0c404571a277?pid=TROHZGH5AHHZQHNK</t>
-        </is>
-      </c>
-      <c r="X502" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y502" s="2" t="n"/>
-      <c r="Z502" s="2" t="n"/>
-      <c r="AA502" s="2" t="n"/>
-      <c r="AB502" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itme0c404571a277?pid=TROHZGH5AHHZQHNK</t>
-        </is>
-      </c>
-      <c r="AC502" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD502" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="503" ht="22" customHeight="1">
-      <c r="A503" s="5" t="inlineStr">
-        <is>
-          <t>OSWAL NETWORK PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B503" s="5" t="n"/>
-      <c r="C503" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D503" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E503" s="5" t="inlineStr">
-        <is>
-          <t>Private Limited Company</t>
-        </is>
-      </c>
-      <c r="F503" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G503" s="5" t="n"/>
-      <c r="H503" s="6" t="n"/>
-      <c r="I503" s="5" t="n"/>
-      <c r="J503" s="6" t="n"/>
-      <c r="K503" s="6" t="n"/>
-      <c r="L503" s="6" t="n"/>
-      <c r="M503" s="5" t="n"/>
-      <c r="N503" s="5" t="n"/>
-      <c r="O503" s="5" t="n"/>
-      <c r="P503" s="5" t="n"/>
-      <c r="Q503" s="6" t="n"/>
-      <c r="R503" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S503" s="5" t="n"/>
-      <c r="T503" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U503" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V503" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W503" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/ad-av-regular-fit-men-black-trousers/p/itmfgpmyczzn5hyz?pid=TROFGPJWAHPHH97B</t>
-        </is>
-      </c>
-      <c r="X503" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y503" s="5" t="n"/>
-      <c r="Z503" s="5" t="n"/>
-      <c r="AA503" s="5" t="n"/>
-      <c r="AB503" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/ad-av-regular-fit-men-black-trousers/p/itmfgpmyczzn5hyz?pid=TROFGPJWAHPHH97B</t>
-        </is>
-      </c>
-      <c r="AC503" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD503" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="504" ht="22" customHeight="1">
-      <c r="A504" s="2" t="inlineStr">
-        <is>
-          <t>ManakStore</t>
-        </is>
-      </c>
-      <c r="B504" s="2" t="n"/>
-      <c r="C504" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D504" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F504" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G504" s="2" t="n"/>
-      <c r="H504" s="3" t="n"/>
-      <c r="I504" s="2" t="n"/>
-      <c r="J504" s="3" t="n"/>
-      <c r="K504" s="3" t="n"/>
-      <c r="L504" s="3" t="n"/>
-      <c r="M504" s="2" t="n"/>
-      <c r="N504" s="2" t="n"/>
-      <c r="O504" s="2" t="n"/>
-      <c r="P504" s="2" t="n"/>
-      <c r="Q504" s="3" t="n"/>
-      <c r="R504" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S504" s="2" t="n"/>
-      <c r="T504" s="3" t="n"/>
-      <c r="U504" s="3" t="n"/>
-      <c r="V504" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W504" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-cream-trousers/p/itm8b337c68d0e34?pid=TROHZGH9JJY4YSWH</t>
-        </is>
-      </c>
-      <c r="X504" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y504" s="2" t="n"/>
-      <c r="Z504" s="2" t="n"/>
-      <c r="AA504" s="2" t="n"/>
-      <c r="AB504" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-cream-trousers/p/itm8b337c68d0e34?pid=TROHZGH9JJY4YSWH</t>
-        </is>
-      </c>
-      <c r="AC504" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD504" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="505" ht="22" customHeight="1">
-      <c r="A505" s="5" t="inlineStr">
-        <is>
-          <t>GralinHollie</t>
-        </is>
-      </c>
-      <c r="B505" s="5" t="n"/>
-      <c r="C505" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D505" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E505" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F505" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G505" s="5" t="n"/>
-      <c r="H505" s="6" t="n"/>
-      <c r="I505" s="5" t="n"/>
-      <c r="J505" s="6" t="n"/>
-      <c r="K505" s="6" t="n"/>
-      <c r="L505" s="6" t="n"/>
-      <c r="M505" s="5" t="n"/>
-      <c r="N505" s="5" t="n"/>
-      <c r="O505" s="5" t="n"/>
-      <c r="P505" s="5" t="n"/>
-      <c r="Q505" s="6" t="n"/>
-      <c r="R505" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S505" s="5" t="n"/>
-      <c r="T505" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U505" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V505" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W505" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/gralin-hollie-slim-fit-men-black-trousers/p/itm590295fd43789?pid=TROHHAEBZE8SAZWT</t>
-        </is>
-      </c>
-      <c r="X505" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y505" s="5" t="n"/>
-      <c r="Z505" s="5" t="n"/>
-      <c r="AA505" s="5" t="n"/>
-      <c r="AB505" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/gralin-hollie-slim-fit-men-black-trousers/p/itm590295fd43789?pid=TROHHAEBZE8SAZWT</t>
-        </is>
-      </c>
-      <c r="AC505" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD505" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="506" ht="22" customHeight="1">
-      <c r="A506" s="2" t="inlineStr">
-        <is>
-          <t>MarcNTailor</t>
-        </is>
-      </c>
-      <c r="B506" s="2" t="n"/>
-      <c r="C506" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D506" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E506" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F506" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G506" s="2" t="n"/>
-      <c r="H506" s="3" t="n"/>
-      <c r="I506" s="2" t="n"/>
-      <c r="J506" s="3" t="n"/>
-      <c r="K506" s="3" t="n"/>
-      <c r="L506" s="3" t="n"/>
-      <c r="M506" s="2" t="n"/>
-      <c r="N506" s="2" t="n"/>
-      <c r="O506" s="2" t="n"/>
-      <c r="P506" s="2" t="n"/>
-      <c r="Q506" s="3" t="n"/>
-      <c r="R506" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S506" s="2" t="n"/>
-      <c r="T506" s="3" t="n"/>
-      <c r="U506" s="3" t="n"/>
-      <c r="V506" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W506" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/marcntailor-tapered-men-white-trousers/p/itmbc5d15bd3eb6a?pid=TROHAY4YXDHTTGNH</t>
-        </is>
-      </c>
-      <c r="X506" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y506" s="2" t="n"/>
-      <c r="Z506" s="2" t="n"/>
-      <c r="AA506" s="2" t="n"/>
-      <c r="AB506" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/marcntailor-tapered-men-white-trousers/p/itmbc5d15bd3eb6a?pid=TROHAY4YXDHTTGNH</t>
-        </is>
-      </c>
-      <c r="AC506" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD506" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="507" ht="22" customHeight="1">
-      <c r="A507" s="5" t="inlineStr">
-        <is>
-          <t>KATELACREATION</t>
-        </is>
-      </c>
-      <c r="B507" s="5" t="n"/>
-      <c r="C507" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D507" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E507" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F507" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G507" s="5" t="n"/>
-      <c r="H507" s="6" t="n"/>
-      <c r="I507" s="5" t="n"/>
-      <c r="J507" s="6" t="n"/>
-      <c r="K507" s="6" t="n"/>
-      <c r="L507" s="6" t="n"/>
-      <c r="M507" s="5" t="n"/>
-      <c r="N507" s="5" t="n"/>
-      <c r="O507" s="5" t="n"/>
-      <c r="P507" s="5" t="n"/>
-      <c r="Q507" s="6" t="n"/>
-      <c r="R507" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S507" s="5" t="n"/>
-      <c r="T507" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U507" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V507" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W507" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/fubar-regular-fit-men-black-trousers/p/itmfac6bee203897?pid=TROH7X3AYBNFRXSF</t>
-        </is>
-      </c>
-      <c r="X507" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y507" s="5" t="n"/>
-      <c r="Z507" s="5" t="n"/>
-      <c r="AA507" s="5" t="n"/>
-      <c r="AB507" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/fubar-regular-fit-men-black-trousers/p/itmfac6bee203897?pid=TROH7X3AYBNFRXSF</t>
-        </is>
-      </c>
-      <c r="AC507" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD507" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="508" ht="22" customHeight="1">
-      <c r="A508" s="2" t="inlineStr">
-        <is>
-          <t>AUSTENSTITCHERY</t>
-        </is>
-      </c>
-      <c r="B508" s="2" t="n"/>
-      <c r="C508" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D508" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F508" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G508" s="2" t="n"/>
-      <c r="H508" s="3" t="n"/>
-      <c r="I508" s="2" t="n"/>
-      <c r="J508" s="3" t="n"/>
-      <c r="K508" s="3" t="n"/>
-      <c r="L508" s="3" t="n"/>
-      <c r="M508" s="2" t="n"/>
-      <c r="N508" s="2" t="n"/>
-      <c r="O508" s="2" t="n"/>
-      <c r="P508" s="2" t="n"/>
-      <c r="Q508" s="3" t="n"/>
-      <c r="R508" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S508" s="2" t="n"/>
-      <c r="T508" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U508" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V508" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W508" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itm6b1479a914291?pid=TROHZGH5S4XMFPTG</t>
-        </is>
-      </c>
-      <c r="X508" s="2" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y508" s="2" t="n"/>
-      <c r="Z508" s="2" t="n"/>
-      <c r="AA508" s="2" t="n"/>
-      <c r="AB508" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itm6b1479a914291?pid=TROHZGH5S4XMFPTG</t>
-        </is>
-      </c>
-      <c r="AC508" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD508" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="509" ht="22" customHeight="1">
-      <c r="A509" s="5" t="inlineStr">
-        <is>
-          <t>1stShreeJiEnterprises</t>
-        </is>
-      </c>
-      <c r="B509" s="5" t="n"/>
-      <c r="C509" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D509" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E509" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F509" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="G509" s="5" t="n"/>
-      <c r="H509" s="6" t="n"/>
-      <c r="I509" s="5" t="n"/>
-      <c r="J509" s="6" t="n"/>
-      <c r="K509" s="6" t="n"/>
-      <c r="L509" s="6" t="n"/>
-      <c r="M509" s="5" t="n"/>
-      <c r="N509" s="5" t="n"/>
-      <c r="O509" s="5" t="n"/>
-      <c r="P509" s="5" t="n"/>
-      <c r="Q509" s="6" t="n"/>
-      <c r="R509" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S509" s="5" t="n"/>
-      <c r="T509" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U509" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V509" s="6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W509" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itmd4419e16a70a1?pid=TROHZGH53TTYZMCU</t>
-        </is>
-      </c>
-      <c r="X509" s="5" t="inlineStr">
-        <is>
-          <t>Formal Trousers</t>
-        </is>
-      </c>
-      <c r="Y509" s="5" t="n"/>
-      <c r="Z509" s="5" t="n"/>
-      <c r="AA509" s="5" t="n"/>
-      <c r="AB509" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/austenas-trend-slim-fit-men-grey-trousers/p/itmd4419e16a70a1?pid=TROHZGH53TTYZMCU</t>
-        </is>
-      </c>
-      <c r="AC509" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD509" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="510" ht="22" customHeight="1">
-      <c r="A510" s="2" t="inlineStr">
-        <is>
-          <t>KAJARU_V</t>
-        </is>
-      </c>
-      <c r="B510" s="2" t="n"/>
-      <c r="C510" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D510" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E510" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F510" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G510" s="2" t="n"/>
-      <c r="H510" s="3" t="n"/>
-      <c r="I510" s="2" t="n"/>
-      <c r="J510" s="3" t="n"/>
-      <c r="K510" s="3" t="n"/>
-      <c r="L510" s="3" t="n"/>
-      <c r="M510" s="2" t="n"/>
-      <c r="N510" s="2" t="n"/>
-      <c r="O510" s="2" t="n"/>
-      <c r="P510" s="2" t="n"/>
-      <c r="Q510" s="3" t="n"/>
-      <c r="R510" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S510" s="2" t="n"/>
-      <c r="T510" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U510" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V510" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W510" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/kajaru-solid-men-beige-cargo-shorts/p/itm4d39a6d094b50?pid=SRTHEPQT8XSEHNSB</t>
-        </is>
-      </c>
-      <c r="X510" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y510" s="2" t="n"/>
-      <c r="Z510" s="2" t="n"/>
-      <c r="AA510" s="2" t="n"/>
-      <c r="AB510" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/kajaru-solid-men-beige-cargo-shorts/p/itm4d39a6d094b50?pid=SRTHEPQT8XSEHNSB</t>
-        </is>
-      </c>
-      <c r="AC510" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD510" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="511" ht="22" customHeight="1">
-      <c r="A511" s="5" t="inlineStr">
-        <is>
-          <t>PITZZ ENTERPRISE</t>
-        </is>
-      </c>
-      <c r="B511" s="5" t="n"/>
-      <c r="C511" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D511" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E511" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F511" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G511" s="5" t="n"/>
-      <c r="H511" s="6" t="n"/>
-      <c r="I511" s="5" t="n"/>
-      <c r="J511" s="6" t="n"/>
-      <c r="K511" s="6" t="n"/>
-      <c r="L511" s="6" t="n"/>
-      <c r="M511" s="5" t="n"/>
-      <c r="N511" s="5" t="n"/>
-      <c r="O511" s="5" t="n"/>
-      <c r="P511" s="5" t="n"/>
-      <c r="Q511" s="6" t="n"/>
-      <c r="R511" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S511" s="5" t="n"/>
-      <c r="T511" s="6" t="n"/>
-      <c r="U511" s="6" t="n"/>
-      <c r="V511" s="6" t="n"/>
-      <c r="W511" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pitzz-printed-men-grey-cargo-shorts/p/itm0a148475230c6?pid=SRTHPHCSHCHFKMPK</t>
-        </is>
-      </c>
-      <c r="X511" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y511" s="5" t="n"/>
-      <c r="Z511" s="5" t="n"/>
-      <c r="AA511" s="5" t="n"/>
-      <c r="AB511" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/pitzz-printed-men-grey-cargo-shorts/p/itm0a148475230c6?pid=SRTHPHCSHCHFKMPK</t>
-        </is>
-      </c>
-      <c r="AC511" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD511" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="512" ht="22" customHeight="1">
-      <c r="A512" s="2" t="inlineStr">
-        <is>
-          <t>RADHE_CREATION_</t>
-        </is>
-      </c>
-      <c r="B512" s="2" t="n"/>
-      <c r="C512" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D512" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E512" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F512" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G512" s="2" t="n"/>
-      <c r="H512" s="3" t="n"/>
-      <c r="I512" s="2" t="n"/>
-      <c r="J512" s="3" t="n"/>
-      <c r="K512" s="3" t="n"/>
-      <c r="L512" s="3" t="n"/>
-      <c r="M512" s="2" t="n"/>
-      <c r="N512" s="2" t="n"/>
-      <c r="O512" s="2" t="n"/>
-      <c r="P512" s="2" t="n"/>
-      <c r="Q512" s="3" t="n"/>
-      <c r="R512" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S512" s="2" t="n"/>
-      <c r="T512" s="3" t="n"/>
-      <c r="U512" s="3" t="n"/>
-      <c r="V512" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W512" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/glam-elegance-solid-men-grey-cargo-shorts/p/itm2bf1c92520515?pid=SRTHPHJUXBZDZZBK</t>
-        </is>
-      </c>
-      <c r="X512" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y512" s="2" t="n"/>
-      <c r="Z512" s="2" t="n"/>
-      <c r="AA512" s="2" t="n"/>
-      <c r="AB512" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/glam-elegance-solid-men-grey-cargo-shorts/p/itm2bf1c92520515?pid=SRTHPHJUXBZDZZBK</t>
-        </is>
-      </c>
-      <c r="AC512" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD512" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="513" ht="22" customHeight="1">
-      <c r="A513" s="5" t="inlineStr">
-        <is>
-          <t>Minicuddle</t>
-        </is>
-      </c>
-      <c r="B513" s="5" t="n"/>
-      <c r="C513" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D513" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E513" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F513" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G513" s="5" t="n"/>
-      <c r="H513" s="6" t="n"/>
-      <c r="I513" s="5" t="n"/>
-      <c r="J513" s="6" t="n"/>
-      <c r="K513" s="6" t="n"/>
-      <c r="L513" s="6" t="n"/>
-      <c r="M513" s="5" t="n"/>
-      <c r="N513" s="5" t="n"/>
-      <c r="O513" s="5" t="n"/>
-      <c r="P513" s="5" t="n"/>
-      <c r="Q513" s="6" t="n"/>
-      <c r="R513" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S513" s="5" t="n"/>
-      <c r="T513" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U513" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V513" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W513" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/uwald-creation-solid-men-multicolor-cargo-shorts/p/itmc6719bba07dd9?pid=SRTHJJYVTBSPKJNV</t>
-        </is>
-      </c>
-      <c r="X513" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y513" s="5" t="n"/>
-      <c r="Z513" s="5" t="n"/>
-      <c r="AA513" s="5" t="n"/>
-      <c r="AB513" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/uwald-creation-solid-men-multicolor-cargo-shorts/p/itmc6719bba07dd9?pid=SRTHJJYVTBSPKJNV</t>
-        </is>
-      </c>
-      <c r="AC513" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD513" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="514" ht="22" customHeight="1">
-      <c r="A514" s="2" t="inlineStr">
-        <is>
-          <t>JYOTPOOJA</t>
-        </is>
-      </c>
-      <c r="B514" s="2" t="n"/>
-      <c r="C514" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D514" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F514" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G514" s="2" t="n"/>
-      <c r="H514" s="3" t="n"/>
-      <c r="I514" s="2" t="n"/>
-      <c r="J514" s="3" t="n"/>
-      <c r="K514" s="3" t="n"/>
-      <c r="L514" s="3" t="n"/>
-      <c r="M514" s="2" t="n"/>
-      <c r="N514" s="2" t="n"/>
-      <c r="O514" s="2" t="n"/>
-      <c r="P514" s="2" t="n"/>
-      <c r="Q514" s="3" t="n"/>
-      <c r="R514" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S514" s="2" t="n"/>
-      <c r="T514" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U514" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V514" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W514" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/vertali-industries-printed-men-green-cargo-shorts/p/itm869e20d707c77?pid=SRTHPQ2ZWCGZSP6A</t>
-        </is>
-      </c>
-      <c r="X514" s="2" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y514" s="2" t="n"/>
-      <c r="Z514" s="2" t="n"/>
-      <c r="AA514" s="2" t="n"/>
-      <c r="AB514" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/vertali-industries-printed-men-green-cargo-shorts/p/itm869e20d707c77?pid=SRTHPQ2ZWCGZSP6A</t>
-        </is>
-      </c>
-      <c r="AC514" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD514" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="515" ht="22" customHeight="1">
-      <c r="A515" s="5" t="inlineStr">
-        <is>
-          <t>RiddhamCollection</t>
-        </is>
-      </c>
-      <c r="B515" s="5" t="n"/>
-      <c r="C515" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D515" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E515" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F515" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="G515" s="5" t="n"/>
-      <c r="H515" s="6" t="n"/>
-      <c r="I515" s="5" t="n"/>
-      <c r="J515" s="6" t="n"/>
-      <c r="K515" s="6" t="n"/>
-      <c r="L515" s="6" t="n"/>
-      <c r="M515" s="5" t="n"/>
-      <c r="N515" s="5" t="n"/>
-      <c r="O515" s="5" t="n"/>
-      <c r="P515" s="5" t="n"/>
-      <c r="Q515" s="6" t="n"/>
-      <c r="R515" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S515" s="5" t="n"/>
-      <c r="T515" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U515" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V515" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W515" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/fragment-short-boys-girls-casual-solid-cotton-blend/p/itmb0b79c0d89e93?pid=KSHHFHCRBAJBHMBH</t>
-        </is>
-      </c>
-      <c r="X515" s="5" t="inlineStr">
-        <is>
-          <t>Cargo Shorts</t>
-        </is>
-      </c>
-      <c r="Y515" s="5" t="n"/>
-      <c r="Z515" s="5" t="n"/>
-      <c r="AA515" s="5" t="n"/>
-      <c r="AB515" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/fragment-short-boys-girls-casual-solid-cotton-blend/p/itmb0b79c0d89e93?pid=KSHHFHCRBAJBHMBH</t>
-        </is>
-      </c>
-      <c r="AC515" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD515" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="516" ht="22" customHeight="1">
-      <c r="A516" s="2" t="inlineStr">
-        <is>
-          <t>Munnz</t>
-        </is>
-      </c>
-      <c r="B516" s="2" t="n"/>
-      <c r="C516" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D516" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F516" s="2" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="G516" s="2" t="n"/>
-      <c r="H516" s="3" t="n"/>
-      <c r="I516" s="2" t="n"/>
-      <c r="J516" s="3" t="n"/>
-      <c r="K516" s="3" t="n"/>
-      <c r="L516" s="3" t="n"/>
-      <c r="M516" s="2" t="n"/>
-      <c r="N516" s="2" t="n"/>
-      <c r="O516" s="2" t="n"/>
-      <c r="P516" s="2" t="n"/>
-      <c r="Q516" s="3" t="n"/>
-      <c r="R516" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S516" s="2" t="n"/>
-      <c r="T516" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U516" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V516" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W516" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
-        </is>
-      </c>
-      <c r="X516" s="2" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="Y516" s="2" t="n"/>
-      <c r="Z516" s="2" t="n"/>
-      <c r="AA516" s="2" t="n"/>
-      <c r="AB516" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
-        </is>
-      </c>
-      <c r="AC516" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD516" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="517" ht="22" customHeight="1">
-      <c r="A517" s="5" t="inlineStr">
-        <is>
-          <t>RIZIMCLOTHING</t>
-        </is>
-      </c>
-      <c r="B517" s="5" t="n"/>
-      <c r="C517" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D517" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E517" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F517" s="5" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="G517" s="5" t="n"/>
-      <c r="H517" s="6" t="n"/>
-      <c r="I517" s="5" t="n"/>
-      <c r="J517" s="6" t="n"/>
-      <c r="K517" s="6" t="n"/>
-      <c r="L517" s="6" t="n"/>
-      <c r="M517" s="5" t="n"/>
-      <c r="N517" s="5" t="n"/>
-      <c r="O517" s="5" t="n"/>
-      <c r="P517" s="5" t="n"/>
-      <c r="Q517" s="6" t="n"/>
-      <c r="R517" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S517" s="5" t="n"/>
-      <c r="T517" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U517" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="V517" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W517" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/chhote-nawab-solid-women-three-fourths/p/itm6b173939d6fdf?pid=TFHHEGJURRPNZHME</t>
-        </is>
-      </c>
-      <c r="X517" s="5" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="Y517" s="5" t="n"/>
-      <c r="Z517" s="5" t="n"/>
-      <c r="AA517" s="5" t="n"/>
-      <c r="AB517" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/chhote-nawab-solid-women-three-fourths/p/itm6b173939d6fdf?pid=TFHHEGJURRPNZHME</t>
-        </is>
-      </c>
-      <c r="AC517" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD517" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="518" ht="22" customHeight="1">
-      <c r="A518" s="2" t="inlineStr">
-        <is>
-          <t>BHAVAY</t>
-        </is>
-      </c>
-      <c r="B518" s="2" t="n"/>
-      <c r="C518" s="3" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D518" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F518" s="2" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="G518" s="2" t="n"/>
-      <c r="H518" s="3" t="n"/>
-      <c r="I518" s="2" t="n"/>
-      <c r="J518" s="3" t="n"/>
-      <c r="K518" s="3" t="n"/>
-      <c r="L518" s="3" t="n"/>
-      <c r="M518" s="2" t="n"/>
-      <c r="N518" s="2" t="n"/>
-      <c r="O518" s="2" t="n"/>
-      <c r="P518" s="2" t="n"/>
-      <c r="Q518" s="3" t="n"/>
-      <c r="R518" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S518" s="2" t="n"/>
-      <c r="T518" s="3" t="n"/>
-      <c r="U518" s="3" t="n"/>
-      <c r="V518" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W518" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/proxima-striped-men-three-fourths/p/itm7961f4cd42893?pid=TFHG9ZVZM3KFC2AX</t>
-        </is>
-      </c>
-      <c r="X518" s="2" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="Y518" s="2" t="n"/>
-      <c r="Z518" s="2" t="n"/>
-      <c r="AA518" s="2" t="n"/>
-      <c r="AB518" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/proxima-striped-men-three-fourths/p/itm7961f4cd42893?pid=TFHG9ZVZM3KFC2AX</t>
-        </is>
-      </c>
-      <c r="AC518" s="2" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD518" s="2" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
-    <row r="519" ht="22" customHeight="1">
-      <c r="A519" s="5" t="inlineStr">
-        <is>
-          <t>BIKROM GARMENTS</t>
-        </is>
-      </c>
-      <c r="B519" s="5" t="n"/>
-      <c r="C519" s="6" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
-      <c r="D519" s="10" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
-        </is>
-      </c>
-      <c r="E519" s="5" t="inlineStr">
-        <is>
-          <t>B2C / Retail</t>
-        </is>
-      </c>
-      <c r="F519" s="5" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="G519" s="5" t="n"/>
-      <c r="H519" s="6" t="n"/>
-      <c r="I519" s="5" t="n"/>
-      <c r="J519" s="6" t="n"/>
-      <c r="K519" s="6" t="n"/>
-      <c r="L519" s="6" t="n"/>
-      <c r="M519" s="5" t="n"/>
-      <c r="N519" s="5" t="n"/>
-      <c r="O519" s="5" t="n"/>
-      <c r="P519" s="5" t="n"/>
-      <c r="Q519" s="6" t="n"/>
-      <c r="R519" s="5" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="S519" s="5" t="n"/>
-      <c r="T519" s="6" t="n"/>
-      <c r="U519" s="6" t="n"/>
-      <c r="V519" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W519" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
-        </is>
-      </c>
-      <c r="X519" s="5" t="inlineStr">
-        <is>
-          <t>Three-Fourths</t>
-        </is>
-      </c>
-      <c r="Y519" s="5" t="n"/>
-      <c r="Z519" s="5" t="n"/>
-      <c r="AA519" s="5" t="n"/>
-      <c r="AB519" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
-        </is>
-      </c>
-      <c r="AC519" s="5" t="inlineStr">
-        <is>
-          <t>state_json_sold_by</t>
-        </is>
-      </c>
-      <c r="AD519" s="5" t="inlineStr">
-        <is>
-          <t>search_query</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/flipkart_sellers.xlsx
+++ b/output/flipkart_sellers.xlsx
@@ -544,8 +544,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD453"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AD568"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -11194,7 +11194,7 @@
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Bhagvati88</t>
+          <t>BHAGVATI88</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -11207,13 +11207,21 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>ENRICHMENT_PENDING</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="n"/>
-      <c r="F145" s="5" t="n"/>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
       <c r="G145" s="5" t="n"/>
       <c r="H145" s="6" t="n"/>
       <c r="I145" s="5" t="n"/>
@@ -11225,31 +11233,45 @@
       <c r="O145" s="5" t="n"/>
       <c r="P145" s="5" t="n"/>
       <c r="Q145" s="6" t="n"/>
-      <c r="R145" s="5" t="n"/>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="S145" s="5" t="n"/>
       <c r="T145" s="6" t="n"/>
       <c r="U145" s="6" t="n"/>
-      <c r="V145" s="6" t="n"/>
+      <c r="V145" s="6" t="n">
+        <v>4.6</v>
+      </c>
       <c r="W145" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/bhagwati-shirt-pant-co-ords-set/p/itm1def0435cf10e?pid=AZTHPNYKBJ2TRP7J</t>
+          <t>https://www.flipkart.com/bhagwati-embroidered-kurta-trouser-pant-dupatta-set/p/itm286d1ea30724f?pid=SWDHPNYEYVBFQ7RG</t>
         </is>
       </c>
       <c r="X145" s="5" t="inlineStr">
         <is>
-          <t>Women's Formals</t>
+          <t>Suit Trousers</t>
         </is>
       </c>
       <c r="Y145" s="5" t="n"/>
       <c r="Z145" s="5" t="n"/>
       <c r="AA145" s="5" t="n"/>
-      <c r="AB145" s="5" t="n"/>
+      <c r="AB145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bhagwati-embroidered-kurta-trouser-pant-dupatta-set/p/itm286d1ea30724f?pid=SWDHPNYEYVBFQ7RG</t>
+        </is>
+      </c>
       <c r="AC145" s="5" t="inlineStr">
         <is>
           <t>fulfillment_label</t>
         </is>
       </c>
-      <c r="AD145" s="5" t="n"/>
+      <c r="AD145" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -38861,6 +38883,9412 @@
         </is>
       </c>
     </row>
+    <row r="454" ht="22" customHeight="1">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Reoutlook</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>Reoutlook</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D454" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="n"/>
+      <c r="H454" s="3" t="n"/>
+      <c r="I454" s="2" t="n"/>
+      <c r="J454" s="3" t="n"/>
+      <c r="K454" s="3" t="n"/>
+      <c r="L454" s="3" t="n"/>
+      <c r="M454" s="2" t="n"/>
+      <c r="N454" s="2" t="n"/>
+      <c r="O454" s="2" t="n"/>
+      <c r="P454" s="2" t="n"/>
+      <c r="Q454" s="3" t="n"/>
+      <c r="R454" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S454" s="2" t="n"/>
+      <c r="T454" s="3" t="n"/>
+      <c r="U454" s="3" t="n"/>
+      <c r="V454" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/reoutlook-solid-men-three-fourths/p/itmd13c195670a4e?pid=TFHHZM9SD6VHW2FR</t>
+        </is>
+      </c>
+      <c r="X454" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y454" s="2" t="n"/>
+      <c r="Z454" s="2" t="n"/>
+      <c r="AA454" s="2" t="n"/>
+      <c r="AB454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/reoutlook-solid-men-three-fourths/p/itmd13c195670a4e?pid=TFHHZM9SD6VHW2FR</t>
+        </is>
+      </c>
+      <c r="AC454" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD454" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="1">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t>UrbanShortsCompany</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>UrbanShortsCompany</t>
+        </is>
+      </c>
+      <c r="C455" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D455" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E455" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="n"/>
+      <c r="H455" s="6" t="n"/>
+      <c r="I455" s="5" t="n"/>
+      <c r="J455" s="6" t="n"/>
+      <c r="K455" s="6" t="n"/>
+      <c r="L455" s="6" t="n"/>
+      <c r="M455" s="5" t="n"/>
+      <c r="N455" s="5" t="n"/>
+      <c r="O455" s="5" t="n"/>
+      <c r="P455" s="5" t="n"/>
+      <c r="Q455" s="6" t="n"/>
+      <c r="R455" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S455" s="5" t="n"/>
+      <c r="T455" s="6" t="n"/>
+      <c r="U455" s="6" t="n"/>
+      <c r="V455" s="6" t="n"/>
+      <c r="W455" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/finefashion-checkered-men-three-fourths/p/itm9a1664b6b8297?pid=TFHHZNEFFESNGVTB</t>
+        </is>
+      </c>
+      <c r="X455" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y455" s="5" t="n"/>
+      <c r="Z455" s="5" t="n"/>
+      <c r="AA455" s="5" t="n"/>
+      <c r="AB455" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/finefashion-checkered-men-three-fourths/p/itm9a1664b6b8297?pid=TFHHZNEFFESNGVTB</t>
+        </is>
+      </c>
+      <c r="AC455" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD455" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="22" customHeight="1">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>retailvmart</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>retailvmart</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D456" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="n"/>
+      <c r="H456" s="3" t="n"/>
+      <c r="I456" s="2" t="n"/>
+      <c r="J456" s="3" t="n"/>
+      <c r="K456" s="3" t="n"/>
+      <c r="L456" s="3" t="n"/>
+      <c r="M456" s="2" t="n"/>
+      <c r="N456" s="2" t="n"/>
+      <c r="O456" s="2" t="n"/>
+      <c r="P456" s="2" t="n"/>
+      <c r="Q456" s="3" t="n"/>
+      <c r="R456" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S456" s="2" t="n"/>
+      <c r="T456" s="3" t="n"/>
+      <c r="U456" s="3" t="n"/>
+      <c r="V456" s="3" t="n"/>
+      <c r="W456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/v-mart-printed-men-grey-regular-shorts/p/itm56b0b849b40c2?pid=SRTHZZPS237XSXJH</t>
+        </is>
+      </c>
+      <c r="X456" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y456" s="2" t="n"/>
+      <c r="Z456" s="2" t="n"/>
+      <c r="AA456" s="2" t="n"/>
+      <c r="AB456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/v-mart-printed-men-grey-regular-shorts/p/itm56b0b849b40c2?pid=SRTHZZPS237XSXJH</t>
+        </is>
+      </c>
+      <c r="AC456" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD456" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="22" customHeight="1">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>Gentleman</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>Gentleman</t>
+        </is>
+      </c>
+      <c r="C457" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D457" s="7" t="inlineStr">
+        <is>
+          <t>PARTIALLY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="n"/>
+      <c r="H457" s="6" t="n"/>
+      <c r="I457" s="5" t="inlineStr">
+        <is>
+          <t>contact@thegentlemansjournal.com</t>
+        </is>
+      </c>
+      <c r="J457" s="6" t="n"/>
+      <c r="K457" s="6" t="n"/>
+      <c r="L457" s="6" t="n"/>
+      <c r="M457" s="5" t="n"/>
+      <c r="N457" s="5" t="n"/>
+      <c r="O457" s="5" t="n"/>
+      <c r="P457" s="5" t="n"/>
+      <c r="Q457" s="6" t="n"/>
+      <c r="R457" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thegentlemansjournal.com</t>
+        </is>
+      </c>
+      <c r="T457" s="6" t="n"/>
+      <c r="U457" s="6" t="n"/>
+      <c r="V457" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/0-degree-solid-men-three-fourths/p/itm1b4978b596931?pid=TFHFKG48MQTUTTGA</t>
+        </is>
+      </c>
+      <c r="X457" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y457" s="5" t="n"/>
+      <c r="Z457" s="5" t="n"/>
+      <c r="AA457" s="5" t="n"/>
+      <c r="AB457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/0-degree-solid-men-three-fourths/p/itm1b4978b596931?pid=TFHFKG48MQTUTTGA</t>
+        </is>
+      </c>
+      <c r="AC457" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD457" s="5" t="inlineStr">
+        <is>
+          <t>company_website</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>OUTFLITS</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>OUTFLITS</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D458" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="n"/>
+      <c r="H458" s="3" t="n"/>
+      <c r="I458" s="2" t="n"/>
+      <c r="J458" s="3" t="n"/>
+      <c r="K458" s="3" t="n"/>
+      <c r="L458" s="3" t="n"/>
+      <c r="M458" s="2" t="n"/>
+      <c r="N458" s="2" t="n"/>
+      <c r="O458" s="2" t="n"/>
+      <c r="P458" s="2" t="n"/>
+      <c r="Q458" s="3" t="n"/>
+      <c r="R458" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S458" s="2" t="n"/>
+      <c r="T458" s="3" t="n"/>
+      <c r="U458" s="3" t="n"/>
+      <c r="V458" s="3" t="n"/>
+      <c r="W458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/2k-kids-three-fourth-boys/p/itm747f588054d0c?pid=KTFHPBR8Q7AAHYP3</t>
+        </is>
+      </c>
+      <c r="X458" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y458" s="2" t="n"/>
+      <c r="Z458" s="2" t="n"/>
+      <c r="AA458" s="2" t="n"/>
+      <c r="AB458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/2k-kids-three-fourth-boys/p/itm747f588054d0c?pid=KTFHPBR8Q7AAHYP3</t>
+        </is>
+      </c>
+      <c r="AC458" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD458" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="22" customHeight="1">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t>PRATHAKSHANAEXPORTS</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>PRATHAKSHANAEXPORTS</t>
+        </is>
+      </c>
+      <c r="C459" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D459" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="n"/>
+      <c r="H459" s="6" t="n"/>
+      <c r="I459" s="5" t="n"/>
+      <c r="J459" s="6" t="n"/>
+      <c r="K459" s="6" t="n"/>
+      <c r="L459" s="6" t="n"/>
+      <c r="M459" s="5" t="n"/>
+      <c r="N459" s="5" t="n"/>
+      <c r="O459" s="5" t="n"/>
+      <c r="P459" s="5" t="n"/>
+      <c r="Q459" s="6" t="n"/>
+      <c r="R459" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S459" s="5" t="n"/>
+      <c r="T459" s="6" t="n"/>
+      <c r="U459" s="6" t="n"/>
+      <c r="V459" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W459" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/prathakshana-three-fourth-boys/p/itmc088a175edec6?pid=KTFH938E6QTEFPNE</t>
+        </is>
+      </c>
+      <c r="X459" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y459" s="5" t="n"/>
+      <c r="Z459" s="5" t="n"/>
+      <c r="AA459" s="5" t="n"/>
+      <c r="AB459" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/prathakshana-three-fourth-boys/p/itmc088a175edec6?pid=KTFH938E6QTEFPNE</t>
+        </is>
+      </c>
+      <c r="AC459" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD459" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="22" customHeight="1">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>GUIDEFASHION</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>GUIDEFASHION</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D460" s="7" t="inlineStr">
+        <is>
+          <t>PARTIALLY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="n"/>
+      <c r="H460" s="3" t="n"/>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>themeruby@gmail.com</t>
+        </is>
+      </c>
+      <c r="J460" s="3" t="n"/>
+      <c r="K460" s="3" t="n"/>
+      <c r="L460" s="3" t="n"/>
+      <c r="M460" s="2" t="n"/>
+      <c r="N460" s="2" t="n"/>
+      <c r="O460" s="2" t="n"/>
+      <c r="P460" s="2" t="n"/>
+      <c r="Q460" s="3" t="n"/>
+      <c r="R460" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S460" s="2" t="inlineStr">
+        <is>
+          <t>https://onlymechanic.com</t>
+        </is>
+      </c>
+      <c r="T460" s="3" t="n"/>
+      <c r="U460" s="3" t="n"/>
+      <c r="V460" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/guide-printed-men-three-fourths/p/itm4de65af49932f?pid=TFHG4R9EXFFJQWUH</t>
+        </is>
+      </c>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="n"/>
+      <c r="Z460" s="2" t="n"/>
+      <c r="AA460" s="2" t="n"/>
+      <c r="AB460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/guide-printed-men-three-fourths/p/itm4de65af49932f?pid=TFHG4R9EXFFJQWUH</t>
+        </is>
+      </c>
+      <c r="AC460" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD460" s="2" t="inlineStr">
+        <is>
+          <t>company_website</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="22" customHeight="1">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>Mentionstore</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>Mentionstore</t>
+        </is>
+      </c>
+      <c r="C461" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D461" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E461" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="n"/>
+      <c r="H461" s="6" t="n"/>
+      <c r="I461" s="5" t="n"/>
+      <c r="J461" s="6" t="n"/>
+      <c r="K461" s="6" t="n"/>
+      <c r="L461" s="6" t="n"/>
+      <c r="M461" s="5" t="n"/>
+      <c r="N461" s="5" t="n"/>
+      <c r="O461" s="5" t="n"/>
+      <c r="P461" s="5" t="n"/>
+      <c r="Q461" s="6" t="n"/>
+      <c r="R461" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S461" s="5" t="n"/>
+      <c r="T461" s="6" t="n"/>
+      <c r="U461" s="6" t="n"/>
+      <c r="V461" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W461" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mention-solid-men-three-fourths/p/itmbde3275f31805?pid=TFHHD69EZUQKFEHH</t>
+        </is>
+      </c>
+      <c r="X461" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y461" s="5" t="n"/>
+      <c r="Z461" s="5" t="n"/>
+      <c r="AA461" s="5" t="n"/>
+      <c r="AB461" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mention-solid-men-three-fourths/p/itmbde3275f31805?pid=TFHHD69EZUQKFEHH</t>
+        </is>
+      </c>
+      <c r="AC461" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD461" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="1">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>SPNAPPARELS</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>SPNAPPARELS</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D462" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="n"/>
+      <c r="H462" s="3" t="n"/>
+      <c r="I462" s="2" t="n"/>
+      <c r="J462" s="3" t="n"/>
+      <c r="K462" s="3" t="n"/>
+      <c r="L462" s="3" t="n"/>
+      <c r="M462" s="2" t="n"/>
+      <c r="N462" s="2" t="n"/>
+      <c r="O462" s="2" t="n"/>
+      <c r="P462" s="2" t="n"/>
+      <c r="Q462" s="3" t="n"/>
+      <c r="R462" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S462" s="2" t="n"/>
+      <c r="T462" s="3" t="n"/>
+      <c r="U462" s="3" t="n"/>
+      <c r="V462" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/spn-solid-men-three-fourths/p/itm20ad4797bf520?pid=TFHHJ7YZHCEXP2YV</t>
+        </is>
+      </c>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="n"/>
+      <c r="Z462" s="2" t="n"/>
+      <c r="AA462" s="2" t="n"/>
+      <c r="AB462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/spn-solid-men-three-fourths/p/itm20ad4797bf520?pid=TFHHJ7YZHCEXP2YV</t>
+        </is>
+      </c>
+      <c r="AC462" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD462" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="22" customHeight="1">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t>SINGLECHOICE</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>SINGLECHOICE</t>
+        </is>
+      </c>
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D463" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E463" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="n"/>
+      <c r="H463" s="6" t="n"/>
+      <c r="I463" s="5" t="n"/>
+      <c r="J463" s="6" t="n"/>
+      <c r="K463" s="6" t="n"/>
+      <c r="L463" s="6" t="n"/>
+      <c r="M463" s="5" t="n"/>
+      <c r="N463" s="5" t="n"/>
+      <c r="O463" s="5" t="n"/>
+      <c r="P463" s="5" t="n"/>
+      <c r="Q463" s="6" t="n"/>
+      <c r="R463" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S463" s="5" t="n"/>
+      <c r="T463" s="6" t="n"/>
+      <c r="U463" s="6" t="n"/>
+      <c r="V463" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="W463" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kasid-enterprises-checkered-men-three-fourths/p/itm020094df3008e?pid=TFHGGV25CUNYCFDV</t>
+        </is>
+      </c>
+      <c r="X463" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y463" s="5" t="n"/>
+      <c r="Z463" s="5" t="n"/>
+      <c r="AA463" s="5" t="n"/>
+      <c r="AB463" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kasid-enterprises-checkered-men-three-fourths/p/itm020094df3008e?pid=TFHGGV25CUNYCFDV</t>
+        </is>
+      </c>
+      <c r="AC463" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD463" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="22" customHeight="1">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>MADE4GOOD</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>MADE4GOOD</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D464" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="n"/>
+      <c r="H464" s="3" t="n"/>
+      <c r="I464" s="2" t="n"/>
+      <c r="J464" s="3" t="n"/>
+      <c r="K464" s="3" t="n"/>
+      <c r="L464" s="3" t="n"/>
+      <c r="M464" s="2" t="n"/>
+      <c r="N464" s="2" t="n"/>
+      <c r="O464" s="2" t="n"/>
+      <c r="P464" s="2" t="n"/>
+      <c r="Q464" s="3" t="n"/>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="n"/>
+      <c r="T464" s="3" t="n"/>
+      <c r="U464" s="3" t="n"/>
+      <c r="V464" s="3" t="n"/>
+      <c r="W464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/made4good-women-grey-capri/p/itmac2fb23d2231e?pid=CPIHZQHGPKA68FTH</t>
+        </is>
+      </c>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="n"/>
+      <c r="Z464" s="2" t="n"/>
+      <c r="AA464" s="2" t="n"/>
+      <c r="AB464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/made4good-women-grey-capri/p/itmac2fb23d2231e?pid=CPIHZQHGPKA68FTH</t>
+        </is>
+      </c>
+      <c r="AC464" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD464" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="22" customHeight="1">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t>KRDFASHION</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>KRDFASHION</t>
+        </is>
+      </c>
+      <c r="C465" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D465" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F465" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G465" s="5" t="n"/>
+      <c r="H465" s="6" t="n"/>
+      <c r="I465" s="5" t="n"/>
+      <c r="J465" s="6" t="n"/>
+      <c r="K465" s="6" t="n"/>
+      <c r="L465" s="6" t="n"/>
+      <c r="M465" s="5" t="n"/>
+      <c r="N465" s="5" t="n"/>
+      <c r="O465" s="5" t="n"/>
+      <c r="P465" s="5" t="n"/>
+      <c r="Q465" s="6" t="n"/>
+      <c r="R465" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S465" s="5" t="n"/>
+      <c r="T465" s="6" t="n"/>
+      <c r="U465" s="6" t="n"/>
+      <c r="V465" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W465" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/krd-fashion-printed-men-three-fourths/p/itmb6031fa49428a?pid=TFHGGFDBQSYVH8XB</t>
+        </is>
+      </c>
+      <c r="X465" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y465" s="5" t="n"/>
+      <c r="Z465" s="5" t="n"/>
+      <c r="AA465" s="5" t="n"/>
+      <c r="AB465" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/krd-fashion-printed-men-three-fourths/p/itmb6031fa49428a?pid=TFHGGFDBQSYVH8XB</t>
+        </is>
+      </c>
+      <c r="AC465" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD465" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="22" customHeight="1">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Cosvos</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Cosvos</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D466" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="n"/>
+      <c r="H466" s="3" t="n"/>
+      <c r="I466" s="2" t="n"/>
+      <c r="J466" s="3" t="n"/>
+      <c r="K466" s="3" t="n"/>
+      <c r="L466" s="3" t="n"/>
+      <c r="M466" s="2" t="n"/>
+      <c r="N466" s="2" t="n"/>
+      <c r="O466" s="2" t="n"/>
+      <c r="P466" s="2" t="n"/>
+      <c r="Q466" s="3" t="n"/>
+      <c r="R466" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S466" s="2" t="n"/>
+      <c r="T466" s="3" t="n"/>
+      <c r="U466" s="3" t="n"/>
+      <c r="V466" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cosvos-solid-women-black-tights/p/itm7a656f8f54813?pid=TGTGGE5CPPVCZCZY</t>
+        </is>
+      </c>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="n"/>
+      <c r="Z466" s="2" t="n"/>
+      <c r="AA466" s="2" t="n"/>
+      <c r="AB466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cosvos-solid-women-black-tights/p/itm7a656f8f54813?pid=TGTGGE5CPPVCZCZY</t>
+        </is>
+      </c>
+      <c r="AC466" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD466" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="22" customHeight="1">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t>TroopLine</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>TroopLine</t>
+        </is>
+      </c>
+      <c r="C467" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D467" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="n"/>
+      <c r="H467" s="6" t="n"/>
+      <c r="I467" s="5" t="n"/>
+      <c r="J467" s="6" t="n"/>
+      <c r="K467" s="6" t="n"/>
+      <c r="L467" s="6" t="n"/>
+      <c r="M467" s="5" t="n"/>
+      <c r="N467" s="5" t="n"/>
+      <c r="O467" s="5" t="n"/>
+      <c r="P467" s="5" t="n"/>
+      <c r="Q467" s="6" t="n"/>
+      <c r="R467" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S467" s="5" t="n"/>
+      <c r="T467" s="6" t="n"/>
+      <c r="U467" s="6" t="n"/>
+      <c r="V467" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W467" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/troopline-solid-men-dark-blue-tights/p/itmd8e7d38442a02?pid=TGTH3CH9AQHAMTJM</t>
+        </is>
+      </c>
+      <c r="X467" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y467" s="5" t="n"/>
+      <c r="Z467" s="5" t="n"/>
+      <c r="AA467" s="5" t="n"/>
+      <c r="AB467" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/troopline-solid-men-dark-blue-tights/p/itmd8e7d38442a02?pid=TGTH3CH9AQHAMTJM</t>
+        </is>
+      </c>
+      <c r="AC467" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD467" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="1">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>POOJARAN SAREE</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>POOJARAN SAREE</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D468" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="n"/>
+      <c r="H468" s="3" t="n"/>
+      <c r="I468" s="2" t="n"/>
+      <c r="J468" s="3" t="n"/>
+      <c r="K468" s="3" t="n"/>
+      <c r="L468" s="3" t="n"/>
+      <c r="M468" s="2" t="n"/>
+      <c r="N468" s="2" t="n"/>
+      <c r="O468" s="2" t="n"/>
+      <c r="P468" s="2" t="n"/>
+      <c r="Q468" s="3" t="n"/>
+      <c r="R468" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S468" s="2" t="n"/>
+      <c r="T468" s="3" t="n"/>
+      <c r="U468" s="3" t="n"/>
+      <c r="V468" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/poojaran-solid-women-multicolor-tights/p/itmf7e5a6c8c0004?pid=TGTHM8NVQ2YGJ56U</t>
+        </is>
+      </c>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="n"/>
+      <c r="Z468" s="2" t="n"/>
+      <c r="AA468" s="2" t="n"/>
+      <c r="AB468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/poojaran-solid-women-multicolor-tights/p/itmf7e5a6c8c0004?pid=TGTHM8NVQ2YGJ56U</t>
+        </is>
+      </c>
+      <c r="AC468" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD468" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="22" customHeight="1">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t>CenturyIndia</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>CenturyIndia</t>
+        </is>
+      </c>
+      <c r="C469" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D469" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="n"/>
+      <c r="H469" s="6" t="n"/>
+      <c r="I469" s="5" t="n"/>
+      <c r="J469" s="6" t="n"/>
+      <c r="K469" s="6" t="n"/>
+      <c r="L469" s="6" t="n"/>
+      <c r="M469" s="5" t="n"/>
+      <c r="N469" s="5" t="n"/>
+      <c r="O469" s="5" t="n"/>
+      <c r="P469" s="5" t="n"/>
+      <c r="Q469" s="6" t="n"/>
+      <c r="R469" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S469" s="5" t="n"/>
+      <c r="T469" s="6" t="n"/>
+      <c r="U469" s="6" t="n"/>
+      <c r="V469" s="6" t="n"/>
+      <c r="W469" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/never-quit-solid-men-black-tights/p/itm7f795c116bf66?pid=TGTHNTE9FRDTJHSQ</t>
+        </is>
+      </c>
+      <c r="X469" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y469" s="5" t="n"/>
+      <c r="Z469" s="5" t="n"/>
+      <c r="AA469" s="5" t="n"/>
+      <c r="AB469" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/never-quit-solid-men-black-tights/p/itm7f795c116bf66?pid=TGTHNTE9FRDTJHSQ</t>
+        </is>
+      </c>
+      <c r="AC469" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD469" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="22" customHeight="1">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>NIshant sports g textile</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>NIshant sports g textile</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D470" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="n"/>
+      <c r="H470" s="3" t="n"/>
+      <c r="I470" s="2" t="n"/>
+      <c r="J470" s="3" t="n"/>
+      <c r="K470" s="3" t="n"/>
+      <c r="L470" s="3" t="n"/>
+      <c r="M470" s="2" t="n"/>
+      <c r="N470" s="2" t="n"/>
+      <c r="O470" s="2" t="n"/>
+      <c r="P470" s="2" t="n"/>
+      <c r="Q470" s="3" t="n"/>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="n"/>
+      <c r="T470" s="3" t="n"/>
+      <c r="U470" s="3" t="n"/>
+      <c r="V470" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nishant-sports-solid-men-black-tights/p/itmed6e52389ca1e?pid=TGTGG4B69GDGZKGP</t>
+        </is>
+      </c>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="n"/>
+      <c r="Z470" s="2" t="n"/>
+      <c r="AA470" s="2" t="n"/>
+      <c r="AB470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nishant-sports-solid-men-black-tights/p/itmed6e52389ca1e?pid=TGTGG4B69GDGZKGP</t>
+        </is>
+      </c>
+      <c r="AC470" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD470" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="22" customHeight="1">
+      <c r="A471" s="5" t="inlineStr">
+        <is>
+          <t>AoneVenturesPvtLtd</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>AoneVenturesPvtLtd</t>
+        </is>
+      </c>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D471" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="inlineStr">
+        <is>
+          <t>Public Limited Company</t>
+        </is>
+      </c>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="n"/>
+      <c r="H471" s="6" t="n"/>
+      <c r="I471" s="5" t="n"/>
+      <c r="J471" s="6" t="n"/>
+      <c r="K471" s="6" t="n"/>
+      <c r="L471" s="6" t="n"/>
+      <c r="M471" s="5" t="n"/>
+      <c r="N471" s="5" t="n"/>
+      <c r="O471" s="5" t="n"/>
+      <c r="P471" s="5" t="n"/>
+      <c r="Q471" s="6" t="n"/>
+      <c r="R471" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S471" s="5" t="n"/>
+      <c r="T471" s="6" t="n"/>
+      <c r="U471" s="6" t="n"/>
+      <c r="V471" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W471" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/revora-solid-women-black-tights/p/itm0046e1b627114?pid=TGTHZD7GQ66TYXDF</t>
+        </is>
+      </c>
+      <c r="X471" s="5" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y471" s="5" t="n"/>
+      <c r="Z471" s="5" t="n"/>
+      <c r="AA471" s="5" t="n"/>
+      <c r="AB471" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/revora-solid-women-black-tights/p/itm0046e1b627114?pid=TGTHZD7GQ66TYXDF</t>
+        </is>
+      </c>
+      <c r="AC471" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD471" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="22" customHeight="1">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>KGNHUB</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>KGNHUB</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D472" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="n"/>
+      <c r="H472" s="3" t="n"/>
+      <c r="I472" s="2" t="n"/>
+      <c r="J472" s="3" t="n"/>
+      <c r="K472" s="3" t="n"/>
+      <c r="L472" s="3" t="n"/>
+      <c r="M472" s="2" t="n"/>
+      <c r="N472" s="2" t="n"/>
+      <c r="O472" s="2" t="n"/>
+      <c r="P472" s="2" t="n"/>
+      <c r="Q472" s="3" t="n"/>
+      <c r="R472" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S472" s="2" t="n"/>
+      <c r="T472" s="3" t="n"/>
+      <c r="U472" s="3" t="n"/>
+      <c r="V472" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kgn-hub-color-block-women-black-white-tights/p/itmce8d0a68594a6?pid=TGTHPRGWGNAKMPYA</t>
+        </is>
+      </c>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>Tights</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="n"/>
+      <c r="Z472" s="2" t="n"/>
+      <c r="AA472" s="2" t="n"/>
+      <c r="AB472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kgn-hub-color-block-women-black-white-tights/p/itmce8d0a68594a6?pid=TGTHPRGWGNAKMPYA</t>
+        </is>
+      </c>
+      <c r="AC472" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD472" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="22" customHeight="1">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>RadhaRaniCreationlko</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>RadhaRaniCreationlko</t>
+        </is>
+      </c>
+      <c r="C473" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="n"/>
+      <c r="H473" s="6" t="n"/>
+      <c r="I473" s="5" t="n"/>
+      <c r="J473" s="6" t="n"/>
+      <c r="K473" s="6" t="n"/>
+      <c r="L473" s="6" t="n"/>
+      <c r="M473" s="5" t="n"/>
+      <c r="N473" s="5" t="n"/>
+      <c r="O473" s="5" t="n"/>
+      <c r="P473" s="5" t="n"/>
+      <c r="Q473" s="6" t="n"/>
+      <c r="R473" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S473" s="5" t="n"/>
+      <c r="T473" s="6" t="n"/>
+      <c r="U473" s="6" t="n"/>
+      <c r="V473" s="6" t="n"/>
+      <c r="W473" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kiya-suit-solid-girls/p/itmd84c9cd041864?pid=SUIHZFFGGSBFQBTD</t>
+        </is>
+      </c>
+      <c r="X473" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y473" s="5" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z473" s="5" t="n"/>
+      <c r="AA473" s="5" t="n"/>
+      <c r="AB473" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kiya-suit-solid-girls/p/itmd84c9cd041864?pid=SUIHZFFGGSBFQBTD</t>
+        </is>
+      </c>
+      <c r="AC473" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD473" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="22" customHeight="1">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Arshiafashions</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>Arshiafashions</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D474" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="n"/>
+      <c r="H474" s="3" t="n"/>
+      <c r="I474" s="2" t="n"/>
+      <c r="J474" s="3" t="n"/>
+      <c r="K474" s="3" t="n"/>
+      <c r="L474" s="3" t="n"/>
+      <c r="M474" s="2" t="n"/>
+      <c r="N474" s="2" t="n"/>
+      <c r="O474" s="2" t="n"/>
+      <c r="P474" s="2" t="n"/>
+      <c r="Q474" s="3" t="n"/>
+      <c r="R474" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S474" s="2" t="n"/>
+      <c r="T474" s="3" t="n"/>
+      <c r="U474" s="3" t="n"/>
+      <c r="V474" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/arshia-fashions-kids-waistcoat-suit-checkered-boys/p/itm544144a495800?pid=SUIFXU6HT2APEPAU</t>
+        </is>
+      </c>
+      <c r="X474" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z474" s="2" t="n"/>
+      <c r="AA474" s="2" t="n"/>
+      <c r="AB474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/arshia-fashions-kids-waistcoat-suit-checkered-boys/p/itm544144a495800?pid=SUIFXU6HT2APEPAU</t>
+        </is>
+      </c>
+      <c r="AC474" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD474" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="22" customHeight="1">
+      <c r="A475" s="5" t="inlineStr">
+        <is>
+          <t>OMOMSHRIBALAJI</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>OMOMSHRIBALAJI</t>
+        </is>
+      </c>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D475" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G475" s="5" t="n"/>
+      <c r="H475" s="6" t="n"/>
+      <c r="I475" s="5" t="n"/>
+      <c r="J475" s="6" t="n"/>
+      <c r="K475" s="6" t="n"/>
+      <c r="L475" s="6" t="n"/>
+      <c r="M475" s="5" t="n"/>
+      <c r="N475" s="5" t="n"/>
+      <c r="O475" s="5" t="n"/>
+      <c r="P475" s="5" t="n"/>
+      <c r="Q475" s="6" t="n"/>
+      <c r="R475" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S475" s="5" t="n"/>
+      <c r="T475" s="6" t="n"/>
+      <c r="U475" s="6" t="n"/>
+      <c r="V475" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/om-shribalaji-suit-set-solid-boys/p/itmf567a28a6fd37?pid=SUIHNGYCF8JNZFU9</t>
+        </is>
+      </c>
+      <c r="X475" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y475" s="5" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z475" s="5" t="n"/>
+      <c r="AA475" s="5" t="n"/>
+      <c r="AB475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/om-shribalaji-suit-set-solid-boys/p/itmf567a28a6fd37?pid=SUIHNGYCF8JNZFU9</t>
+        </is>
+      </c>
+      <c r="AC475" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD475" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="22" customHeight="1">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>BTDEZINES</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>BTDEZINES</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D476" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="n"/>
+      <c r="H476" s="3" t="n"/>
+      <c r="I476" s="2" t="n"/>
+      <c r="J476" s="3" t="n"/>
+      <c r="K476" s="3" t="n"/>
+      <c r="L476" s="3" t="n"/>
+      <c r="M476" s="2" t="n"/>
+      <c r="N476" s="2" t="n"/>
+      <c r="O476" s="2" t="n"/>
+      <c r="P476" s="2" t="n"/>
+      <c r="Q476" s="3" t="n"/>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="n"/>
+      <c r="T476" s="3" t="n"/>
+      <c r="U476" s="3" t="n"/>
+      <c r="V476" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bt-dezines-5-piece-coat-pant-suit-set-boys-self-design/p/itm264b4599e8186?pid=SUIGJF9HNEPW35RU</t>
+        </is>
+      </c>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z476" s="2" t="n"/>
+      <c r="AA476" s="2" t="n"/>
+      <c r="AB476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bt-dezines-5-piece-coat-pant-suit-set-boys-self-design/p/itm264b4599e8186?pid=SUIGJF9HNEPW35RU</t>
+        </is>
+      </c>
+      <c r="AC476" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD476" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="22" customHeight="1">
+      <c r="A477" s="5" t="inlineStr">
+        <is>
+          <t>Fourfolds</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>Fourfolds</t>
+        </is>
+      </c>
+      <c r="C477" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D477" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E477" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G477" s="5" t="n"/>
+      <c r="H477" s="6" t="n"/>
+      <c r="I477" s="5" t="n"/>
+      <c r="J477" s="6" t="n"/>
+      <c r="K477" s="6" t="n"/>
+      <c r="L477" s="6" t="n"/>
+      <c r="M477" s="5" t="n"/>
+      <c r="N477" s="5" t="n"/>
+      <c r="O477" s="5" t="n"/>
+      <c r="P477" s="5" t="n"/>
+      <c r="Q477" s="6" t="n"/>
+      <c r="R477" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S477" s="5" t="n"/>
+      <c r="T477" s="6" t="n"/>
+      <c r="U477" s="6" t="n"/>
+      <c r="V477" s="6" t="n"/>
+      <c r="W477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fourfolds-3-piece-embroidered-boys-suit/p/itmcafc5eee8d287?pid=SUIHPF6UYCAFWE2Y</t>
+        </is>
+      </c>
+      <c r="X477" s="5" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y477" s="5" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z477" s="5" t="n"/>
+      <c r="AA477" s="5" t="n"/>
+      <c r="AB477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fourfolds-3-piece-embroidered-boys-suit/p/itmcafc5eee8d287?pid=SUIHPF6UYCAFWE2Y</t>
+        </is>
+      </c>
+      <c r="AC477" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD477" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="1">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Unitedt</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Unitedt</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D478" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="n"/>
+      <c r="H478" s="3" t="n"/>
+      <c r="I478" s="2" t="n"/>
+      <c r="J478" s="3" t="n"/>
+      <c r="K478" s="3" t="n"/>
+      <c r="L478" s="3" t="n"/>
+      <c r="M478" s="2" t="n"/>
+      <c r="N478" s="2" t="n"/>
+      <c r="O478" s="2" t="n"/>
+      <c r="P478" s="2" t="n"/>
+      <c r="Q478" s="3" t="n"/>
+      <c r="R478" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S478" s="2" t="n"/>
+      <c r="T478" s="3" t="n"/>
+      <c r="U478" s="3" t="n"/>
+      <c r="V478" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/utsav-creation-solid-men-waistcoat/p/itm2c473982f2be5?pid=WSCHKWZMHAFNEH4H</t>
+        </is>
+      </c>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>Blazers, Waistcoats &amp; Suits</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="inlineStr">
+        <is>
+          <t>Suits</t>
+        </is>
+      </c>
+      <c r="Z478" s="2" t="n"/>
+      <c r="AA478" s="2" t="n"/>
+      <c r="AB478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/utsav-creation-solid-men-waistcoat/p/itm2c473982f2be5?pid=WSCHKWZMHAFNEH4H</t>
+        </is>
+      </c>
+      <c r="AC478" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD478" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="1">
+      <c r="A479" s="5" t="inlineStr">
+        <is>
+          <t>JUSTSHOP1912</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>JUSTSHOP1912</t>
+        </is>
+      </c>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D479" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G479" s="5" t="n"/>
+      <c r="H479" s="6" t="n"/>
+      <c r="I479" s="5" t="n"/>
+      <c r="J479" s="6" t="n"/>
+      <c r="K479" s="6" t="n"/>
+      <c r="L479" s="6" t="n"/>
+      <c r="M479" s="5" t="n"/>
+      <c r="N479" s="5" t="n"/>
+      <c r="O479" s="5" t="n"/>
+      <c r="P479" s="5" t="n"/>
+      <c r="Q479" s="6" t="n"/>
+      <c r="R479" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S479" s="5" t="n"/>
+      <c r="T479" s="6" t="n"/>
+      <c r="U479" s="6" t="n"/>
+      <c r="V479" s="6" t="n"/>
+      <c r="W479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/just-shop-solid-women-waistcoat/p/itm9377ed2c0c86a?pid=WSCHPJKZW46TQKPZ</t>
+        </is>
+      </c>
+      <c r="X479" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y479" s="5" t="n"/>
+      <c r="Z479" s="5" t="n"/>
+      <c r="AA479" s="5" t="n"/>
+      <c r="AB479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/just-shop-solid-women-waistcoat/p/itm9377ed2c0c86a?pid=WSCHPJKZW46TQKPZ</t>
+        </is>
+      </c>
+      <c r="AC479" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD479" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="22" customHeight="1">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Mfiya</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>Mfiya</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D480" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="n"/>
+      <c r="H480" s="3" t="n"/>
+      <c r="I480" s="2" t="n"/>
+      <c r="J480" s="3" t="n"/>
+      <c r="K480" s="3" t="n"/>
+      <c r="L480" s="3" t="n"/>
+      <c r="M480" s="2" t="n"/>
+      <c r="N480" s="2" t="n"/>
+      <c r="O480" s="2" t="n"/>
+      <c r="P480" s="2" t="n"/>
+      <c r="Q480" s="3" t="n"/>
+      <c r="R480" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S480" s="2" t="n"/>
+      <c r="T480" s="3" t="n"/>
+      <c r="U480" s="3" t="n"/>
+      <c r="V480" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mfiya-printed-men-waistcoat/p/itmd766fb57a4f1e?pid=WSCHM5F9GEEJBZEY</t>
+        </is>
+      </c>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="n"/>
+      <c r="Z480" s="2" t="n"/>
+      <c r="AA480" s="2" t="n"/>
+      <c r="AB480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/mfiya-printed-men-waistcoat/p/itmd766fb57a4f1e?pid=WSCHM5F9GEEJBZEY</t>
+        </is>
+      </c>
+      <c r="AC480" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD480" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="1">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>OrientCreations</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>OrientCreations</t>
+        </is>
+      </c>
+      <c r="C481" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D481" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G481" s="5" t="n"/>
+      <c r="H481" s="6" t="n"/>
+      <c r="I481" s="5" t="n"/>
+      <c r="J481" s="6" t="n"/>
+      <c r="K481" s="6" t="n"/>
+      <c r="L481" s="6" t="n"/>
+      <c r="M481" s="5" t="n"/>
+      <c r="N481" s="5" t="n"/>
+      <c r="O481" s="5" t="n"/>
+      <c r="P481" s="5" t="n"/>
+      <c r="Q481" s="6" t="n"/>
+      <c r="R481" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S481" s="5" t="n"/>
+      <c r="T481" s="6" t="n"/>
+      <c r="U481" s="6" t="n"/>
+      <c r="V481" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/apkr-solid-men-waistcoat/p/itm71fbda620d081?pid=WSCGYDS9GCYRUSCY</t>
+        </is>
+      </c>
+      <c r="X481" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y481" s="5" t="n"/>
+      <c r="Z481" s="5" t="n"/>
+      <c r="AA481" s="5" t="n"/>
+      <c r="AB481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/apkr-solid-men-waistcoat/p/itm71fbda620d081?pid=WSCGYDS9GCYRUSCY</t>
+        </is>
+      </c>
+      <c r="AC481" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD481" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="22" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Aestheticapparels</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>Aestheticapparels</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D482" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="n"/>
+      <c r="H482" s="3" t="n"/>
+      <c r="I482" s="2" t="n"/>
+      <c r="J482" s="3" t="n"/>
+      <c r="K482" s="3" t="n"/>
+      <c r="L482" s="3" t="n"/>
+      <c r="M482" s="2" t="n"/>
+      <c r="N482" s="2" t="n"/>
+      <c r="O482" s="2" t="n"/>
+      <c r="P482" s="2" t="n"/>
+      <c r="Q482" s="3" t="n"/>
+      <c r="R482" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S482" s="2" t="n"/>
+      <c r="T482" s="3" t="n"/>
+      <c r="U482" s="3" t="n"/>
+      <c r="V482" s="3" t="n"/>
+      <c r="W482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/asthetic-solid-men-waistcoat/p/itm8b9588fb57c5d?pid=WSCHPHNQT2DGVAZK</t>
+        </is>
+      </c>
+      <c r="X482" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y482" s="2" t="n"/>
+      <c r="Z482" s="2" t="n"/>
+      <c r="AA482" s="2" t="n"/>
+      <c r="AB482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/asthetic-solid-men-waistcoat/p/itm8b9588fb57c5d?pid=WSCHPHNQT2DGVAZK</t>
+        </is>
+      </c>
+      <c r="AC482" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD482" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="22" customHeight="1">
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>naryantraders</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>naryantraders</t>
+        </is>
+      </c>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E483" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G483" s="5" t="n"/>
+      <c r="H483" s="6" t="n"/>
+      <c r="I483" s="5" t="n"/>
+      <c r="J483" s="6" t="n"/>
+      <c r="K483" s="6" t="n"/>
+      <c r="L483" s="6" t="n"/>
+      <c r="M483" s="5" t="n"/>
+      <c r="N483" s="5" t="n"/>
+      <c r="O483" s="5" t="n"/>
+      <c r="P483" s="5" t="n"/>
+      <c r="Q483" s="6" t="n"/>
+      <c r="R483" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S483" s="5" t="n"/>
+      <c r="T483" s="6" t="n"/>
+      <c r="U483" s="6" t="n"/>
+      <c r="V483" s="6" t="n"/>
+      <c r="W483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tinz-solid-women-waistcoat/p/itm4645b43ee1733?pid=WSCHZZNEM7WRQFPX</t>
+        </is>
+      </c>
+      <c r="X483" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y483" s="5" t="n"/>
+      <c r="Z483" s="5" t="n"/>
+      <c r="AA483" s="5" t="n"/>
+      <c r="AB483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tinz-solid-women-waistcoat/p/itm4645b43ee1733?pid=WSCHZZNEM7WRQFPX</t>
+        </is>
+      </c>
+      <c r="AC483" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD483" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="22" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>MeethuCreations</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>MeethuCreations</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D484" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="n"/>
+      <c r="H484" s="3" t="n"/>
+      <c r="I484" s="2" t="n"/>
+      <c r="J484" s="3" t="n"/>
+      <c r="K484" s="3" t="n"/>
+      <c r="L484" s="3" t="n"/>
+      <c r="M484" s="2" t="n"/>
+      <c r="N484" s="2" t="n"/>
+      <c r="O484" s="2" t="n"/>
+      <c r="P484" s="2" t="n"/>
+      <c r="Q484" s="3" t="n"/>
+      <c r="R484" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S484" s="2" t="n"/>
+      <c r="T484" s="3" t="n"/>
+      <c r="U484" s="3" t="n"/>
+      <c r="V484" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/atly-solid-men-waistcoat/p/itmb53645ebaa828?pid=WSCGWFDYYQTXQCUE</t>
+        </is>
+      </c>
+      <c r="X484" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y484" s="2" t="n"/>
+      <c r="Z484" s="2" t="n"/>
+      <c r="AA484" s="2" t="n"/>
+      <c r="AB484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/atly-solid-men-waistcoat/p/itmb53645ebaa828?pid=WSCGWFDYYQTXQCUE</t>
+        </is>
+      </c>
+      <c r="AC484" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD484" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="22" customHeight="1">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>Tribaltrancefashion</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>Tribaltrancefashion</t>
+        </is>
+      </c>
+      <c r="C485" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D485" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E485" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G485" s="5" t="n"/>
+      <c r="H485" s="6" t="n"/>
+      <c r="I485" s="5" t="n"/>
+      <c r="J485" s="6" t="n"/>
+      <c r="K485" s="6" t="n"/>
+      <c r="L485" s="6" t="n"/>
+      <c r="M485" s="5" t="n"/>
+      <c r="N485" s="5" t="n"/>
+      <c r="O485" s="5" t="n"/>
+      <c r="P485" s="5" t="n"/>
+      <c r="Q485" s="6" t="n"/>
+      <c r="R485" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S485" s="5" t="n"/>
+      <c r="T485" s="6" t="n"/>
+      <c r="U485" s="6" t="n"/>
+      <c r="V485" s="6" t="n"/>
+      <c r="W485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tribal-embroidered-men-waistcoat/p/itm962d98f53c62a?pid=WSCHHR48EUBWGYVU</t>
+        </is>
+      </c>
+      <c r="X485" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y485" s="5" t="n"/>
+      <c r="Z485" s="5" t="n"/>
+      <c r="AA485" s="5" t="n"/>
+      <c r="AB485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tribal-embroidered-men-waistcoat/p/itm962d98f53c62a?pid=WSCHHR48EUBWGYVU</t>
+        </is>
+      </c>
+      <c r="AC485" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD485" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="22" customHeight="1">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>BBenEnterprises</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>BBenEnterprises</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D486" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="n"/>
+      <c r="H486" s="3" t="n"/>
+      <c r="I486" s="2" t="n"/>
+      <c r="J486" s="3" t="n"/>
+      <c r="K486" s="3" t="n"/>
+      <c r="L486" s="3" t="n"/>
+      <c r="M486" s="2" t="n"/>
+      <c r="N486" s="2" t="n"/>
+      <c r="O486" s="2" t="n"/>
+      <c r="P486" s="2" t="n"/>
+      <c r="Q486" s="3" t="n"/>
+      <c r="R486" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S486" s="2" t="n"/>
+      <c r="T486" s="3" t="n"/>
+      <c r="U486" s="3" t="n"/>
+      <c r="V486" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/trend-tide-solid-men-waistcoat/p/itm114bc02a69f82?pid=WSCHCZQPZAZYGJ2H</t>
+        </is>
+      </c>
+      <c r="X486" s="2" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y486" s="2" t="n"/>
+      <c r="Z486" s="2" t="n"/>
+      <c r="AA486" s="2" t="n"/>
+      <c r="AB486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/trend-tide-solid-men-waistcoat/p/itm114bc02a69f82?pid=WSCHCZQPZAZYGJ2H</t>
+        </is>
+      </c>
+      <c r="AC486" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD486" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="22" customHeight="1">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>KHADISTYLE</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>KHADISTYLE</t>
+        </is>
+      </c>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D487" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="G487" s="5" t="n"/>
+      <c r="H487" s="6" t="n"/>
+      <c r="I487" s="5" t="n"/>
+      <c r="J487" s="6" t="n"/>
+      <c r="K487" s="6" t="n"/>
+      <c r="L487" s="6" t="n"/>
+      <c r="M487" s="5" t="n"/>
+      <c r="N487" s="5" t="n"/>
+      <c r="O487" s="5" t="n"/>
+      <c r="P487" s="5" t="n"/>
+      <c r="Q487" s="6" t="n"/>
+      <c r="R487" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S487" s="5" t="n"/>
+      <c r="T487" s="6" t="n"/>
+      <c r="U487" s="6" t="n"/>
+      <c r="V487" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/w-s-textile-checkered-men-waistcoat/p/itm39650890f6402?pid=WSCHF7JFFSDDSGY5</t>
+        </is>
+      </c>
+      <c r="X487" s="5" t="inlineStr">
+        <is>
+          <t>Waistcoats</t>
+        </is>
+      </c>
+      <c r="Y487" s="5" t="n"/>
+      <c r="Z487" s="5" t="n"/>
+      <c r="AA487" s="5" t="n"/>
+      <c r="AB487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/w-s-textile-checkered-men-waistcoat/p/itm39650890f6402?pid=WSCHF7JFFSDDSGY5</t>
+        </is>
+      </c>
+      <c r="AC487" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD487" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="22" customHeight="1">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>ABCGARMENTS</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>ABCGARMENTS</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D488" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="n"/>
+      <c r="H488" s="3" t="n"/>
+      <c r="I488" s="2" t="n"/>
+      <c r="J488" s="3" t="n"/>
+      <c r="K488" s="3" t="n"/>
+      <c r="L488" s="3" t="n"/>
+      <c r="M488" s="2" t="n"/>
+      <c r="N488" s="2" t="n"/>
+      <c r="O488" s="2" t="n"/>
+      <c r="P488" s="2" t="n"/>
+      <c r="Q488" s="3" t="n"/>
+      <c r="R488" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S488" s="2" t="n"/>
+      <c r="T488" s="3" t="n"/>
+      <c r="U488" s="3" t="n"/>
+      <c r="V488" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/abc-garments-solid-single-breasted-casual-men-blazer/p/itm0fb0e6dab3f98?pid=BZRGK5X6DKPPG9HH</t>
+        </is>
+      </c>
+      <c r="X488" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y488" s="2" t="n"/>
+      <c r="Z488" s="2" t="n"/>
+      <c r="AA488" s="2" t="n"/>
+      <c r="AB488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/abc-garments-solid-single-breasted-casual-men-blazer/p/itm0fb0e6dab3f98?pid=BZRGK5X6DKPPG9HH</t>
+        </is>
+      </c>
+      <c r="AC488" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD488" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="22" customHeight="1">
+      <c r="A489" s="5" t="inlineStr">
+        <is>
+          <t>JSRSENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>JSRSENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C489" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D489" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G489" s="5" t="n"/>
+      <c r="H489" s="6" t="n"/>
+      <c r="I489" s="5" t="n"/>
+      <c r="J489" s="6" t="n"/>
+      <c r="K489" s="6" t="n"/>
+      <c r="L489" s="6" t="n"/>
+      <c r="M489" s="5" t="n"/>
+      <c r="N489" s="5" t="n"/>
+      <c r="O489" s="5" t="n"/>
+      <c r="P489" s="5" t="n"/>
+      <c r="Q489" s="6" t="n"/>
+      <c r="R489" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S489" s="5" t="n"/>
+      <c r="T489" s="6" t="n"/>
+      <c r="U489" s="6" t="n"/>
+      <c r="V489" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fivefeb-solid-single-breasted-wedding-formal-casual-men-blazer/p/itm94d496def7732?pid=BZRGZ7R6VDGAJEFN</t>
+        </is>
+      </c>
+      <c r="X489" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y489" s="5" t="n"/>
+      <c r="Z489" s="5" t="n"/>
+      <c r="AA489" s="5" t="n"/>
+      <c r="AB489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fivefeb-solid-single-breasted-wedding-formal-casual-men-blazer/p/itm94d496def7732?pid=BZRGZ7R6VDGAJEFN</t>
+        </is>
+      </c>
+      <c r="AC489" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD489" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="22" customHeight="1">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>TAHVODESIGNSANDPRODUCTIONS</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>TAHVODESIGNSANDPRODUCTIONS</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D490" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="n"/>
+      <c r="H490" s="3" t="n"/>
+      <c r="I490" s="2" t="n"/>
+      <c r="J490" s="3" t="n"/>
+      <c r="K490" s="3" t="n"/>
+      <c r="L490" s="3" t="n"/>
+      <c r="M490" s="2" t="n"/>
+      <c r="N490" s="2" t="n"/>
+      <c r="O490" s="2" t="n"/>
+      <c r="P490" s="2" t="n"/>
+      <c r="Q490" s="3" t="n"/>
+      <c r="R490" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S490" s="2" t="n"/>
+      <c r="T490" s="3" t="n"/>
+      <c r="U490" s="3" t="n"/>
+      <c r="V490" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tahvo-solid-single-breasted-casual-men-blazer/p/itm99eb57135cecd?pid=BZRGB6D5M6ABBGHC</t>
+        </is>
+      </c>
+      <c r="X490" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y490" s="2" t="n"/>
+      <c r="Z490" s="2" t="n"/>
+      <c r="AA490" s="2" t="n"/>
+      <c r="AB490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tahvo-solid-single-breasted-casual-men-blazer/p/itm99eb57135cecd?pid=BZRGB6D5M6ABBGHC</t>
+        </is>
+      </c>
+      <c r="AC490" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD490" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="22" customHeight="1">
+      <c r="A491" s="5" t="inlineStr">
+        <is>
+          <t>ANUSHKAGARMENTSTORE</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>ANUSHKAGARMENTSTORE</t>
+        </is>
+      </c>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D491" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E491" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G491" s="5" t="n"/>
+      <c r="H491" s="6" t="n"/>
+      <c r="I491" s="5" t="n"/>
+      <c r="J491" s="6" t="n"/>
+      <c r="K491" s="6" t="n"/>
+      <c r="L491" s="6" t="n"/>
+      <c r="M491" s="5" t="n"/>
+      <c r="N491" s="5" t="n"/>
+      <c r="O491" s="5" t="n"/>
+      <c r="P491" s="5" t="n"/>
+      <c r="Q491" s="6" t="n"/>
+      <c r="R491" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S491" s="5" t="n"/>
+      <c r="T491" s="6" t="n"/>
+      <c r="U491" s="6" t="n"/>
+      <c r="V491" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/humjoli-mens-wear-solid-bandhgala-casual-formal-party-festive-wedding-men-blazer/p/itm8162afa35e45e?pid=BZRHC4H7XAMK7G53</t>
+        </is>
+      </c>
+      <c r="X491" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y491" s="5" t="n"/>
+      <c r="Z491" s="5" t="n"/>
+      <c r="AA491" s="5" t="n"/>
+      <c r="AB491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/humjoli-mens-wear-solid-bandhgala-casual-formal-party-festive-wedding-men-blazer/p/itm8162afa35e45e?pid=BZRHC4H7XAMK7G53</t>
+        </is>
+      </c>
+      <c r="AC491" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD491" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="22" customHeight="1">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>SagarFabrication</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>SagarFabrication</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D492" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="n"/>
+      <c r="H492" s="3" t="n"/>
+      <c r="I492" s="2" t="n"/>
+      <c r="J492" s="3" t="n"/>
+      <c r="K492" s="3" t="n"/>
+      <c r="L492" s="3" t="n"/>
+      <c r="M492" s="2" t="n"/>
+      <c r="N492" s="2" t="n"/>
+      <c r="O492" s="2" t="n"/>
+      <c r="P492" s="2" t="n"/>
+      <c r="Q492" s="3" t="n"/>
+      <c r="R492" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S492" s="2" t="n"/>
+      <c r="T492" s="3" t="n"/>
+      <c r="U492" s="3" t="n"/>
+      <c r="V492" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cloflix-full-sleeve-striped-men-jacket/p/itm737a72c614a5b?pid=JCKG8FYEMZJVDCZT</t>
+        </is>
+      </c>
+      <c r="X492" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y492" s="2" t="n"/>
+      <c r="Z492" s="2" t="n"/>
+      <c r="AA492" s="2" t="n"/>
+      <c r="AB492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cloflix-full-sleeve-striped-men-jacket/p/itm737a72c614a5b?pid=JCKG8FYEMZJVDCZT</t>
+        </is>
+      </c>
+      <c r="AC492" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD492" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="22" customHeight="1">
+      <c r="A493" s="5" t="inlineStr">
+        <is>
+          <t>sunrisetailors</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>sunrisetailors</t>
+        </is>
+      </c>
+      <c r="C493" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D493" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E493" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G493" s="5" t="n"/>
+      <c r="H493" s="6" t="n"/>
+      <c r="I493" s="5" t="n"/>
+      <c r="J493" s="6" t="n"/>
+      <c r="K493" s="6" t="n"/>
+      <c r="L493" s="6" t="n"/>
+      <c r="M493" s="5" t="n"/>
+      <c r="N493" s="5" t="n"/>
+      <c r="O493" s="5" t="n"/>
+      <c r="P493" s="5" t="n"/>
+      <c r="Q493" s="6" t="n"/>
+      <c r="R493" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S493" s="5" t="n"/>
+      <c r="T493" s="6" t="n"/>
+      <c r="U493" s="6" t="n"/>
+      <c r="V493" s="6" t="n"/>
+      <c r="W493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sunrisefashion-jodhpuri-suit-solid-men/p/itm61f57ee56239a?pid=SUIHQH2WGPDZJQF3</t>
+        </is>
+      </c>
+      <c r="X493" s="5" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y493" s="5" t="n"/>
+      <c r="Z493" s="5" t="n"/>
+      <c r="AA493" s="5" t="n"/>
+      <c r="AB493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sunrisefashion-jodhpuri-suit-solid-men/p/itm61f57ee56239a?pid=SUIHQH2WGPDZJQF3</t>
+        </is>
+      </c>
+      <c r="AC493" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD493" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="22" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>R K Design</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>R K Design</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D494" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="n"/>
+      <c r="H494" s="3" t="n"/>
+      <c r="I494" s="2" t="n"/>
+      <c r="J494" s="3" t="n"/>
+      <c r="K494" s="3" t="n"/>
+      <c r="L494" s="3" t="n"/>
+      <c r="M494" s="2" t="n"/>
+      <c r="N494" s="2" t="n"/>
+      <c r="O494" s="2" t="n"/>
+      <c r="P494" s="2" t="n"/>
+      <c r="Q494" s="3" t="n"/>
+      <c r="R494" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S494" s="2" t="n"/>
+      <c r="T494" s="3" t="n"/>
+      <c r="U494" s="3" t="n"/>
+      <c r="V494" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/print-cultr-solid-single-breasted-festive-wedding-men-blazer/p/itm4aeb901fac176?pid=BZRGS8GGZZVZGMHS</t>
+        </is>
+      </c>
+      <c r="X494" s="2" t="inlineStr">
+        <is>
+          <t>Suit Jackets</t>
+        </is>
+      </c>
+      <c r="Y494" s="2" t="n"/>
+      <c r="Z494" s="2" t="n"/>
+      <c r="AA494" s="2" t="n"/>
+      <c r="AB494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/print-cultr-solid-single-breasted-festive-wedding-men-blazer/p/itm4aeb901fac176?pid=BZRGS8GGZZVZGMHS</t>
+        </is>
+      </c>
+      <c r="AC494" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD494" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="22" customHeight="1">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>ShreeRamkrishnaFab</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>ShreeRamkrishnaFab</t>
+        </is>
+      </c>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D495" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G495" s="5" t="n"/>
+      <c r="H495" s="6" t="n"/>
+      <c r="I495" s="5" t="n"/>
+      <c r="J495" s="6" t="n"/>
+      <c r="K495" s="6" t="n"/>
+      <c r="L495" s="6" t="n"/>
+      <c r="M495" s="5" t="n"/>
+      <c r="N495" s="5" t="n"/>
+      <c r="O495" s="5" t="n"/>
+      <c r="P495" s="5" t="n"/>
+      <c r="Q495" s="6" t="n"/>
+      <c r="R495" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S495" s="5" t="n"/>
+      <c r="T495" s="6" t="n"/>
+      <c r="U495" s="6" t="n"/>
+      <c r="V495" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/shree-ramkrishna-fab-embroidered-kurta-trouser-pant-dupatta-set/p/itmb153bbc1a789a?pid=SWDHHZQ7KCNFUGZZ</t>
+        </is>
+      </c>
+      <c r="X495" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y495" s="5" t="n"/>
+      <c r="Z495" s="5" t="n"/>
+      <c r="AA495" s="5" t="n"/>
+      <c r="AB495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/shree-ramkrishna-fab-embroidered-kurta-trouser-pant-dupatta-set/p/itmb153bbc1a789a?pid=SWDHHZQ7KCNFUGZZ</t>
+        </is>
+      </c>
+      <c r="AC495" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD495" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="22" customHeight="1">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>KridhaImpex</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>KridhaImpex</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D496" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="n"/>
+      <c r="H496" s="3" t="n"/>
+      <c r="I496" s="2" t="n"/>
+      <c r="J496" s="3" t="n"/>
+      <c r="K496" s="3" t="n"/>
+      <c r="L496" s="3" t="n"/>
+      <c r="M496" s="2" t="n"/>
+      <c r="N496" s="2" t="n"/>
+      <c r="O496" s="2" t="n"/>
+      <c r="P496" s="2" t="n"/>
+      <c r="Q496" s="3" t="n"/>
+      <c r="R496" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S496" s="2" t="n"/>
+      <c r="T496" s="3" t="n"/>
+      <c r="U496" s="3" t="n"/>
+      <c r="V496" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/angira-jaipur-women-kurta-pant-set/p/itm1f272a29e3fbc?pid=ETHGMDKAZYHHCYSG</t>
+        </is>
+      </c>
+      <c r="X496" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y496" s="2" t="n"/>
+      <c r="Z496" s="2" t="n"/>
+      <c r="AA496" s="2" t="n"/>
+      <c r="AB496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/angira-jaipur-women-kurta-pant-set/p/itm1f272a29e3fbc?pid=ETHGMDKAZYHHCYSG</t>
+        </is>
+      </c>
+      <c r="AC496" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD496" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="22" customHeight="1">
+      <c r="A497" s="5" t="inlineStr">
+        <is>
+          <t>RadhaRaniCollectiion</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>RadhaRaniCollectiion</t>
+        </is>
+      </c>
+      <c r="C497" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D497" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G497" s="5" t="n"/>
+      <c r="H497" s="6" t="n"/>
+      <c r="I497" s="5" t="n"/>
+      <c r="J497" s="6" t="n"/>
+      <c r="K497" s="6" t="n"/>
+      <c r="L497" s="6" t="n"/>
+      <c r="M497" s="5" t="n"/>
+      <c r="N497" s="5" t="n"/>
+      <c r="O497" s="5" t="n"/>
+      <c r="P497" s="5" t="n"/>
+      <c r="Q497" s="6" t="n"/>
+      <c r="R497" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S497" s="5" t="n"/>
+      <c r="T497" s="6" t="n"/>
+      <c r="U497" s="6" t="n"/>
+      <c r="V497" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/keya-designs-embroidered-kurta-trouser-pant-dupatta-set/p/itm3a3b402922c60?pid=SWDHZE8MSZQ2WQHG</t>
+        </is>
+      </c>
+      <c r="X497" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y497" s="5" t="n"/>
+      <c r="Z497" s="5" t="n"/>
+      <c r="AA497" s="5" t="n"/>
+      <c r="AB497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/keya-designs-embroidered-kurta-trouser-pant-dupatta-set/p/itm3a3b402922c60?pid=SWDHZE8MSZQ2WQHG</t>
+        </is>
+      </c>
+      <c r="AC497" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD497" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="22" customHeight="1">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>ZenziorBrandTechnology</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>ZenziorBrandTechnology</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D498" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="n"/>
+      <c r="H498" s="3" t="n"/>
+      <c r="I498" s="2" t="n"/>
+      <c r="J498" s="3" t="n"/>
+      <c r="K498" s="3" t="n"/>
+      <c r="L498" s="3" t="n"/>
+      <c r="M498" s="2" t="n"/>
+      <c r="N498" s="2" t="n"/>
+      <c r="O498" s="2" t="n"/>
+      <c r="P498" s="2" t="n"/>
+      <c r="Q498" s="3" t="n"/>
+      <c r="R498" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S498" s="2" t="n"/>
+      <c r="T498" s="3" t="n"/>
+      <c r="U498" s="3" t="n"/>
+      <c r="V498" s="3" t="n"/>
+      <c r="W498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/indo-era-women-kurta-pant-dupatta-set/p/itm6397e30ad49d4?pid=ETHHJH37QGHGYJWW</t>
+        </is>
+      </c>
+      <c r="X498" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y498" s="2" t="n"/>
+      <c r="Z498" s="2" t="n"/>
+      <c r="AA498" s="2" t="n"/>
+      <c r="AB498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/indo-era-women-kurta-pant-dupatta-set/p/itm6397e30ad49d4?pid=ETHHJH37QGHGYJWW</t>
+        </is>
+      </c>
+      <c r="AC498" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD498" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="22" customHeight="1">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>Shree04</t>
+        </is>
+      </c>
+      <c r="B499" s="5" t="inlineStr">
+        <is>
+          <t>Shree04</t>
+        </is>
+      </c>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D499" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E499" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G499" s="5" t="n"/>
+      <c r="H499" s="6" t="n"/>
+      <c r="I499" s="5" t="n"/>
+      <c r="J499" s="6" t="n"/>
+      <c r="K499" s="6" t="n"/>
+      <c r="L499" s="6" t="n"/>
+      <c r="M499" s="5" t="n"/>
+      <c r="N499" s="5" t="n"/>
+      <c r="O499" s="5" t="n"/>
+      <c r="P499" s="5" t="n"/>
+      <c r="Q499" s="6" t="n"/>
+      <c r="R499" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S499" s="5" t="n"/>
+      <c r="T499" s="6" t="n"/>
+      <c r="U499" s="6" t="n"/>
+      <c r="V499" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W499" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ethnickurti-printed-kurta-trouser-pant-dupatta-set/p/itm51fd725b93f73?pid=SWDHPGDQKVGBKYKV</t>
+        </is>
+      </c>
+      <c r="X499" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y499" s="5" t="n"/>
+      <c r="Z499" s="5" t="n"/>
+      <c r="AA499" s="5" t="n"/>
+      <c r="AB499" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ethnickurti-printed-kurta-trouser-pant-dupatta-set/p/itm51fd725b93f73?pid=SWDHPGDQKVGBKYKV</t>
+        </is>
+      </c>
+      <c r="AC499" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD499" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="22" customHeight="1">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>NiluTextiles</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>NiluTextiles</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D500" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="n"/>
+      <c r="H500" s="3" t="n"/>
+      <c r="I500" s="2" t="n"/>
+      <c r="J500" s="3" t="n"/>
+      <c r="K500" s="3" t="n"/>
+      <c r="L500" s="3" t="n"/>
+      <c r="M500" s="2" t="n"/>
+      <c r="N500" s="2" t="n"/>
+      <c r="O500" s="2" t="n"/>
+      <c r="P500" s="2" t="n"/>
+      <c r="Q500" s="3" t="n"/>
+      <c r="R500" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S500" s="2" t="n"/>
+      <c r="T500" s="3" t="n"/>
+      <c r="U500" s="3" t="n"/>
+      <c r="V500" s="3" t="n"/>
+      <c r="W500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nilu-textiles-embroidered-kurta-trouser-pant-dupatta-set/p/itm8b0da9dce73dd?pid=SWDHHQRANT66KCWN</t>
+        </is>
+      </c>
+      <c r="X500" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y500" s="2" t="n"/>
+      <c r="Z500" s="2" t="n"/>
+      <c r="AA500" s="2" t="n"/>
+      <c r="AB500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nilu-textiles-embroidered-kurta-trouser-pant-dupatta-set/p/itm8b0da9dce73dd?pid=SWDHHQRANT66KCWN</t>
+        </is>
+      </c>
+      <c r="AC500" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD500" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="5" t="inlineStr">
+        <is>
+          <t>Jaipurfashionfactory</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="inlineStr">
+        <is>
+          <t>Jaipurfashionfactory</t>
+        </is>
+      </c>
+      <c r="C501" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D501" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G501" s="5" t="n"/>
+      <c r="H501" s="6" t="n"/>
+      <c r="I501" s="5" t="n"/>
+      <c r="J501" s="6" t="n"/>
+      <c r="K501" s="6" t="n"/>
+      <c r="L501" s="6" t="n"/>
+      <c r="M501" s="5" t="n"/>
+      <c r="N501" s="5" t="n"/>
+      <c r="O501" s="5" t="n"/>
+      <c r="P501" s="5" t="n"/>
+      <c r="Q501" s="6" t="n"/>
+      <c r="R501" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S501" s="5" t="n"/>
+      <c r="T501" s="6" t="n"/>
+      <c r="U501" s="6" t="n"/>
+      <c r="V501" s="6" t="n"/>
+      <c r="W501" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jaipur-fashion-factory-embroidered-kurta-trouser-pant-dupatta-set/p/itm64a4ae9628593?pid=SWDHZHZ4GD3ZXQGW</t>
+        </is>
+      </c>
+      <c r="X501" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y501" s="5" t="n"/>
+      <c r="Z501" s="5" t="n"/>
+      <c r="AA501" s="5" t="n"/>
+      <c r="AB501" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jaipur-fashion-factory-embroidered-kurta-trouser-pant-dupatta-set/p/itm64a4ae9628593?pid=SWDHZHZ4GD3ZXQGW</t>
+        </is>
+      </c>
+      <c r="AC501" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD501" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="22" customHeight="1">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>AAKARCREATION</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>AAKARCREATION</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D502" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="n"/>
+      <c r="H502" s="3" t="n"/>
+      <c r="I502" s="2" t="n"/>
+      <c r="J502" s="3" t="n"/>
+      <c r="K502" s="3" t="n"/>
+      <c r="L502" s="3" t="n"/>
+      <c r="M502" s="2" t="n"/>
+      <c r="N502" s="2" t="n"/>
+      <c r="O502" s="2" t="n"/>
+      <c r="P502" s="2" t="n"/>
+      <c r="Q502" s="3" t="n"/>
+      <c r="R502" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S502" s="2" t="n"/>
+      <c r="T502" s="3" t="n"/>
+      <c r="U502" s="3" t="n"/>
+      <c r="V502" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/denigma-suit-solid-men/p/itmc853a604854ff?pid=SUIHNYPPZZNPFYNA</t>
+        </is>
+      </c>
+      <c r="X502" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y502" s="2" t="n"/>
+      <c r="Z502" s="2" t="n"/>
+      <c r="AA502" s="2" t="n"/>
+      <c r="AB502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/denigma-suit-solid-men/p/itmc853a604854ff?pid=SUIHNYPPZZNPFYNA</t>
+        </is>
+      </c>
+      <c r="AC502" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD502" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="22" customHeight="1">
+      <c r="A503" s="5" t="inlineStr">
+        <is>
+          <t>MISHVACREATION12</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>MISHVACREATION12</t>
+        </is>
+      </c>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D503" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E503" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G503" s="5" t="n"/>
+      <c r="H503" s="6" t="n"/>
+      <c r="I503" s="5" t="n"/>
+      <c r="J503" s="6" t="n"/>
+      <c r="K503" s="6" t="n"/>
+      <c r="L503" s="6" t="n"/>
+      <c r="M503" s="5" t="n"/>
+      <c r="N503" s="5" t="n"/>
+      <c r="O503" s="5" t="n"/>
+      <c r="P503" s="5" t="n"/>
+      <c r="Q503" s="6" t="n"/>
+      <c r="R503" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S503" s="5" t="n"/>
+      <c r="T503" s="6" t="n"/>
+      <c r="U503" s="6" t="n"/>
+      <c r="V503" s="6" t="n"/>
+      <c r="W503" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/eeloo-embroidered-kurta-trouser-pant-dupatta-set/p/itmb425cf3a75f83?pid=SWDHJXFJEXBAN2XY</t>
+        </is>
+      </c>
+      <c r="X503" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y503" s="5" t="n"/>
+      <c r="Z503" s="5" t="n"/>
+      <c r="AA503" s="5" t="n"/>
+      <c r="AB503" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/eeloo-embroidered-kurta-trouser-pant-dupatta-set/p/itmb425cf3a75f83?pid=SWDHJXFJEXBAN2XY</t>
+        </is>
+      </c>
+      <c r="AC503" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD503" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="22" customHeight="1">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>KLIKNIZ</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>KLIKNIZ</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D504" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="n"/>
+      <c r="H504" s="3" t="n"/>
+      <c r="I504" s="2" t="n"/>
+      <c r="J504" s="3" t="n"/>
+      <c r="K504" s="3" t="n"/>
+      <c r="L504" s="3" t="n"/>
+      <c r="M504" s="2" t="n"/>
+      <c r="N504" s="2" t="n"/>
+      <c r="O504" s="2" t="n"/>
+      <c r="P504" s="2" t="n"/>
+      <c r="Q504" s="3" t="n"/>
+      <c r="R504" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S504" s="2" t="n"/>
+      <c r="T504" s="3" t="n"/>
+      <c r="U504" s="3" t="n"/>
+      <c r="V504" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/klikniz-embroidered-kurta-trouser-pant-dupatta-set/p/itm7dd9d1e9a3c91?pid=SWDHZFZJGRMUGNGK</t>
+        </is>
+      </c>
+      <c r="X504" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y504" s="2" t="n"/>
+      <c r="Z504" s="2" t="n"/>
+      <c r="AA504" s="2" t="n"/>
+      <c r="AB504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/klikniz-embroidered-kurta-trouser-pant-dupatta-set/p/itm7dd9d1e9a3c91?pid=SWDHZFZJGRMUGNGK</t>
+        </is>
+      </c>
+      <c r="AC504" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD504" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="22" customHeight="1">
+      <c r="A505" s="5" t="inlineStr">
+        <is>
+          <t>Loomscart</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="inlineStr">
+        <is>
+          <t>Loomscart</t>
+        </is>
+      </c>
+      <c r="C505" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D505" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E505" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G505" s="5" t="n"/>
+      <c r="H505" s="6" t="n"/>
+      <c r="I505" s="5" t="n"/>
+      <c r="J505" s="6" t="n"/>
+      <c r="K505" s="6" t="n"/>
+      <c r="L505" s="6" t="n"/>
+      <c r="M505" s="5" t="n"/>
+      <c r="N505" s="5" t="n"/>
+      <c r="O505" s="5" t="n"/>
+      <c r="P505" s="5" t="n"/>
+      <c r="Q505" s="6" t="n"/>
+      <c r="R505" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S505" s="5" t="n"/>
+      <c r="T505" s="6" t="n"/>
+      <c r="U505" s="6" t="n"/>
+      <c r="V505" s="6" t="n"/>
+      <c r="W505" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/loomscart-embroidered-kurta-trouser-pant-dupatta-set/p/itmb0c6f618d6e95?pid=SWDHQE28FHFGE6PM</t>
+        </is>
+      </c>
+      <c r="X505" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y505" s="5" t="n"/>
+      <c r="Z505" s="5" t="n"/>
+      <c r="AA505" s="5" t="n"/>
+      <c r="AB505" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/loomscart-embroidered-kurta-trouser-pant-dupatta-set/p/itmb0c6f618d6e95?pid=SWDHQE28FHFGE6PM</t>
+        </is>
+      </c>
+      <c r="AC505" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD505" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="22" customHeight="1">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Divyya</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>Divyya</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D506" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="n"/>
+      <c r="H506" s="3" t="n"/>
+      <c r="I506" s="2" t="n"/>
+      <c r="J506" s="3" t="n"/>
+      <c r="K506" s="3" t="n"/>
+      <c r="L506" s="3" t="n"/>
+      <c r="M506" s="2" t="n"/>
+      <c r="N506" s="2" t="n"/>
+      <c r="O506" s="2" t="n"/>
+      <c r="P506" s="2" t="n"/>
+      <c r="Q506" s="3" t="n"/>
+      <c r="R506" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S506" s="2" t="n"/>
+      <c r="T506" s="3" t="n"/>
+      <c r="U506" s="3" t="n"/>
+      <c r="V506" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bruno-printed-kurta-trouser-pant-dupatta-set/p/itm3e63e309c0329?pid=SWDGZYY92WKHY7ZF</t>
+        </is>
+      </c>
+      <c r="X506" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y506" s="2" t="n"/>
+      <c r="Z506" s="2" t="n"/>
+      <c r="AA506" s="2" t="n"/>
+      <c r="AB506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bruno-printed-kurta-trouser-pant-dupatta-set/p/itm3e63e309c0329?pid=SWDGZYY92WKHY7ZF</t>
+        </is>
+      </c>
+      <c r="AC506" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD506" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="22" customHeight="1">
+      <c r="A507" s="5" t="inlineStr">
+        <is>
+          <t>VFASHIONNF</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="inlineStr">
+        <is>
+          <t>VFASHIONNF</t>
+        </is>
+      </c>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D507" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E507" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G507" s="5" t="n"/>
+      <c r="H507" s="6" t="n"/>
+      <c r="I507" s="5" t="n"/>
+      <c r="J507" s="6" t="n"/>
+      <c r="K507" s="6" t="n"/>
+      <c r="L507" s="6" t="n"/>
+      <c r="M507" s="5" t="n"/>
+      <c r="N507" s="5" t="n"/>
+      <c r="O507" s="5" t="n"/>
+      <c r="P507" s="5" t="n"/>
+      <c r="Q507" s="6" t="n"/>
+      <c r="R507" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S507" s="5" t="n"/>
+      <c r="T507" s="6" t="n"/>
+      <c r="U507" s="6" t="n"/>
+      <c r="V507" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W507" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jainica-embroidered-kurta-trouser-pant-dupatta-set/p/itm1a7c1dbeab72f?pid=SWDHPP8U2Y9DZDC6</t>
+        </is>
+      </c>
+      <c r="X507" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y507" s="5" t="n"/>
+      <c r="Z507" s="5" t="n"/>
+      <c r="AA507" s="5" t="n"/>
+      <c r="AB507" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jainica-embroidered-kurta-trouser-pant-dupatta-set/p/itm1a7c1dbeab72f?pid=SWDHPP8U2Y9DZDC6</t>
+        </is>
+      </c>
+      <c r="AC507" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD507" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="22" customHeight="1">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>kurtiesforcuties</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>kurtiesforcuties</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D508" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="n"/>
+      <c r="H508" s="3" t="n"/>
+      <c r="I508" s="2" t="n"/>
+      <c r="J508" s="3" t="n"/>
+      <c r="K508" s="3" t="n"/>
+      <c r="L508" s="3" t="n"/>
+      <c r="M508" s="2" t="n"/>
+      <c r="N508" s="2" t="n"/>
+      <c r="O508" s="2" t="n"/>
+      <c r="P508" s="2" t="n"/>
+      <c r="Q508" s="3" t="n"/>
+      <c r="R508" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S508" s="2" t="n"/>
+      <c r="T508" s="3" t="n"/>
+      <c r="U508" s="3" t="n"/>
+      <c r="V508" s="3" t="n"/>
+      <c r="W508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/shreeji-embroidered-kurta-trouser-pant-dupatta-set/p/itmf3119a187c9e3?pid=SWDHQEWHUP5YFKHU</t>
+        </is>
+      </c>
+      <c r="X508" s="2" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y508" s="2" t="n"/>
+      <c r="Z508" s="2" t="n"/>
+      <c r="AA508" s="2" t="n"/>
+      <c r="AB508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/shreeji-embroidered-kurta-trouser-pant-dupatta-set/p/itmf3119a187c9e3?pid=SWDHQEWHUP5YFKHU</t>
+        </is>
+      </c>
+      <c r="AC508" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD508" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="22" customHeight="1">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>anushansa</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>anushansa</t>
+        </is>
+      </c>
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D509" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="n"/>
+      <c r="H509" s="6" t="n"/>
+      <c r="I509" s="5" t="n"/>
+      <c r="J509" s="6" t="n"/>
+      <c r="K509" s="6" t="n"/>
+      <c r="L509" s="6" t="n"/>
+      <c r="M509" s="5" t="n"/>
+      <c r="N509" s="5" t="n"/>
+      <c r="O509" s="5" t="n"/>
+      <c r="P509" s="5" t="n"/>
+      <c r="Q509" s="6" t="n"/>
+      <c r="R509" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S509" s="5" t="n"/>
+      <c r="T509" s="6" t="n"/>
+      <c r="U509" s="6" t="n"/>
+      <c r="V509" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W509" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/anushansa-women-kurta-palazzo-dupatta-set/p/itmb70ef00ecbc2b?pid=ETHHJHYG2GVBRJAF</t>
+        </is>
+      </c>
+      <c r="X509" s="5" t="inlineStr">
+        <is>
+          <t>Suit Trousers</t>
+        </is>
+      </c>
+      <c r="Y509" s="5" t="n"/>
+      <c r="Z509" s="5" t="n"/>
+      <c r="AA509" s="5" t="n"/>
+      <c r="AB509" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/anushansa-women-kurta-palazzo-dupatta-set/p/itmb70ef00ecbc2b?pid=ETHHJHYG2GVBRJAF</t>
+        </is>
+      </c>
+      <c r="AC509" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD509" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>MOONXS</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>MOONXS</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D510" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="n"/>
+      <c r="H510" s="3" t="n"/>
+      <c r="I510" s="2" t="n"/>
+      <c r="J510" s="3" t="n"/>
+      <c r="K510" s="3" t="n"/>
+      <c r="L510" s="3" t="n"/>
+      <c r="M510" s="2" t="n"/>
+      <c r="N510" s="2" t="n"/>
+      <c r="O510" s="2" t="n"/>
+      <c r="P510" s="2" t="n"/>
+      <c r="Q510" s="3" t="n"/>
+      <c r="R510" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S510" s="2" t="n"/>
+      <c r="T510" s="3" t="n"/>
+      <c r="U510" s="3" t="n"/>
+      <c r="V510" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/moonxs-solid-single-breasted-wedding-men-blazer/p/itm1264cc4a1c9dd?pid=BZRHMJWQKPYAYTNU</t>
+        </is>
+      </c>
+      <c r="X510" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y510" s="2" t="n"/>
+      <c r="Z510" s="2" t="n"/>
+      <c r="AA510" s="2" t="n"/>
+      <c r="AB510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/moonxs-solid-single-breasted-wedding-men-blazer/p/itm1264cc4a1c9dd?pid=BZRHMJWQKPYAYTNU</t>
+        </is>
+      </c>
+      <c r="AC510" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD510" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="22" customHeight="1">
+      <c r="A511" s="5" t="inlineStr">
+        <is>
+          <t>ArvindLifestyleBrands</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="inlineStr">
+        <is>
+          <t>ArvindLifestyleBrands</t>
+        </is>
+      </c>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D511" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E511" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G511" s="5" t="n"/>
+      <c r="H511" s="6" t="n"/>
+      <c r="I511" s="5" t="n"/>
+      <c r="J511" s="6" t="n"/>
+      <c r="K511" s="6" t="n"/>
+      <c r="L511" s="6" t="n"/>
+      <c r="M511" s="5" t="n"/>
+      <c r="N511" s="5" t="n"/>
+      <c r="O511" s="5" t="n"/>
+      <c r="P511" s="5" t="n"/>
+      <c r="Q511" s="6" t="n"/>
+      <c r="R511" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S511" s="5" t="n"/>
+      <c r="T511" s="6" t="n"/>
+      <c r="U511" s="6" t="n"/>
+      <c r="V511" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W511" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/arrow-embroidered-single-breasted-casual-men-blazer/p/itma27c12177672a?pid=BZRHCGESRGGHVRRQ</t>
+        </is>
+      </c>
+      <c r="X511" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y511" s="5" t="n"/>
+      <c r="Z511" s="5" t="n"/>
+      <c r="AA511" s="5" t="n"/>
+      <c r="AB511" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/arrow-embroidered-single-breasted-casual-men-blazer/p/itma27c12177672a?pid=BZRHCGESRGGHVRRQ</t>
+        </is>
+      </c>
+      <c r="AC511" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD511" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="22" customHeight="1">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>ATOLimitedCompany</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>ATOLimitedCompany</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D512" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>Public Limited Company</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="n"/>
+      <c r="H512" s="3" t="n"/>
+      <c r="I512" s="2" t="n"/>
+      <c r="J512" s="3" t="n"/>
+      <c r="K512" s="3" t="n"/>
+      <c r="L512" s="3" t="n"/>
+      <c r="M512" s="2" t="n"/>
+      <c r="N512" s="2" t="n"/>
+      <c r="O512" s="2" t="n"/>
+      <c r="P512" s="2" t="n"/>
+      <c r="Q512" s="3" t="n"/>
+      <c r="R512" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S512" s="2" t="n"/>
+      <c r="T512" s="3" t="n"/>
+      <c r="U512" s="3" t="n"/>
+      <c r="V512" s="3" t="n"/>
+      <c r="W512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ato-solid-single-breasted-casual-party-festive-wedding-formal-wedding-men-blazer/p/itm267e2d19a10b2?pid=BZRHGDGBP4FJXJSY</t>
+        </is>
+      </c>
+      <c r="X512" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y512" s="2" t="n"/>
+      <c r="Z512" s="2" t="n"/>
+      <c r="AA512" s="2" t="n"/>
+      <c r="AB512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ato-solid-single-breasted-casual-party-festive-wedding-formal-wedding-men-blazer/p/itm267e2d19a10b2?pid=BZRHGDGBP4FJXJSY</t>
+        </is>
+      </c>
+      <c r="AC512" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD512" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="22" customHeight="1">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>4SILAI</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="inlineStr">
+        <is>
+          <t>4SILAI</t>
+        </is>
+      </c>
+      <c r="C513" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D513" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E513" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G513" s="5" t="n"/>
+      <c r="H513" s="6" t="n"/>
+      <c r="I513" s="5" t="n"/>
+      <c r="J513" s="6" t="n"/>
+      <c r="K513" s="6" t="n"/>
+      <c r="L513" s="6" t="n"/>
+      <c r="M513" s="5" t="n"/>
+      <c r="N513" s="5" t="n"/>
+      <c r="O513" s="5" t="n"/>
+      <c r="P513" s="5" t="n"/>
+      <c r="Q513" s="6" t="n"/>
+      <c r="R513" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S513" s="5" t="n"/>
+      <c r="T513" s="6" t="n"/>
+      <c r="U513" s="6" t="n"/>
+      <c r="V513" s="6" t="n"/>
+      <c r="W513" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/four-silai-solid-single-breasted-formal-men-blazer/p/itm10b72cad0bc59?pid=BZRHMUUYMKGUGHYX</t>
+        </is>
+      </c>
+      <c r="X513" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y513" s="5" t="n"/>
+      <c r="Z513" s="5" t="n"/>
+      <c r="AA513" s="5" t="n"/>
+      <c r="AB513" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/four-silai-solid-single-breasted-formal-men-blazer/p/itm10b72cad0bc59?pid=BZRHMUUYMKGUGHYX</t>
+        </is>
+      </c>
+      <c r="AC513" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD513" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="22" customHeight="1">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>NFNEWFASHION</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>NFNEWFASHION</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D514" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="n"/>
+      <c r="H514" s="3" t="n"/>
+      <c r="I514" s="2" t="n"/>
+      <c r="J514" s="3" t="n"/>
+      <c r="K514" s="3" t="n"/>
+      <c r="L514" s="3" t="n"/>
+      <c r="M514" s="2" t="n"/>
+      <c r="N514" s="2" t="n"/>
+      <c r="O514" s="2" t="n"/>
+      <c r="P514" s="2" t="n"/>
+      <c r="Q514" s="3" t="n"/>
+      <c r="R514" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S514" s="2" t="n"/>
+      <c r="T514" s="3" t="n"/>
+      <c r="U514" s="3" t="n"/>
+      <c r="V514" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nf-new-fashion-solid-tuxedo-style-formal-festive-wedding-party-men-blazer/p/itm8aa4e4ca9e918?pid=BZRHKH8GQHE2HFKZ</t>
+        </is>
+      </c>
+      <c r="X514" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y514" s="2" t="n"/>
+      <c r="Z514" s="2" t="n"/>
+      <c r="AA514" s="2" t="n"/>
+      <c r="AB514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/nf-new-fashion-solid-tuxedo-style-formal-festive-wedding-party-men-blazer/p/itm8aa4e4ca9e918?pid=BZRHKH8GQHE2HFKZ</t>
+        </is>
+      </c>
+      <c r="AC514" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD514" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="22" customHeight="1">
+      <c r="A515" s="5" t="inlineStr">
+        <is>
+          <t>VenusTailors</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="inlineStr">
+        <is>
+          <t>VenusTailors</t>
+        </is>
+      </c>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D515" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E515" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G515" s="5" t="n"/>
+      <c r="H515" s="6" t="n"/>
+      <c r="I515" s="5" t="n"/>
+      <c r="J515" s="6" t="n"/>
+      <c r="K515" s="6" t="n"/>
+      <c r="L515" s="6" t="n"/>
+      <c r="M515" s="5" t="n"/>
+      <c r="N515" s="5" t="n"/>
+      <c r="O515" s="5" t="n"/>
+      <c r="P515" s="5" t="n"/>
+      <c r="Q515" s="6" t="n"/>
+      <c r="R515" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S515" s="5" t="n"/>
+      <c r="T515" s="6" t="n"/>
+      <c r="U515" s="6" t="n"/>
+      <c r="V515" s="6" t="n"/>
+      <c r="W515" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/venustailors-embroidered-tuxedo-style-festive-wedding-formal-party-men-blazer/p/itm9342ecc72a04f?pid=BZRHQFRFRTGGXFGA</t>
+        </is>
+      </c>
+      <c r="X515" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y515" s="5" t="n"/>
+      <c r="Z515" s="5" t="n"/>
+      <c r="AA515" s="5" t="n"/>
+      <c r="AB515" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/venustailors-embroidered-tuxedo-style-festive-wedding-formal-party-men-blazer/p/itm9342ecc72a04f?pid=BZRHQFRFRTGGXFGA</t>
+        </is>
+      </c>
+      <c r="AC515" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD515" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="22" customHeight="1">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>RaeenMensWear03</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>RaeenMensWear03</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D516" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="n"/>
+      <c r="H516" s="3" t="n"/>
+      <c r="I516" s="2" t="n"/>
+      <c r="J516" s="3" t="n"/>
+      <c r="K516" s="3" t="n"/>
+      <c r="L516" s="3" t="n"/>
+      <c r="M516" s="2" t="n"/>
+      <c r="N516" s="2" t="n"/>
+      <c r="O516" s="2" t="n"/>
+      <c r="P516" s="2" t="n"/>
+      <c r="Q516" s="3" t="n"/>
+      <c r="R516" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S516" s="2" t="n"/>
+      <c r="T516" s="3" t="n"/>
+      <c r="U516" s="3" t="n"/>
+      <c r="V516" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/raeenmenswear-solid-tuxedo-style-casual-festive-festive-wedding-formal-party-wedding-men-blazer/p/itm726301c2ad202?pid=BZRHHXFTAVURKHGX</t>
+        </is>
+      </c>
+      <c r="X516" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y516" s="2" t="n"/>
+      <c r="Z516" s="2" t="n"/>
+      <c r="AA516" s="2" t="n"/>
+      <c r="AB516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/raeenmenswear-solid-tuxedo-style-casual-festive-festive-wedding-formal-party-wedding-men-blazer/p/itm726301c2ad202?pid=BZRHHXFTAVURKHGX</t>
+        </is>
+      </c>
+      <c r="AC516" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD516" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="22" customHeight="1">
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>BHSTYLE</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="inlineStr">
+        <is>
+          <t>BHSTYLE</t>
+        </is>
+      </c>
+      <c r="C517" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D517" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E517" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G517" s="5" t="n"/>
+      <c r="H517" s="6" t="n"/>
+      <c r="I517" s="5" t="n"/>
+      <c r="J517" s="6" t="n"/>
+      <c r="K517" s="6" t="n"/>
+      <c r="L517" s="6" t="n"/>
+      <c r="M517" s="5" t="n"/>
+      <c r="N517" s="5" t="n"/>
+      <c r="O517" s="5" t="n"/>
+      <c r="P517" s="5" t="n"/>
+      <c r="Q517" s="6" t="n"/>
+      <c r="R517" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S517" s="5" t="n"/>
+      <c r="T517" s="6" t="n"/>
+      <c r="U517" s="6" t="n"/>
+      <c r="V517" s="6" t="n"/>
+      <c r="W517" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bhstyle-solid-tuxedo-style-casual-men-blazer/p/itm294a8429aa0ab?pid=BZRH9DGYDYYVAM86</t>
+        </is>
+      </c>
+      <c r="X517" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y517" s="5" t="n"/>
+      <c r="Z517" s="5" t="n"/>
+      <c r="AA517" s="5" t="n"/>
+      <c r="AB517" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bhstyle-solid-tuxedo-style-casual-men-blazer/p/itm294a8429aa0ab?pid=BZRH9DGYDYYVAM86</t>
+        </is>
+      </c>
+      <c r="AC517" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD517" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="22" customHeight="1">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>MSNEXUSS</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>MSNEXUSS</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D518" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="n"/>
+      <c r="H518" s="3" t="n"/>
+      <c r="I518" s="2" t="n"/>
+      <c r="J518" s="3" t="n"/>
+      <c r="K518" s="3" t="n"/>
+      <c r="L518" s="3" t="n"/>
+      <c r="M518" s="2" t="n"/>
+      <c r="N518" s="2" t="n"/>
+      <c r="O518" s="2" t="n"/>
+      <c r="P518" s="2" t="n"/>
+      <c r="Q518" s="3" t="n"/>
+      <c r="R518" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S518" s="2" t="n"/>
+      <c r="T518" s="3" t="n"/>
+      <c r="U518" s="3" t="n"/>
+      <c r="V518" s="3" t="n"/>
+      <c r="W518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/msnexuss-solid-tuxedo-style-formal-men-blazer/p/itm7141d0d01f329?pid=BZRGRZMGMWGSHDMD</t>
+        </is>
+      </c>
+      <c r="X518" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedos</t>
+        </is>
+      </c>
+      <c r="Y518" s="2" t="n"/>
+      <c r="Z518" s="2" t="n"/>
+      <c r="AA518" s="2" t="n"/>
+      <c r="AB518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/msnexuss-solid-tuxedo-style-formal-men-blazer/p/itm7141d0d01f329?pid=BZRGRZMGMWGSHDMD</t>
+        </is>
+      </c>
+      <c r="AC518" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD518" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="22" customHeight="1">
+      <c r="A519" s="5" t="inlineStr">
+        <is>
+          <t>IFOXLIFESTYLE</t>
+        </is>
+      </c>
+      <c r="B519" s="5" t="inlineStr">
+        <is>
+          <t>IFOXLIFESTYLE</t>
+        </is>
+      </c>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D519" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E519" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedo Jackets</t>
+        </is>
+      </c>
+      <c r="G519" s="5" t="n"/>
+      <c r="H519" s="6" t="n"/>
+      <c r="I519" s="5" t="n"/>
+      <c r="J519" s="6" t="n"/>
+      <c r="K519" s="6" t="n"/>
+      <c r="L519" s="6" t="n"/>
+      <c r="M519" s="5" t="n"/>
+      <c r="N519" s="5" t="n"/>
+      <c r="O519" s="5" t="n"/>
+      <c r="P519" s="5" t="n"/>
+      <c r="Q519" s="6" t="n"/>
+      <c r="R519" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S519" s="5" t="n"/>
+      <c r="T519" s="6" t="n"/>
+      <c r="U519" s="6" t="n"/>
+      <c r="V519" s="6" t="n"/>
+      <c r="W519" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ifox-lifestyle-solid-single-breasted-festive-wedding-men-blazer/p/itmf927be75fae39?pid=BZRHGXWPJBAA8SEQ</t>
+        </is>
+      </c>
+      <c r="X519" s="5" t="inlineStr">
+        <is>
+          <t>Tuxedo Jackets</t>
+        </is>
+      </c>
+      <c r="Y519" s="5" t="n"/>
+      <c r="Z519" s="5" t="n"/>
+      <c r="AA519" s="5" t="n"/>
+      <c r="AB519" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ifox-lifestyle-solid-single-breasted-festive-wedding-men-blazer/p/itmf927be75fae39?pid=BZRHGXWPJBAA8SEQ</t>
+        </is>
+      </c>
+      <c r="AC519" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD519" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="22" customHeight="1">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>POOJAENTERPRISES010</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>POOJAENTERPRISES010</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D520" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedo Jackets</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="n"/>
+      <c r="H520" s="3" t="n"/>
+      <c r="I520" s="2" t="n"/>
+      <c r="J520" s="3" t="n"/>
+      <c r="K520" s="3" t="n"/>
+      <c r="L520" s="3" t="n"/>
+      <c r="M520" s="2" t="n"/>
+      <c r="N520" s="2" t="n"/>
+      <c r="O520" s="2" t="n"/>
+      <c r="P520" s="2" t="n"/>
+      <c r="Q520" s="3" t="n"/>
+      <c r="R520" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S520" s="2" t="n"/>
+      <c r="T520" s="3" t="n"/>
+      <c r="U520" s="3" t="n"/>
+      <c r="V520" s="3" t="n"/>
+      <c r="W520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fijuca-fashion-solid-single-breasted-casual-formal-party-festive-wedding-men-blazer/p/itme26968f7f3a26?pid=BZRHNT9RFT3JGGFG</t>
+        </is>
+      </c>
+      <c r="X520" s="2" t="inlineStr">
+        <is>
+          <t>Tuxedo Jackets</t>
+        </is>
+      </c>
+      <c r="Y520" s="2" t="n"/>
+      <c r="Z520" s="2" t="n"/>
+      <c r="AA520" s="2" t="n"/>
+      <c r="AB520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fijuca-fashion-solid-single-breasted-casual-formal-party-festive-wedding-men-blazer/p/itme26968f7f3a26?pid=BZRHNT9RFT3JGGFG</t>
+        </is>
+      </c>
+      <c r="AC520" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD520" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="22" customHeight="1">
+      <c r="A521" s="5" t="inlineStr">
+        <is>
+          <t>Pkenterprises009</t>
+        </is>
+      </c>
+      <c r="B521" s="5" t="inlineStr">
+        <is>
+          <t>Pkenterprises009</t>
+        </is>
+      </c>
+      <c r="C521" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D521" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E521" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G521" s="5" t="n"/>
+      <c r="H521" s="6" t="n"/>
+      <c r="I521" s="5" t="n"/>
+      <c r="J521" s="6" t="n"/>
+      <c r="K521" s="6" t="n"/>
+      <c r="L521" s="6" t="n"/>
+      <c r="M521" s="5" t="n"/>
+      <c r="N521" s="5" t="n"/>
+      <c r="O521" s="5" t="n"/>
+      <c r="P521" s="5" t="n"/>
+      <c r="Q521" s="6" t="n"/>
+      <c r="R521" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S521" s="5" t="n"/>
+      <c r="T521" s="6" t="n"/>
+      <c r="U521" s="6" t="n"/>
+      <c r="V521" s="6" t="n"/>
+      <c r="W521" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fuelfiit-cotton-blend-embroidered-coat/p/itmdf859b931cda0?pid=CATHPQKBBUAYUNWS</t>
+        </is>
+      </c>
+      <c r="X521" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y521" s="5" t="n"/>
+      <c r="Z521" s="5" t="n"/>
+      <c r="AA521" s="5" t="n"/>
+      <c r="AB521" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fuelfiit-cotton-blend-embroidered-coat/p/itmdf859b931cda0?pid=CATHPQKBBUAYUNWS</t>
+        </is>
+      </c>
+      <c r="AC521" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD521" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="22" customHeight="1">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>RoopRashmi</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>RoopRashmi</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D522" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="n"/>
+      <c r="H522" s="3" t="n"/>
+      <c r="I522" s="2" t="n"/>
+      <c r="J522" s="3" t="n"/>
+      <c r="K522" s="3" t="n"/>
+      <c r="L522" s="3" t="n"/>
+      <c r="M522" s="2" t="n"/>
+      <c r="N522" s="2" t="n"/>
+      <c r="O522" s="2" t="n"/>
+      <c r="P522" s="2" t="n"/>
+      <c r="Q522" s="3" t="n"/>
+      <c r="R522" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S522" s="2" t="n"/>
+      <c r="T522" s="3" t="n"/>
+      <c r="U522" s="3" t="n"/>
+      <c r="V522" s="3" t="n"/>
+      <c r="W522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gfo-suede-solid-coat/p/itm855533d82fdb6?pid=CATHZA3V8AHBF8SQ</t>
+        </is>
+      </c>
+      <c r="X522" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y522" s="2" t="n"/>
+      <c r="Z522" s="2" t="n"/>
+      <c r="AA522" s="2" t="n"/>
+      <c r="AB522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gfo-suede-solid-coat/p/itm855533d82fdb6?pid=CATHZA3V8AHBF8SQ</t>
+        </is>
+      </c>
+      <c r="AC522" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD522" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="22" customHeight="1">
+      <c r="A523" s="5" t="inlineStr">
+        <is>
+          <t>Pankaj</t>
+        </is>
+      </c>
+      <c r="B523" s="5" t="inlineStr">
+        <is>
+          <t>Pankaj</t>
+        </is>
+      </c>
+      <c r="C523" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D523" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E523" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G523" s="5" t="n"/>
+      <c r="H523" s="6" t="n"/>
+      <c r="I523" s="5" t="n"/>
+      <c r="J523" s="6" t="n"/>
+      <c r="K523" s="6" t="n"/>
+      <c r="L523" s="6" t="n"/>
+      <c r="M523" s="5" t="n"/>
+      <c r="N523" s="5" t="n"/>
+      <c r="O523" s="5" t="n"/>
+      <c r="P523" s="5" t="n"/>
+      <c r="Q523" s="6" t="n"/>
+      <c r="R523" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S523" s="5" t="n"/>
+      <c r="T523" s="6" t="n"/>
+      <c r="U523" s="6" t="n"/>
+      <c r="V523" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W523" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/roarerss-poly-fleece-solid-coat/p/itmb2b4facbcd38c?pid=CATHGYRZ5QY7FDGH</t>
+        </is>
+      </c>
+      <c r="X523" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y523" s="5" t="n"/>
+      <c r="Z523" s="5" t="n"/>
+      <c r="AA523" s="5" t="n"/>
+      <c r="AB523" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/roarerss-poly-fleece-solid-coat/p/itmb2b4facbcd38c?pid=CATHGYRZ5QY7FDGH</t>
+        </is>
+      </c>
+      <c r="AC523" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD523" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="22" customHeight="1">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Premiumrobes</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>Premiumrobes</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D524" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="n"/>
+      <c r="H524" s="3" t="n"/>
+      <c r="I524" s="2" t="n"/>
+      <c r="J524" s="3" t="n"/>
+      <c r="K524" s="3" t="n"/>
+      <c r="L524" s="3" t="n"/>
+      <c r="M524" s="2" t="n"/>
+      <c r="N524" s="2" t="n"/>
+      <c r="O524" s="2" t="n"/>
+      <c r="P524" s="2" t="n"/>
+      <c r="Q524" s="3" t="n"/>
+      <c r="R524" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S524" s="2" t="n"/>
+      <c r="T524" s="3" t="n"/>
+      <c r="U524" s="3" t="n"/>
+      <c r="V524" s="3" t="n"/>
+      <c r="W524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gwalior-law-firm-cotton-blend-coat/p/itmaa58e9323e147?pid=CATHDHVEDMNJW5PG</t>
+        </is>
+      </c>
+      <c r="X524" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y524" s="2" t="n"/>
+      <c r="Z524" s="2" t="n"/>
+      <c r="AA524" s="2" t="n"/>
+      <c r="AB524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gwalior-law-firm-cotton-blend-coat/p/itmaa58e9323e147?pid=CATHDHVEDMNJW5PG</t>
+        </is>
+      </c>
+      <c r="AC524" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD524" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="22" customHeight="1">
+      <c r="A525" s="5" t="inlineStr">
+        <is>
+          <t>NGOLDFASHION</t>
+        </is>
+      </c>
+      <c r="B525" s="5" t="inlineStr">
+        <is>
+          <t>NGOLDFASHION</t>
+        </is>
+      </c>
+      <c r="C525" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D525" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E525" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G525" s="5" t="n"/>
+      <c r="H525" s="6" t="n"/>
+      <c r="I525" s="5" t="n"/>
+      <c r="J525" s="6" t="n"/>
+      <c r="K525" s="6" t="n"/>
+      <c r="L525" s="6" t="n"/>
+      <c r="M525" s="5" t="n"/>
+      <c r="N525" s="5" t="n"/>
+      <c r="O525" s="5" t="n"/>
+      <c r="P525" s="5" t="n"/>
+      <c r="Q525" s="6" t="n"/>
+      <c r="R525" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S525" s="5" t="n"/>
+      <c r="T525" s="6" t="n"/>
+      <c r="U525" s="6" t="n"/>
+      <c r="V525" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W525" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/aayat-wool-solid-coat/p/itm642b65591e378?pid=CATHGUTWVJGEUAYN</t>
+        </is>
+      </c>
+      <c r="X525" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y525" s="5" t="n"/>
+      <c r="Z525" s="5" t="n"/>
+      <c r="AA525" s="5" t="n"/>
+      <c r="AB525" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/aayat-wool-solid-coat/p/itm642b65591e378?pid=CATHGUTWVJGEUAYN</t>
+        </is>
+      </c>
+      <c r="AC525" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD525" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="22" customHeight="1">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>SualehaTrends24</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>SualehaTrends24</t>
+        </is>
+      </c>
+      <c r="C526" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D526" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="n"/>
+      <c r="H526" s="3" t="n"/>
+      <c r="I526" s="2" t="n"/>
+      <c r="J526" s="3" t="n"/>
+      <c r="K526" s="3" t="n"/>
+      <c r="L526" s="3" t="n"/>
+      <c r="M526" s="2" t="n"/>
+      <c r="N526" s="2" t="n"/>
+      <c r="O526" s="2" t="n"/>
+      <c r="P526" s="2" t="n"/>
+      <c r="Q526" s="3" t="n"/>
+      <c r="R526" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S526" s="2" t="n"/>
+      <c r="T526" s="3" t="n"/>
+      <c r="U526" s="3" t="n"/>
+      <c r="V526" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sualehatrends-winter-based-solid-coat/p/itm33d9a7a0f2348?pid=CATHZEVQZSFJ2EDZ</t>
+        </is>
+      </c>
+      <c r="X526" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y526" s="2" t="n"/>
+      <c r="Z526" s="2" t="n"/>
+      <c r="AA526" s="2" t="n"/>
+      <c r="AB526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sualehatrends-winter-based-solid-coat/p/itm33d9a7a0f2348?pid=CATHZEVQZSFJ2EDZ</t>
+        </is>
+      </c>
+      <c r="AC526" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD526" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="22" customHeight="1">
+      <c r="A527" s="5" t="inlineStr">
+        <is>
+          <t>Monte Carlo Fashion Ltd</t>
+        </is>
+      </c>
+      <c r="B527" s="5" t="inlineStr">
+        <is>
+          <t>Monte Carlo Fashion Ltd</t>
+        </is>
+      </c>
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D527" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E527" s="5" t="inlineStr">
+        <is>
+          <t>Public Limited Company</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G527" s="5" t="n"/>
+      <c r="H527" s="6" t="n"/>
+      <c r="I527" s="5" t="n"/>
+      <c r="J527" s="6" t="n"/>
+      <c r="K527" s="6" t="n"/>
+      <c r="L527" s="6" t="n"/>
+      <c r="M527" s="5" t="n"/>
+      <c r="N527" s="5" t="n"/>
+      <c r="O527" s="5" t="n"/>
+      <c r="P527" s="5" t="n"/>
+      <c r="Q527" s="6" t="n"/>
+      <c r="R527" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S527" s="5" t="n"/>
+      <c r="T527" s="6" t="n"/>
+      <c r="U527" s="6" t="n"/>
+      <c r="V527" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W527" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/monte-carlo-wool-blend-coat/p/itm5b02873e390e7?pid=CATH5VRKPE6YWUAV</t>
+        </is>
+      </c>
+      <c r="X527" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y527" s="5" t="n"/>
+      <c r="Z527" s="5" t="n"/>
+      <c r="AA527" s="5" t="n"/>
+      <c r="AB527" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/monte-carlo-wool-blend-coat/p/itm5b02873e390e7?pid=CATH5VRKPE6YWUAV</t>
+        </is>
+      </c>
+      <c r="AC527" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD527" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="22" customHeight="1">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>LloydsandCo</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>LloydsandCo</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D528" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="n"/>
+      <c r="H528" s="3" t="n"/>
+      <c r="I528" s="2" t="n"/>
+      <c r="J528" s="3" t="n"/>
+      <c r="K528" s="3" t="n"/>
+      <c r="L528" s="3" t="n"/>
+      <c r="M528" s="2" t="n"/>
+      <c r="N528" s="2" t="n"/>
+      <c r="O528" s="2" t="n"/>
+      <c r="P528" s="2" t="n"/>
+      <c r="Q528" s="3" t="n"/>
+      <c r="R528" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S528" s="2" t="n"/>
+      <c r="T528" s="3" t="n"/>
+      <c r="U528" s="3" t="n"/>
+      <c r="V528" s="3" t="n"/>
+      <c r="W528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/armisto-wool-solid-coat/p/itma473cb80e4388?pid=CATHZBN7JP5ZPFG4</t>
+        </is>
+      </c>
+      <c r="X528" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y528" s="2" t="n"/>
+      <c r="Z528" s="2" t="n"/>
+      <c r="AA528" s="2" t="n"/>
+      <c r="AB528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/armisto-wool-solid-coat/p/itma473cb80e4388?pid=CATHZBN7JP5ZPFG4</t>
+        </is>
+      </c>
+      <c r="AC528" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD528" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="22" customHeight="1">
+      <c r="A529" s="5" t="inlineStr">
+        <is>
+          <t>CHKOKKO</t>
+        </is>
+      </c>
+      <c r="B529" s="5" t="inlineStr">
+        <is>
+          <t>CHKOKKO</t>
+        </is>
+      </c>
+      <c r="C529" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D529" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E529" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G529" s="5" t="n"/>
+      <c r="H529" s="6" t="n"/>
+      <c r="I529" s="5" t="n"/>
+      <c r="J529" s="6" t="n"/>
+      <c r="K529" s="6" t="n"/>
+      <c r="L529" s="6" t="n"/>
+      <c r="M529" s="5" t="n"/>
+      <c r="N529" s="5" t="n"/>
+      <c r="O529" s="5" t="n"/>
+      <c r="P529" s="5" t="n"/>
+      <c r="Q529" s="6" t="n"/>
+      <c r="R529" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S529" s="5" t="n"/>
+      <c r="T529" s="6" t="n"/>
+      <c r="U529" s="6" t="n"/>
+      <c r="V529" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W529" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/chkokko-tweed-solid-coat/p/itmffed5fe34d0f7?pid=CATHG6XSTEV4HGHU</t>
+        </is>
+      </c>
+      <c r="X529" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y529" s="5" t="n"/>
+      <c r="Z529" s="5" t="n"/>
+      <c r="AA529" s="5" t="n"/>
+      <c r="AB529" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/chkokko-tweed-solid-coat/p/itmffed5fe34d0f7?pid=CATHG6XSTEV4HGHU</t>
+        </is>
+      </c>
+      <c r="AC529" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD529" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="22" customHeight="1">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>CrimsouneClub</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>CrimsouneClub</t>
+        </is>
+      </c>
+      <c r="C530" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D530" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="n"/>
+      <c r="H530" s="3" t="n"/>
+      <c r="I530" s="2" t="n"/>
+      <c r="J530" s="3" t="n"/>
+      <c r="K530" s="3" t="n"/>
+      <c r="L530" s="3" t="n"/>
+      <c r="M530" s="2" t="n"/>
+      <c r="N530" s="2" t="n"/>
+      <c r="O530" s="2" t="n"/>
+      <c r="P530" s="2" t="n"/>
+      <c r="Q530" s="3" t="n"/>
+      <c r="R530" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S530" s="2" t="n"/>
+      <c r="T530" s="3" t="n"/>
+      <c r="U530" s="3" t="n"/>
+      <c r="V530" s="3" t="n"/>
+      <c r="W530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/crimsoune-club-polyester-solid-coat/p/itm7c85b3598c454?pid=CATH8G29MGFDCNR3</t>
+        </is>
+      </c>
+      <c r="X530" s="2" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y530" s="2" t="n"/>
+      <c r="Z530" s="2" t="n"/>
+      <c r="AA530" s="2" t="n"/>
+      <c r="AB530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/crimsoune-club-polyester-solid-coat/p/itm7c85b3598c454?pid=CATH8G29MGFDCNR3</t>
+        </is>
+      </c>
+      <c r="AC530" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD530" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="22" customHeight="1">
+      <c r="A531" s="5" t="inlineStr">
+        <is>
+          <t>PLAGG</t>
+        </is>
+      </c>
+      <c r="B531" s="5" t="inlineStr">
+        <is>
+          <t>PLAGG</t>
+        </is>
+      </c>
+      <c r="C531" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D531" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F531" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="G531" s="5" t="n"/>
+      <c r="H531" s="6" t="n"/>
+      <c r="I531" s="5" t="n"/>
+      <c r="J531" s="6" t="n"/>
+      <c r="K531" s="6" t="n"/>
+      <c r="L531" s="6" t="n"/>
+      <c r="M531" s="5" t="n"/>
+      <c r="N531" s="5" t="n"/>
+      <c r="O531" s="5" t="n"/>
+      <c r="P531" s="5" t="n"/>
+      <c r="Q531" s="6" t="n"/>
+      <c r="R531" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S531" s="5" t="n"/>
+      <c r="T531" s="6" t="n"/>
+      <c r="U531" s="6" t="n"/>
+      <c r="V531" s="6" t="n"/>
+      <c r="W531" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metronaut-wool-blended-solid-coat/p/itmc7fe4467ac7c0?pid=CATHP9ZEGVYPPHVG</t>
+        </is>
+      </c>
+      <c r="X531" s="5" t="inlineStr">
+        <is>
+          <t>Coats</t>
+        </is>
+      </c>
+      <c r="Y531" s="5" t="n"/>
+      <c r="Z531" s="5" t="n"/>
+      <c r="AA531" s="5" t="n"/>
+      <c r="AB531" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metronaut-wool-blended-solid-coat/p/itmc7fe4467ac7c0?pid=CATHP9ZEGVYPPHVG</t>
+        </is>
+      </c>
+      <c r="AC531" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD531" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="22" customHeight="1">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>LOVELUX</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>LOVELUX</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D532" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="n"/>
+      <c r="H532" s="3" t="n"/>
+      <c r="I532" s="2" t="n"/>
+      <c r="J532" s="3" t="n"/>
+      <c r="K532" s="3" t="n"/>
+      <c r="L532" s="3" t="n"/>
+      <c r="M532" s="2" t="n"/>
+      <c r="N532" s="2" t="n"/>
+      <c r="O532" s="2" t="n"/>
+      <c r="P532" s="2" t="n"/>
+      <c r="Q532" s="3" t="n"/>
+      <c r="R532" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S532" s="2" t="n"/>
+      <c r="T532" s="3" t="n"/>
+      <c r="U532" s="3" t="n"/>
+      <c r="V532" s="3" t="n"/>
+      <c r="W532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fivelove-unisex-striped-calf-length/p/itmebe9f541bd9f1?pid=SOCHPBXRHDN4ZEBW</t>
+        </is>
+      </c>
+      <c r="X532" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y532" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z532" s="2" t="n"/>
+      <c r="AA532" s="2" t="n"/>
+      <c r="AB532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fivelove-unisex-striped-calf-length/p/itmebe9f541bd9f1?pid=SOCHPBXRHDN4ZEBW</t>
+        </is>
+      </c>
+      <c r="AC532" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD532" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="22" customHeight="1">
+      <c r="A533" s="5" t="inlineStr">
+        <is>
+          <t>YOUNGINDIAWEN</t>
+        </is>
+      </c>
+      <c r="B533" s="5" t="inlineStr">
+        <is>
+          <t>YOUNGINDIAWEN</t>
+        </is>
+      </c>
+      <c r="C533" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D533" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E533" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G533" s="5" t="n"/>
+      <c r="H533" s="6" t="n"/>
+      <c r="I533" s="5" t="n"/>
+      <c r="J533" s="6" t="n"/>
+      <c r="K533" s="6" t="n"/>
+      <c r="L533" s="6" t="n"/>
+      <c r="M533" s="5" t="n"/>
+      <c r="N533" s="5" t="n"/>
+      <c r="O533" s="5" t="n"/>
+      <c r="P533" s="5" t="n"/>
+      <c r="Q533" s="6" t="n"/>
+      <c r="R533" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S533" s="5" t="n"/>
+      <c r="T533" s="6" t="n"/>
+      <c r="U533" s="6" t="n"/>
+      <c r="V533" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W533" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/dumleto-unisex-color-block-calf-length/p/itmd1e86431d80a6?pid=SOCHMEYZFWNHGGCS</t>
+        </is>
+      </c>
+      <c r="X533" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y533" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z533" s="5" t="n"/>
+      <c r="AA533" s="5" t="n"/>
+      <c r="AB533" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/dumleto-unisex-color-block-calf-length/p/itmd1e86431d80a6?pid=SOCHMEYZFWNHGGCS</t>
+        </is>
+      </c>
+      <c r="AC533" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD533" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="22" customHeight="1">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>CEVAX</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>CEVAX</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D534" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="n"/>
+      <c r="H534" s="3" t="n"/>
+      <c r="I534" s="2" t="n"/>
+      <c r="J534" s="3" t="n"/>
+      <c r="K534" s="3" t="n"/>
+      <c r="L534" s="3" t="n"/>
+      <c r="M534" s="2" t="n"/>
+      <c r="N534" s="2" t="n"/>
+      <c r="O534" s="2" t="n"/>
+      <c r="P534" s="2" t="n"/>
+      <c r="Q534" s="3" t="n"/>
+      <c r="R534" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S534" s="2" t="n"/>
+      <c r="T534" s="3" t="n"/>
+      <c r="U534" s="3" t="n"/>
+      <c r="V534" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cevax-unisex-striped-mid-calf-crew/p/itm3805c526bf007?pid=SOCHPZZVF2EQPZGY</t>
+        </is>
+      </c>
+      <c r="X534" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y534" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z534" s="2" t="n"/>
+      <c r="AA534" s="2" t="n"/>
+      <c r="AB534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cevax-unisex-striped-mid-calf-crew/p/itm3805c526bf007?pid=SOCHPZZVF2EQPZGY</t>
+        </is>
+      </c>
+      <c r="AC534" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD534" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="22" customHeight="1">
+      <c r="A535" s="5" t="inlineStr">
+        <is>
+          <t>ROZZYBLUE</t>
+        </is>
+      </c>
+      <c r="B535" s="5" t="inlineStr">
+        <is>
+          <t>ROZZYBLUE</t>
+        </is>
+      </c>
+      <c r="C535" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D535" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F535" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G535" s="5" t="n"/>
+      <c r="H535" s="6" t="n"/>
+      <c r="I535" s="5" t="n"/>
+      <c r="J535" s="6" t="n"/>
+      <c r="K535" s="6" t="n"/>
+      <c r="L535" s="6" t="n"/>
+      <c r="M535" s="5" t="n"/>
+      <c r="N535" s="5" t="n"/>
+      <c r="O535" s="5" t="n"/>
+      <c r="P535" s="5" t="n"/>
+      <c r="Q535" s="6" t="n"/>
+      <c r="R535" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S535" s="5" t="n"/>
+      <c r="T535" s="6" t="n"/>
+      <c r="U535" s="6" t="n"/>
+      <c r="V535" s="6" t="n"/>
+      <c r="W535" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rozzyblue-unisex-self-design-ankle-length/p/itmf1eea95b945ca?pid=SOCHZ37FKHZZBMJT</t>
+        </is>
+      </c>
+      <c r="X535" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y535" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z535" s="5" t="n"/>
+      <c r="AA535" s="5" t="n"/>
+      <c r="AB535" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rozzyblue-unisex-self-design-ankle-length/p/itmf1eea95b945ca?pid=SOCHZ37FKHZZBMJT</t>
+        </is>
+      </c>
+      <c r="AC535" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD535" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="22" customHeight="1">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Technosportofficial</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>Technosportofficial</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D536" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="n"/>
+      <c r="H536" s="3" t="n"/>
+      <c r="I536" s="2" t="n"/>
+      <c r="J536" s="3" t="n"/>
+      <c r="K536" s="3" t="n"/>
+      <c r="L536" s="3" t="n"/>
+      <c r="M536" s="2" t="n"/>
+      <c r="N536" s="2" t="n"/>
+      <c r="O536" s="2" t="n"/>
+      <c r="P536" s="2" t="n"/>
+      <c r="Q536" s="3" t="n"/>
+      <c r="R536" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S536" s="2" t="n"/>
+      <c r="T536" s="3" t="n"/>
+      <c r="U536" s="3" t="n"/>
+      <c r="V536" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/technosport-men-self-design-ankle-length/p/itm9f5470493ae69?pid=SOCHDG37GPBJSCG3</t>
+        </is>
+      </c>
+      <c r="X536" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y536" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z536" s="2" t="n"/>
+      <c r="AA536" s="2" t="n"/>
+      <c r="AB536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/technosport-men-self-design-ankle-length/p/itm9f5470493ae69?pid=SOCHDG37GPBJSCG3</t>
+        </is>
+      </c>
+      <c r="AC536" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD536" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="22" customHeight="1">
+      <c r="A537" s="5" t="inlineStr">
+        <is>
+          <t>fexmy</t>
+        </is>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>fexmy</t>
+        </is>
+      </c>
+      <c r="C537" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D537" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G537" s="5" t="n"/>
+      <c r="H537" s="6" t="n"/>
+      <c r="I537" s="5" t="n"/>
+      <c r="J537" s="6" t="n"/>
+      <c r="K537" s="6" t="n"/>
+      <c r="L537" s="6" t="n"/>
+      <c r="M537" s="5" t="n"/>
+      <c r="N537" s="5" t="n"/>
+      <c r="O537" s="5" t="n"/>
+      <c r="P537" s="5" t="n"/>
+      <c r="Q537" s="6" t="n"/>
+      <c r="R537" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S537" s="5" t="n"/>
+      <c r="T537" s="6" t="n"/>
+      <c r="U537" s="6" t="n"/>
+      <c r="V537" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W537" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fexmy-men-women-checkered-calf-length/p/itm30882c065bde8?pid=SOCH7Z9QC2AVFNKN</t>
+        </is>
+      </c>
+      <c r="X537" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y537" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z537" s="5" t="n"/>
+      <c r="AA537" s="5" t="n"/>
+      <c r="AB537" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fexmy-men-women-checkered-calf-length/p/itm30882c065bde8?pid=SOCH7Z9QC2AVFNKN</t>
+        </is>
+      </c>
+      <c r="AC537" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD537" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="22" customHeight="1">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>SuperSox</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>SuperSox</t>
+        </is>
+      </c>
+      <c r="C538" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D538" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="n"/>
+      <c r="H538" s="3" t="n"/>
+      <c r="I538" s="2" t="n"/>
+      <c r="J538" s="3" t="n"/>
+      <c r="K538" s="3" t="n"/>
+      <c r="L538" s="3" t="n"/>
+      <c r="M538" s="2" t="n"/>
+      <c r="N538" s="2" t="n"/>
+      <c r="O538" s="2" t="n"/>
+      <c r="P538" s="2" t="n"/>
+      <c r="Q538" s="3" t="n"/>
+      <c r="R538" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S538" s="2" t="n"/>
+      <c r="T538" s="3" t="n"/>
+      <c r="U538" s="3" t="n"/>
+      <c r="V538" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/supersox-men-striped-ankle-length/p/itm47961f7ee7a5d?pid=SOCGWH9HKDAY9Q2N</t>
+        </is>
+      </c>
+      <c r="X538" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y538" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z538" s="2" t="n"/>
+      <c r="AA538" s="2" t="n"/>
+      <c r="AB538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/supersox-men-striped-ankle-length/p/itm47961f7ee7a5d?pid=SOCGWH9HKDAY9Q2N</t>
+        </is>
+      </c>
+      <c r="AC538" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD538" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="22" customHeight="1">
+      <c r="A539" s="5" t="inlineStr">
+        <is>
+          <t>KrizadivEthnics</t>
+        </is>
+      </c>
+      <c r="B539" s="5" t="inlineStr">
+        <is>
+          <t>KrizadivEthnics</t>
+        </is>
+      </c>
+      <c r="C539" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D539" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E539" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F539" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G539" s="5" t="n"/>
+      <c r="H539" s="6" t="n"/>
+      <c r="I539" s="5" t="n"/>
+      <c r="J539" s="6" t="n"/>
+      <c r="K539" s="6" t="n"/>
+      <c r="L539" s="6" t="n"/>
+      <c r="M539" s="5" t="n"/>
+      <c r="N539" s="5" t="n"/>
+      <c r="O539" s="5" t="n"/>
+      <c r="P539" s="5" t="n"/>
+      <c r="Q539" s="6" t="n"/>
+      <c r="R539" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S539" s="5" t="n"/>
+      <c r="T539" s="6" t="n"/>
+      <c r="U539" s="6" t="n"/>
+      <c r="V539" s="6" t="n"/>
+      <c r="W539" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lagecy-unisex-printed-ankle-length/p/itmaacf8f70a038f?pid=SOCHHYY9TGY9G55Y</t>
+        </is>
+      </c>
+      <c r="X539" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y539" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z539" s="5" t="n"/>
+      <c r="AA539" s="5" t="n"/>
+      <c r="AB539" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lagecy-unisex-printed-ankle-length/p/itmaacf8f70a038f?pid=SOCHHYY9TGY9G55Y</t>
+        </is>
+      </c>
+      <c r="AC539" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD539" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="22" customHeight="1">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>RozzyBlueSocks</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>RozzyBlueSocks</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D540" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="n"/>
+      <c r="H540" s="3" t="n"/>
+      <c r="I540" s="2" t="n"/>
+      <c r="J540" s="3" t="n"/>
+      <c r="K540" s="3" t="n"/>
+      <c r="L540" s="3" t="n"/>
+      <c r="M540" s="2" t="n"/>
+      <c r="N540" s="2" t="n"/>
+      <c r="O540" s="2" t="n"/>
+      <c r="P540" s="2" t="n"/>
+      <c r="Q540" s="3" t="n"/>
+      <c r="R540" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S540" s="2" t="n"/>
+      <c r="T540" s="3" t="n"/>
+      <c r="U540" s="3" t="n"/>
+      <c r="V540" s="3" t="n"/>
+      <c r="W540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rozzyblue-unisex-self-design-ankle-length/p/itmac875a5f91947?pid=SOCHPS9PPSUT2KFG</t>
+        </is>
+      </c>
+      <c r="X540" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y540" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z540" s="2" t="n"/>
+      <c r="AA540" s="2" t="n"/>
+      <c r="AB540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rozzyblue-unisex-self-design-ankle-length/p/itmac875a5f91947?pid=SOCHPS9PPSUT2KFG</t>
+        </is>
+      </c>
+      <c r="AC540" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD540" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="22" customHeight="1">
+      <c r="A541" s="5" t="inlineStr">
+        <is>
+          <t>SoxSense</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
+        <is>
+          <t>SoxSense</t>
+        </is>
+      </c>
+      <c r="C541" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D541" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E541" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G541" s="5" t="n"/>
+      <c r="H541" s="6" t="n"/>
+      <c r="I541" s="5" t="n"/>
+      <c r="J541" s="6" t="n"/>
+      <c r="K541" s="6" t="n"/>
+      <c r="L541" s="6" t="n"/>
+      <c r="M541" s="5" t="n"/>
+      <c r="N541" s="5" t="n"/>
+      <c r="O541" s="5" t="n"/>
+      <c r="P541" s="5" t="n"/>
+      <c r="Q541" s="6" t="n"/>
+      <c r="R541" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S541" s="5" t="n"/>
+      <c r="T541" s="6" t="n"/>
+      <c r="U541" s="6" t="n"/>
+      <c r="V541" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W541" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/premiumsock-men-women-graphic-print-mid-calf-crew/p/itmee7e133f63414?pid=SOCHZT4ZD4ZG2KMZ</t>
+        </is>
+      </c>
+      <c r="X541" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y541" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z541" s="5" t="n"/>
+      <c r="AA541" s="5" t="n"/>
+      <c r="AB541" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/premiumsock-men-women-graphic-print-mid-calf-crew/p/itmee7e133f63414?pid=SOCHZT4ZD4ZG2KMZ</t>
+        </is>
+      </c>
+      <c r="AC541" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD541" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="22" customHeight="1">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Naamik</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>Naamik</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D542" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="n"/>
+      <c r="H542" s="3" t="n"/>
+      <c r="I542" s="2" t="n"/>
+      <c r="J542" s="3" t="n"/>
+      <c r="K542" s="3" t="n"/>
+      <c r="L542" s="3" t="n"/>
+      <c r="M542" s="2" t="n"/>
+      <c r="N542" s="2" t="n"/>
+      <c r="O542" s="2" t="n"/>
+      <c r="P542" s="2" t="n"/>
+      <c r="Q542" s="3" t="n"/>
+      <c r="R542" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S542" s="2" t="n"/>
+      <c r="T542" s="3" t="n"/>
+      <c r="U542" s="3" t="n"/>
+      <c r="V542" s="3" t="n"/>
+      <c r="W542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/naamik-unisex-solid-mid-calf-crew/p/itmcca3028fee2ec?pid=SOCHKE5ZFRRVQXQR</t>
+        </is>
+      </c>
+      <c r="X542" s="2" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y542" s="2" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z542" s="2" t="n"/>
+      <c r="AA542" s="2" t="n"/>
+      <c r="AB542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/naamik-unisex-solid-mid-calf-crew/p/itmcca3028fee2ec?pid=SOCHKE5ZFRRVQXQR</t>
+        </is>
+      </c>
+      <c r="AC542" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD542" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="22" customHeight="1">
+      <c r="A543" s="5" t="inlineStr">
+        <is>
+          <t>METROSOXINDIA</t>
+        </is>
+      </c>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>METROSOXINDIA</t>
+        </is>
+      </c>
+      <c r="C543" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D543" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E543" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="G543" s="5" t="n"/>
+      <c r="H543" s="6" t="n"/>
+      <c r="I543" s="5" t="n"/>
+      <c r="J543" s="6" t="n"/>
+      <c r="K543" s="6" t="n"/>
+      <c r="L543" s="6" t="n"/>
+      <c r="M543" s="5" t="n"/>
+      <c r="N543" s="5" t="n"/>
+      <c r="O543" s="5" t="n"/>
+      <c r="P543" s="5" t="n"/>
+      <c r="Q543" s="6" t="n"/>
+      <c r="R543" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S543" s="5" t="n"/>
+      <c r="T543" s="6" t="n"/>
+      <c r="U543" s="6" t="n"/>
+      <c r="V543" s="6" t="n"/>
+      <c r="W543" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metrosox-men-solid-ankle-length/p/itm8690e119752f8?pid=SOCHPYZQ7CF5SMZD</t>
+        </is>
+      </c>
+      <c r="X543" s="5" t="inlineStr">
+        <is>
+          <t>Sportswear</t>
+        </is>
+      </c>
+      <c r="Y543" s="5" t="inlineStr">
+        <is>
+          <t>Athletic Socks</t>
+        </is>
+      </c>
+      <c r="Z543" s="5" t="n"/>
+      <c r="AA543" s="5" t="n"/>
+      <c r="AB543" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/metrosox-men-solid-ankle-length/p/itm8690e119752f8?pid=SOCHPYZQ7CF5SMZD</t>
+        </is>
+      </c>
+      <c r="AC543" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD543" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="22" customHeight="1">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>MGold</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>MGold</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D544" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="n"/>
+      <c r="H544" s="3" t="n"/>
+      <c r="I544" s="2" t="n"/>
+      <c r="J544" s="3" t="n"/>
+      <c r="K544" s="3" t="n"/>
+      <c r="L544" s="3" t="n"/>
+      <c r="M544" s="2" t="n"/>
+      <c r="N544" s="2" t="n"/>
+      <c r="O544" s="2" t="n"/>
+      <c r="P544" s="2" t="n"/>
+      <c r="Q544" s="3" t="n"/>
+      <c r="R544" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S544" s="2" t="n"/>
+      <c r="T544" s="3" t="n"/>
+      <c r="U544" s="3" t="n"/>
+      <c r="V544" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/m-creation-alloy-gold-plated-gold-jewellery-set/p/itm8ea27ed06eaf0?pid=JWSGA2EFZYRW4G8X</t>
+        </is>
+      </c>
+      <c r="X544" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y544" s="2" t="n"/>
+      <c r="Z544" s="2" t="n"/>
+      <c r="AA544" s="2" t="n"/>
+      <c r="AB544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/m-creation-alloy-gold-plated-gold-jewellery-set/p/itm8ea27ed06eaf0?pid=JWSGA2EFZYRW4G8X</t>
+        </is>
+      </c>
+      <c r="AC544" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD544" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="22" customHeight="1">
+      <c r="A545" s="5" t="inlineStr">
+        <is>
+          <t>Vivanta</t>
+        </is>
+      </c>
+      <c r="B545" s="5" t="inlineStr">
+        <is>
+          <t>Vivanta</t>
+        </is>
+      </c>
+      <c r="C545" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D545" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E545" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G545" s="5" t="n"/>
+      <c r="H545" s="6" t="n"/>
+      <c r="I545" s="5" t="n"/>
+      <c r="J545" s="6" t="n"/>
+      <c r="K545" s="6" t="n"/>
+      <c r="L545" s="6" t="n"/>
+      <c r="M545" s="5" t="n"/>
+      <c r="N545" s="5" t="n"/>
+      <c r="O545" s="5" t="n"/>
+      <c r="P545" s="5" t="n"/>
+      <c r="Q545" s="6" t="n"/>
+      <c r="R545" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S545" s="5" t="n"/>
+      <c r="T545" s="6" t="n"/>
+      <c r="U545" s="6" t="n"/>
+      <c r="V545" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W545" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vivanta-alloy-multicolor-jewellery-set/p/itm8b61c4eee5a24?pid=JWSGX37FBHRJYVJN</t>
+        </is>
+      </c>
+      <c r="X545" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y545" s="5" t="n"/>
+      <c r="Z545" s="5" t="n"/>
+      <c r="AA545" s="5" t="n"/>
+      <c r="AB545" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/vivanta-alloy-multicolor-jewellery-set/p/itm8b61c4eee5a24?pid=JWSGX37FBHRJYVJN</t>
+        </is>
+      </c>
+      <c r="AC545" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD545" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="22" customHeight="1">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>SmaaartChoice</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>SmaaartChoice</t>
+        </is>
+      </c>
+      <c r="C546" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D546" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="n"/>
+      <c r="H546" s="3" t="n"/>
+      <c r="I546" s="2" t="n"/>
+      <c r="J546" s="3" t="n"/>
+      <c r="K546" s="3" t="n"/>
+      <c r="L546" s="3" t="n"/>
+      <c r="M546" s="2" t="n"/>
+      <c r="N546" s="2" t="n"/>
+      <c r="O546" s="2" t="n"/>
+      <c r="P546" s="2" t="n"/>
+      <c r="Q546" s="3" t="n"/>
+      <c r="R546" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S546" s="2" t="n"/>
+      <c r="T546" s="3" t="n"/>
+      <c r="U546" s="3" t="n"/>
+      <c r="V546" s="3" t="n"/>
+      <c r="W546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/smart-choice-kitchenelite-10-piece-cookware-set-ultimate-cooking-performance-induction-bottom-non-stick-coated-set/p/itm402446c7f16a8?pid=CKSHNAFJPSEC8ZYZ</t>
+        </is>
+      </c>
+      <c r="X546" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y546" s="2" t="n"/>
+      <c r="Z546" s="2" t="n"/>
+      <c r="AA546" s="2" t="n"/>
+      <c r="AB546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/smart-choice-kitchenelite-10-piece-cookware-set-ultimate-cooking-performance-induction-bottom-non-stick-coated-set/p/itm402446c7f16a8?pid=CKSHNAFJPSEC8ZYZ</t>
+        </is>
+      </c>
+      <c r="AC546" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD546" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="22" customHeight="1">
+      <c r="A547" s="5" t="inlineStr">
+        <is>
+          <t>Maharajee</t>
+        </is>
+      </c>
+      <c r="B547" s="5" t="inlineStr">
+        <is>
+          <t>Maharajee</t>
+        </is>
+      </c>
+      <c r="C547" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D547" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G547" s="5" t="n"/>
+      <c r="H547" s="6" t="n"/>
+      <c r="I547" s="5" t="n"/>
+      <c r="J547" s="6" t="n"/>
+      <c r="K547" s="6" t="n"/>
+      <c r="L547" s="6" t="n"/>
+      <c r="M547" s="5" t="n"/>
+      <c r="N547" s="5" t="n"/>
+      <c r="O547" s="5" t="n"/>
+      <c r="P547" s="5" t="n"/>
+      <c r="Q547" s="6" t="n"/>
+      <c r="R547" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S547" s="5" t="n"/>
+      <c r="T547" s="6" t="n"/>
+      <c r="U547" s="6" t="n"/>
+      <c r="V547" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W547" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/maharajee-smartbuy-induction-bottom-non-stick-coated-cookware-set/p/itma58a1d936e81b?pid=CKSH96HVY35AQGPW</t>
+        </is>
+      </c>
+      <c r="X547" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y547" s="5" t="n"/>
+      <c r="Z547" s="5" t="n"/>
+      <c r="AA547" s="5" t="n"/>
+      <c r="AB547" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/maharajee-smartbuy-induction-bottom-non-stick-coated-cookware-set/p/itma58a1d936e81b?pid=CKSH96HVY35AQGPW</t>
+        </is>
+      </c>
+      <c r="AC547" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD547" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="22" customHeight="1">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>SHREEADINARAYANSALES</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>SHREEADINARAYANSALES</t>
+        </is>
+      </c>
+      <c r="C548" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D548" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="n"/>
+      <c r="H548" s="3" t="n"/>
+      <c r="I548" s="2" t="n"/>
+      <c r="J548" s="3" t="n"/>
+      <c r="K548" s="3" t="n"/>
+      <c r="L548" s="3" t="n"/>
+      <c r="M548" s="2" t="n"/>
+      <c r="N548" s="2" t="n"/>
+      <c r="O548" s="2" t="n"/>
+      <c r="P548" s="2" t="n"/>
+      <c r="Q548" s="3" t="n"/>
+      <c r="R548" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S548" s="2" t="n"/>
+      <c r="T548" s="3" t="n"/>
+      <c r="U548" s="3" t="n"/>
+      <c r="V548" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rienta-jwl-alloy-gold-plated-gold-jewellery-set/p/itm76ada1a30af30?pid=JWSGYAFYF92GWJK9</t>
+        </is>
+      </c>
+      <c r="X548" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y548" s="2" t="n"/>
+      <c r="Z548" s="2" t="n"/>
+      <c r="AA548" s="2" t="n"/>
+      <c r="AB548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rienta-jwl-alloy-gold-plated-gold-jewellery-set/p/itm76ada1a30af30?pid=JWSGYAFYF92GWJK9</t>
+        </is>
+      </c>
+      <c r="AC548" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD548" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="22" customHeight="1">
+      <c r="A549" s="5" t="inlineStr">
+        <is>
+          <t>GROWIN</t>
+        </is>
+      </c>
+      <c r="B549" s="5" t="inlineStr">
+        <is>
+          <t>GROWIN</t>
+        </is>
+      </c>
+      <c r="C549" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D549" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E549" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G549" s="5" t="n"/>
+      <c r="H549" s="6" t="n"/>
+      <c r="I549" s="5" t="n"/>
+      <c r="J549" s="6" t="n"/>
+      <c r="K549" s="6" t="n"/>
+      <c r="L549" s="6" t="n"/>
+      <c r="M549" s="5" t="n"/>
+      <c r="N549" s="5" t="n"/>
+      <c r="O549" s="5" t="n"/>
+      <c r="P549" s="5" t="n"/>
+      <c r="Q549" s="6" t="n"/>
+      <c r="R549" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S549" s="5" t="n"/>
+      <c r="T549" s="6" t="n"/>
+      <c r="U549" s="6" t="n"/>
+      <c r="V549" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W549" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ultono-metal-plastic-gold-plated-gold-jewellery-set/p/itm42964d166afd0?pid=JWSGBXWGGWHX7YFJ</t>
+        </is>
+      </c>
+      <c r="X549" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y549" s="5" t="n"/>
+      <c r="Z549" s="5" t="n"/>
+      <c r="AA549" s="5" t="n"/>
+      <c r="AB549" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ultono-metal-plastic-gold-plated-gold-jewellery-set/p/itm42964d166afd0?pid=JWSGBXWGGWHX7YFJ</t>
+        </is>
+      </c>
+      <c r="AC549" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD549" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="22" customHeight="1">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>COOKPRO</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>COOKPRO</t>
+        </is>
+      </c>
+      <c r="C550" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D550" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="n"/>
+      <c r="H550" s="3" t="n"/>
+      <c r="I550" s="2" t="n"/>
+      <c r="J550" s="3" t="n"/>
+      <c r="K550" s="3" t="n"/>
+      <c r="L550" s="3" t="n"/>
+      <c r="M550" s="2" t="n"/>
+      <c r="N550" s="2" t="n"/>
+      <c r="O550" s="2" t="n"/>
+      <c r="P550" s="2" t="n"/>
+      <c r="Q550" s="3" t="n"/>
+      <c r="R550" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S550" s="2" t="n"/>
+      <c r="T550" s="3" t="n"/>
+      <c r="U550" s="3" t="n"/>
+      <c r="V550" s="3" t="n"/>
+      <c r="W550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cookpro-kashvi-kadai-lid-tawa-sauce-pan-fry-frying-tadka-pan-cast-iron-induction-bottom-non-stick-coated-cookware-set/p/itm19b1199954c6d?pid=CKSHB3HG95SZTRFY</t>
+        </is>
+      </c>
+      <c r="X550" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y550" s="2" t="n"/>
+      <c r="Z550" s="2" t="n"/>
+      <c r="AA550" s="2" t="n"/>
+      <c r="AB550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/cookpro-kashvi-kadai-lid-tawa-sauce-pan-fry-frying-tadka-pan-cast-iron-induction-bottom-non-stick-coated-cookware-set/p/itm19b1199954c6d?pid=CKSHB3HG95SZTRFY</t>
+        </is>
+      </c>
+      <c r="AC550" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD550" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="22" customHeight="1">
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>KeComs</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="inlineStr">
+        <is>
+          <t>KeComs</t>
+        </is>
+      </c>
+      <c r="C551" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D551" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E551" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G551" s="5" t="n"/>
+      <c r="H551" s="6" t="n"/>
+      <c r="I551" s="5" t="n"/>
+      <c r="J551" s="6" t="n"/>
+      <c r="K551" s="6" t="n"/>
+      <c r="L551" s="6" t="n"/>
+      <c r="M551" s="5" t="n"/>
+      <c r="N551" s="5" t="n"/>
+      <c r="O551" s="5" t="n"/>
+      <c r="P551" s="5" t="n"/>
+      <c r="Q551" s="6" t="n"/>
+      <c r="R551" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S551" s="5" t="n"/>
+      <c r="T551" s="6" t="n"/>
+      <c r="U551" s="6" t="n"/>
+      <c r="V551" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W551" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/impex-nonstick-induction-bottom-granite-festival-giftmfkt-5-layer-super-non-stick-coated-cookware-set/p/itm120bcd2864774?pid=CKSGSSKCSRUMQ8PG</t>
+        </is>
+      </c>
+      <c r="X551" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y551" s="5" t="n"/>
+      <c r="Z551" s="5" t="n"/>
+      <c r="AA551" s="5" t="n"/>
+      <c r="AB551" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/impex-nonstick-induction-bottom-granite-festival-giftmfkt-5-layer-super-non-stick-coated-cookware-set/p/itm120bcd2864774?pid=CKSGSSKCSRUMQ8PG</t>
+        </is>
+      </c>
+      <c r="AC551" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD551" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="22" customHeight="1">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>JMD2022</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>JMD2022</t>
+        </is>
+      </c>
+      <c r="C552" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D552" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="n"/>
+      <c r="H552" s="3" t="n"/>
+      <c r="I552" s="2" t="n"/>
+      <c r="J552" s="3" t="n"/>
+      <c r="K552" s="3" t="n"/>
+      <c r="L552" s="3" t="n"/>
+      <c r="M552" s="2" t="n"/>
+      <c r="N552" s="2" t="n"/>
+      <c r="O552" s="2" t="n"/>
+      <c r="P552" s="2" t="n"/>
+      <c r="Q552" s="3" t="n"/>
+      <c r="R552" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S552" s="2" t="n"/>
+      <c r="T552" s="3" t="n"/>
+      <c r="U552" s="3" t="n"/>
+      <c r="V552" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/maharajee-cookware-set-induction-bottom-non-stick-coated/p/itm9648f5c22c19d?pid=CKSGFEF6XKEUGUGZ</t>
+        </is>
+      </c>
+      <c r="X552" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y552" s="2" t="n"/>
+      <c r="Z552" s="2" t="n"/>
+      <c r="AA552" s="2" t="n"/>
+      <c r="AB552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/maharajee-cookware-set-induction-bottom-non-stick-coated/p/itm9648f5c22c19d?pid=CKSGFEF6XKEUGUGZ</t>
+        </is>
+      </c>
+      <c r="AC552" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD552" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="22" customHeight="1">
+      <c r="A553" s="5" t="inlineStr">
+        <is>
+          <t>TBL Online</t>
+        </is>
+      </c>
+      <c r="B553" s="5" t="inlineStr">
+        <is>
+          <t>TBL Online</t>
+        </is>
+      </c>
+      <c r="C553" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D553" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E553" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F553" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G553" s="5" t="n"/>
+      <c r="H553" s="6" t="n"/>
+      <c r="I553" s="5" t="n"/>
+      <c r="J553" s="6" t="n"/>
+      <c r="K553" s="6" t="n"/>
+      <c r="L553" s="6" t="n"/>
+      <c r="M553" s="5" t="n"/>
+      <c r="N553" s="5" t="n"/>
+      <c r="O553" s="5" t="n"/>
+      <c r="P553" s="5" t="n"/>
+      <c r="Q553" s="6" t="n"/>
+      <c r="R553" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S553" s="5" t="n"/>
+      <c r="T553" s="6" t="n"/>
+      <c r="U553" s="6" t="n"/>
+      <c r="V553" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W553" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pigeon-mio-gift-set-non-stick-coated-cookware/p/itmadb105625b80c?pid=CKSEVAMZSZRHR5H4</t>
+        </is>
+      </c>
+      <c r="X553" s="5" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y553" s="5" t="n"/>
+      <c r="Z553" s="5" t="n"/>
+      <c r="AA553" s="5" t="n"/>
+      <c r="AB553" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/pigeon-mio-gift-set-non-stick-coated-cookware/p/itmadb105625b80c?pid=CKSEVAMZSZRHR5H4</t>
+        </is>
+      </c>
+      <c r="AC553" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD553" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="22" customHeight="1">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Kaashvii</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>Kaashvii</t>
+        </is>
+      </c>
+      <c r="C554" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D554" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="n"/>
+      <c r="H554" s="3" t="n"/>
+      <c r="I554" s="2" t="n"/>
+      <c r="J554" s="3" t="n"/>
+      <c r="K554" s="3" t="n"/>
+      <c r="L554" s="3" t="n"/>
+      <c r="M554" s="2" t="n"/>
+      <c r="N554" s="2" t="n"/>
+      <c r="O554" s="2" t="n"/>
+      <c r="P554" s="2" t="n"/>
+      <c r="Q554" s="3" t="n"/>
+      <c r="R554" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S554" s="2" t="n"/>
+      <c r="T554" s="3" t="n"/>
+      <c r="U554" s="3" t="n"/>
+      <c r="V554" s="3" t="n"/>
+      <c r="W554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kashvi-new25-premium-cookware-set-5-pcs-tawa-kadhai-frypan-saucepan-tadka-induction-bottom-non-stick-coated/p/itme457e25108656?pid=CKSHGGFAWBVYX5BH</t>
+        </is>
+      </c>
+      <c r="X554" s="2" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="Y554" s="2" t="n"/>
+      <c r="Z554" s="2" t="n"/>
+      <c r="AA554" s="2" t="n"/>
+      <c r="AB554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/kashvi-new25-premium-cookware-set-5-pcs-tawa-kadhai-frypan-saucepan-tadka-induction-bottom-non-stick-coated/p/itme457e25108656?pid=CKSHGGFAWBVYX5BH</t>
+        </is>
+      </c>
+      <c r="AC554" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD554" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="22" customHeight="1">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>WORLDS SPORTS</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="inlineStr">
+        <is>
+          <t>WORLDS SPORTS</t>
+        </is>
+      </c>
+      <c r="C555" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D555" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E555" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G555" s="5" t="n"/>
+      <c r="H555" s="6" t="n"/>
+      <c r="I555" s="5" t="n"/>
+      <c r="J555" s="6" t="n"/>
+      <c r="K555" s="6" t="n"/>
+      <c r="L555" s="6" t="n"/>
+      <c r="M555" s="5" t="n"/>
+      <c r="N555" s="5" t="n"/>
+      <c r="O555" s="5" t="n"/>
+      <c r="P555" s="5" t="n"/>
+      <c r="Q555" s="6" t="n"/>
+      <c r="R555" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S555" s="5" t="n"/>
+      <c r="T555" s="6" t="n"/>
+      <c r="U555" s="6" t="n"/>
+      <c r="V555" s="6" t="n"/>
+      <c r="W555" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/world-sports-printed-men-round-neck-multicolor-t-shirt/p/itm2c27e234ea316?pid=TSHGYK9GW2HKSC8H</t>
+        </is>
+      </c>
+      <c r="X555" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y555" s="5" t="n"/>
+      <c r="Z555" s="5" t="n"/>
+      <c r="AA555" s="5" t="n"/>
+      <c r="AB555" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/world-sports-printed-men-round-neck-multicolor-t-shirt/p/itm2c27e234ea316?pid=TSHGYK9GW2HKSC8H</t>
+        </is>
+      </c>
+      <c r="AC555" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD555" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="22" customHeight="1">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>ricpolesports</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>ricpolesports</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D556" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="n"/>
+      <c r="H556" s="3" t="n"/>
+      <c r="I556" s="2" t="n"/>
+      <c r="J556" s="3" t="n"/>
+      <c r="K556" s="3" t="n"/>
+      <c r="L556" s="3" t="n"/>
+      <c r="M556" s="2" t="n"/>
+      <c r="N556" s="2" t="n"/>
+      <c r="O556" s="2" t="n"/>
+      <c r="P556" s="2" t="n"/>
+      <c r="Q556" s="3" t="n"/>
+      <c r="R556" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S556" s="2" t="n"/>
+      <c r="T556" s="3" t="n"/>
+      <c r="U556" s="3" t="n"/>
+      <c r="V556" s="3" t="n"/>
+      <c r="W556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sportify-printed-men-round-neck-orange-t-shirt/p/itm61e2d2d56b886?pid=TSHHNJCATAPGMNNB</t>
+        </is>
+      </c>
+      <c r="X556" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y556" s="2" t="n"/>
+      <c r="Z556" s="2" t="n"/>
+      <c r="AA556" s="2" t="n"/>
+      <c r="AB556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/sportify-printed-men-round-neck-orange-t-shirt/p/itm61e2d2d56b886?pid=TSHHNJCATAPGMNNB</t>
+        </is>
+      </c>
+      <c r="AC556" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD556" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="22" customHeight="1">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>speed sports</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="inlineStr">
+        <is>
+          <t>speed sports</t>
+        </is>
+      </c>
+      <c r="C557" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D557" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F557" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G557" s="5" t="n"/>
+      <c r="H557" s="6" t="n"/>
+      <c r="I557" s="5" t="n"/>
+      <c r="J557" s="6" t="n"/>
+      <c r="K557" s="6" t="n"/>
+      <c r="L557" s="6" t="n"/>
+      <c r="M557" s="5" t="n"/>
+      <c r="N557" s="5" t="n"/>
+      <c r="O557" s="5" t="n"/>
+      <c r="P557" s="5" t="n"/>
+      <c r="Q557" s="6" t="n"/>
+      <c r="R557" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S557" s="5" t="n"/>
+      <c r="T557" s="6" t="n"/>
+      <c r="U557" s="6" t="n"/>
+      <c r="V557" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W557" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gymfit-printed-men-polo-neck-blue-t-shirt/p/itm47c8feee4011b?pid=TSHH93C3DQDF3H5U</t>
+        </is>
+      </c>
+      <c r="X557" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y557" s="5" t="n"/>
+      <c r="Z557" s="5" t="n"/>
+      <c r="AA557" s="5" t="n"/>
+      <c r="AB557" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/gymfit-printed-men-polo-neck-blue-t-shirt/p/itm47c8feee4011b?pid=TSHH93C3DQDF3H5U</t>
+        </is>
+      </c>
+      <c r="AC557" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD557" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="22" customHeight="1">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>NKRFASHIONS</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>NKRFASHIONS</t>
+        </is>
+      </c>
+      <c r="C558" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D558" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="n"/>
+      <c r="H558" s="3" t="n"/>
+      <c r="I558" s="2" t="n"/>
+      <c r="J558" s="3" t="n"/>
+      <c r="K558" s="3" t="n"/>
+      <c r="L558" s="3" t="n"/>
+      <c r="M558" s="2" t="n"/>
+      <c r="N558" s="2" t="n"/>
+      <c r="O558" s="2" t="n"/>
+      <c r="P558" s="2" t="n"/>
+      <c r="Q558" s="3" t="n"/>
+      <c r="R558" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S558" s="2" t="n"/>
+      <c r="T558" s="3" t="n"/>
+      <c r="U558" s="3" t="n"/>
+      <c r="V558" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ryze-printed-men-round-neck-orange-t-shirt/p/itmd7b1666a8ac23?pid=TSHHJ38SHS9HAV9U</t>
+        </is>
+      </c>
+      <c r="X558" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y558" s="2" t="n"/>
+      <c r="Z558" s="2" t="n"/>
+      <c r="AA558" s="2" t="n"/>
+      <c r="AB558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ryze-printed-men-round-neck-orange-t-shirt/p/itmd7b1666a8ac23?pid=TSHHJ38SHS9HAV9U</t>
+        </is>
+      </c>
+      <c r="AC558" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD558" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="22" customHeight="1">
+      <c r="A559" s="5" t="inlineStr">
+        <is>
+          <t>SSASOLUTION</t>
+        </is>
+      </c>
+      <c r="B559" s="5" t="inlineStr">
+        <is>
+          <t>SSASOLUTION</t>
+        </is>
+      </c>
+      <c r="C559" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E559" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F559" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G559" s="5" t="n"/>
+      <c r="H559" s="6" t="n"/>
+      <c r="I559" s="5" t="n"/>
+      <c r="J559" s="6" t="n"/>
+      <c r="K559" s="6" t="n"/>
+      <c r="L559" s="6" t="n"/>
+      <c r="M559" s="5" t="n"/>
+      <c r="N559" s="5" t="n"/>
+      <c r="O559" s="5" t="n"/>
+      <c r="P559" s="5" t="n"/>
+      <c r="Q559" s="6" t="n"/>
+      <c r="R559" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S559" s="5" t="n"/>
+      <c r="T559" s="6" t="n"/>
+      <c r="U559" s="6" t="n"/>
+      <c r="V559" s="6" t="n"/>
+      <c r="W559" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tshirt-men-sporty-round-neck-navy-blue-t-shirt/p/itm201fb1aac6d0a?pid=TSHH2CB4HNFGPXGG</t>
+        </is>
+      </c>
+      <c r="X559" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y559" s="5" t="n"/>
+      <c r="Z559" s="5" t="n"/>
+      <c r="AA559" s="5" t="n"/>
+      <c r="AB559" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tshirt-men-sporty-round-neck-navy-blue-t-shirt/p/itm201fb1aac6d0a?pid=TSHH2CB4HNFGPXGG</t>
+        </is>
+      </c>
+      <c r="AC559" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD559" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="22" customHeight="1">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>OnlineStores1</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>OnlineStores1</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D560" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="n"/>
+      <c r="H560" s="3" t="n"/>
+      <c r="I560" s="2" t="n"/>
+      <c r="J560" s="3" t="n"/>
+      <c r="K560" s="3" t="n"/>
+      <c r="L560" s="3" t="n"/>
+      <c r="M560" s="2" t="n"/>
+      <c r="N560" s="2" t="n"/>
+      <c r="O560" s="2" t="n"/>
+      <c r="P560" s="2" t="n"/>
+      <c r="Q560" s="3" t="n"/>
+      <c r="R560" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S560" s="2" t="n"/>
+      <c r="T560" s="3" t="n"/>
+      <c r="U560" s="3" t="n"/>
+      <c r="V560" s="3" t="n"/>
+      <c r="W560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ilyk-printed-men-round-neck-red-white-t-shirt/p/itm82fc344b88764?pid=TSHHPHUR2ZYKW6SS</t>
+        </is>
+      </c>
+      <c r="X560" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y560" s="2" t="n"/>
+      <c r="Z560" s="2" t="n"/>
+      <c r="AA560" s="2" t="n"/>
+      <c r="AB560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ilyk-printed-men-round-neck-red-white-t-shirt/p/itm82fc344b88764?pid=TSHHPHUR2ZYKW6SS</t>
+        </is>
+      </c>
+      <c r="AC560" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD560" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="22" customHeight="1">
+      <c r="A561" s="5" t="inlineStr">
+        <is>
+          <t>VAIBHAVFABRICS</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="inlineStr">
+        <is>
+          <t>VAIBHAVFABRICS</t>
+        </is>
+      </c>
+      <c r="C561" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D561" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G561" s="5" t="n"/>
+      <c r="H561" s="6" t="n"/>
+      <c r="I561" s="5" t="n"/>
+      <c r="J561" s="6" t="n"/>
+      <c r="K561" s="6" t="n"/>
+      <c r="L561" s="6" t="n"/>
+      <c r="M561" s="5" t="n"/>
+      <c r="N561" s="5" t="n"/>
+      <c r="O561" s="5" t="n"/>
+      <c r="P561" s="5" t="n"/>
+      <c r="Q561" s="6" t="n"/>
+      <c r="R561" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S561" s="5" t="n"/>
+      <c r="T561" s="6" t="n"/>
+      <c r="U561" s="6" t="n"/>
+      <c r="V561" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W561" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rf-raves-colorblock-men-polo-neck-black-t-shirt/p/itm7c02df0d18281?pid=TSHHJ8X3Z286FYHT</t>
+        </is>
+      </c>
+      <c r="X561" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y561" s="5" t="n"/>
+      <c r="Z561" s="5" t="n"/>
+      <c r="AA561" s="5" t="n"/>
+      <c r="AB561" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/rf-raves-colorblock-men-polo-neck-black-t-shirt/p/itm7c02df0d18281?pid=TSHHJ8X3Z286FYHT</t>
+        </is>
+      </c>
+      <c r="AC561" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD561" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="22" customHeight="1">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>JJTEES</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>JJTEES</t>
+        </is>
+      </c>
+      <c r="C562" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D562" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="n"/>
+      <c r="H562" s="3" t="n"/>
+      <c r="I562" s="2" t="n"/>
+      <c r="J562" s="3" t="n"/>
+      <c r="K562" s="3" t="n"/>
+      <c r="L562" s="3" t="n"/>
+      <c r="M562" s="2" t="n"/>
+      <c r="N562" s="2" t="n"/>
+      <c r="O562" s="2" t="n"/>
+      <c r="P562" s="2" t="n"/>
+      <c r="Q562" s="3" t="n"/>
+      <c r="R562" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S562" s="2" t="n"/>
+      <c r="T562" s="3" t="n"/>
+      <c r="U562" s="3" t="n"/>
+      <c r="V562" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jj-tees-printed-men-round-neck-multicolor-t-shirt/p/itma9b291eb8a4d5?pid=TSHG2A6XHNZCMHKY</t>
+        </is>
+      </c>
+      <c r="X562" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y562" s="2" t="n"/>
+      <c r="Z562" s="2" t="n"/>
+      <c r="AA562" s="2" t="n"/>
+      <c r="AB562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jj-tees-printed-men-round-neck-multicolor-t-shirt/p/itma9b291eb8a4d5?pid=TSHG2A6XHNZCMHKY</t>
+        </is>
+      </c>
+      <c r="AC562" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD562" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="22" customHeight="1">
+      <c r="A563" s="5" t="inlineStr">
+        <is>
+          <t>YuvaGarment</t>
+        </is>
+      </c>
+      <c r="B563" s="5" t="inlineStr">
+        <is>
+          <t>YuvaGarment</t>
+        </is>
+      </c>
+      <c r="C563" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D563" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F563" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G563" s="5" t="n"/>
+      <c r="H563" s="6" t="n"/>
+      <c r="I563" s="5" t="n"/>
+      <c r="J563" s="6" t="n"/>
+      <c r="K563" s="6" t="n"/>
+      <c r="L563" s="6" t="n"/>
+      <c r="M563" s="5" t="n"/>
+      <c r="N563" s="5" t="n"/>
+      <c r="O563" s="5" t="n"/>
+      <c r="P563" s="5" t="n"/>
+      <c r="Q563" s="6" t="n"/>
+      <c r="R563" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S563" s="5" t="n"/>
+      <c r="T563" s="6" t="n"/>
+      <c r="U563" s="6" t="n"/>
+      <c r="V563" s="6" t="n"/>
+      <c r="W563" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ockler-sport-colorblock-men-round-neck-light-green-t-shirt/p/itmb15790fd6d240?pid=TSHHPZXFWDGYGQA7</t>
+        </is>
+      </c>
+      <c r="X563" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y563" s="5" t="n"/>
+      <c r="Z563" s="5" t="n"/>
+      <c r="AA563" s="5" t="n"/>
+      <c r="AB563" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/ockler-sport-colorblock-men-round-neck-light-green-t-shirt/p/itmb15790fd6d240?pid=TSHHPZXFWDGYGQA7</t>
+        </is>
+      </c>
+      <c r="AC563" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD563" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="22" customHeight="1">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>SRTradingC</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>SRTradingC</t>
+        </is>
+      </c>
+      <c r="C564" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D564" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="n"/>
+      <c r="H564" s="3" t="n"/>
+      <c r="I564" s="2" t="n"/>
+      <c r="J564" s="3" t="n"/>
+      <c r="K564" s="3" t="n"/>
+      <c r="L564" s="3" t="n"/>
+      <c r="M564" s="2" t="n"/>
+      <c r="N564" s="2" t="n"/>
+      <c r="O564" s="2" t="n"/>
+      <c r="P564" s="2" t="n"/>
+      <c r="Q564" s="3" t="n"/>
+      <c r="R564" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S564" s="2" t="n"/>
+      <c r="T564" s="3" t="n"/>
+      <c r="U564" s="3" t="n"/>
+      <c r="V564" s="3" t="n"/>
+      <c r="W564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/farccilu-graphic-print-men-round-neck-dark-blue-blue-t-shirt/p/itm9f77f7e3a5f6c?pid=TSHHNJ9PW2W9GJS8</t>
+        </is>
+      </c>
+      <c r="X564" s="2" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y564" s="2" t="n"/>
+      <c r="Z564" s="2" t="n"/>
+      <c r="AA564" s="2" t="n"/>
+      <c r="AB564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/farccilu-graphic-print-men-round-neck-dark-blue-blue-t-shirt/p/itm9f77f7e3a5f6c?pid=TSHHNJ9PW2W9GJS8</t>
+        </is>
+      </c>
+      <c r="AC564" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD564" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="22" customHeight="1">
+      <c r="A565" s="5" t="inlineStr">
+        <is>
+          <t>ZVON</t>
+        </is>
+      </c>
+      <c r="B565" s="5" t="inlineStr">
+        <is>
+          <t>ZVON</t>
+        </is>
+      </c>
+      <c r="C565" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D565" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="G565" s="5" t="n"/>
+      <c r="H565" s="6" t="n"/>
+      <c r="I565" s="5" t="n"/>
+      <c r="J565" s="6" t="n"/>
+      <c r="K565" s="6" t="n"/>
+      <c r="L565" s="6" t="n"/>
+      <c r="M565" s="5" t="n"/>
+      <c r="N565" s="5" t="n"/>
+      <c r="O565" s="5" t="n"/>
+      <c r="P565" s="5" t="n"/>
+      <c r="Q565" s="6" t="n"/>
+      <c r="R565" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S565" s="5" t="n"/>
+      <c r="T565" s="6" t="n"/>
+      <c r="U565" s="6" t="n"/>
+      <c r="V565" s="6" t="n"/>
+      <c r="W565" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zvon-printed-men-round-neck-white-t-shirt/p/itme16489087e851?pid=TSHHPHRYNGRC2WKJ</t>
+        </is>
+      </c>
+      <c r="X565" s="5" t="inlineStr">
+        <is>
+          <t>Sports T-Shirts &amp; Jerseys</t>
+        </is>
+      </c>
+      <c r="Y565" s="5" t="n"/>
+      <c r="Z565" s="5" t="n"/>
+      <c r="AA565" s="5" t="n"/>
+      <c r="AB565" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/zvon-printed-men-round-neck-white-t-shirt/p/itme16489087e851?pid=TSHHPHRYNGRC2WKJ</t>
+        </is>
+      </c>
+      <c r="AC565" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD565" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="22" customHeight="1">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>PremsaEnterprises</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>PremsaEnterprises</t>
+        </is>
+      </c>
+      <c r="C566" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D566" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="n"/>
+      <c r="H566" s="3" t="n"/>
+      <c r="I566" s="2" t="n"/>
+      <c r="J566" s="3" t="n"/>
+      <c r="K566" s="3" t="n"/>
+      <c r="L566" s="3" t="n"/>
+      <c r="M566" s="2" t="n"/>
+      <c r="N566" s="2" t="n"/>
+      <c r="O566" s="2" t="n"/>
+      <c r="P566" s="2" t="n"/>
+      <c r="Q566" s="3" t="n"/>
+      <c r="R566" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S566" s="2" t="n"/>
+      <c r="T566" s="3" t="n"/>
+      <c r="U566" s="3" t="n"/>
+      <c r="V566" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lripsome-full-sleeve-solid-men-sweatshirt/p/itm72a67243d0d24?pid=SWSGFWGHYSZ5MBEZ</t>
+        </is>
+      </c>
+      <c r="X566" s="2" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
+      <c r="Y566" s="2" t="n"/>
+      <c r="Z566" s="2" t="n"/>
+      <c r="AA566" s="2" t="n"/>
+      <c r="AB566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/lripsome-full-sleeve-solid-men-sweatshirt/p/itm72a67243d0d24?pid=SWSGFWGHYSZ5MBEZ</t>
+        </is>
+      </c>
+      <c r="AC566" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD566" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="22" customHeight="1">
+      <c r="A567" s="5" t="inlineStr">
+        <is>
+          <t>FLYIND</t>
+        </is>
+      </c>
+      <c r="B567" s="5" t="inlineStr">
+        <is>
+          <t>FLYIND</t>
+        </is>
+      </c>
+      <c r="C567" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D567" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E567" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F567" s="5" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
+      <c r="G567" s="5" t="n"/>
+      <c r="H567" s="6" t="n"/>
+      <c r="I567" s="5" t="n"/>
+      <c r="J567" s="6" t="n"/>
+      <c r="K567" s="6" t="n"/>
+      <c r="L567" s="6" t="n"/>
+      <c r="M567" s="5" t="n"/>
+      <c r="N567" s="5" t="n"/>
+      <c r="O567" s="5" t="n"/>
+      <c r="P567" s="5" t="n"/>
+      <c r="Q567" s="6" t="n"/>
+      <c r="R567" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S567" s="5" t="n"/>
+      <c r="T567" s="6" t="n"/>
+      <c r="U567" s="6" t="n"/>
+      <c r="V567" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W567" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/flyind-outfit-full-sleeve-graphic-print-men-women-sweatshirt/p/itmc2391ebd43285?pid=SWSH4E9KHDC5KUHH</t>
+        </is>
+      </c>
+      <c r="X567" s="5" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
+      <c r="Y567" s="5" t="n"/>
+      <c r="Z567" s="5" t="n"/>
+      <c r="AA567" s="5" t="n"/>
+      <c r="AB567" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/flyind-outfit-full-sleeve-graphic-print-men-women-sweatshirt/p/itmc2391ebd43285?pid=SWSH4E9KHDC5KUHH</t>
+        </is>
+      </c>
+      <c r="AC567" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD567" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="22" customHeight="1">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>FabrrinityFashion</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>FabrrinityFashion</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D568" s="4" t="inlineStr">
+        <is>
+          <t>ENRICHMENT_PENDING</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="n"/>
+      <c r="F568" s="2" t="n"/>
+      <c r="G568" s="2" t="n"/>
+      <c r="H568" s="3" t="n"/>
+      <c r="I568" s="2" t="n"/>
+      <c r="J568" s="3" t="n"/>
+      <c r="K568" s="3" t="n"/>
+      <c r="L568" s="3" t="n"/>
+      <c r="M568" s="2" t="n"/>
+      <c r="N568" s="2" t="n"/>
+      <c r="O568" s="2" t="n"/>
+      <c r="P568" s="2" t="n"/>
+      <c r="Q568" s="3" t="n"/>
+      <c r="R568" s="2" t="n"/>
+      <c r="S568" s="2" t="n"/>
+      <c r="T568" s="3" t="n"/>
+      <c r="U568" s="3" t="n"/>
+      <c r="V568" s="3" t="n"/>
+      <c r="W568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/speed-horse-full-sleeve-graphic-print-boys-sweatshirt/p/itm61c4631fb78f9?pid=SWSHNZZRCHCGQHGM</t>
+        </is>
+      </c>
+      <c r="X568" s="2" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
+      <c r="Y568" s="2" t="n"/>
+      <c r="Z568" s="2" t="n"/>
+      <c r="AA568" s="2" t="n"/>
+      <c r="AB568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/speed-horse-full-sleeve-graphic-print-boys-sweatshirt/p/itm61c4631fb78f9?pid=SWSHNZZRCHCGQHGM</t>
+        </is>
+      </c>
+      <c r="AC568" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD568" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/flipkart_sellers.xlsx
+++ b/output/flipkart_sellers.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD568"/>
+  <dimension ref="A1:AD580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -743,9 +743,9 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>NEEDS_REVIEW</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Electronics &gt; Audio</t>
+          <t>Electronics &gt; Audio &gt; Headphones &gt; Wireless Earbuds</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Road, Mumbai, Maharashtra-400093</t>
+          <t>&amp; Achievements CONTACT US Nampa 2175 N. Samantha CT. Nampa, ID 83687 208-459-7777 Burley 2165 Overland Ave. Burley, ID 833318 208-678-5869</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Road, Mumbai, Maharashtra-400093</t>
+          <t>&amp; Achievements CONTACT US Nampa 2175 N. Samantha CT. Nampa, ID 83687 208-459-7777 Burley 2165 Overland Ave. Burley, ID 833318 208-678-5869</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>400093</t>
+          <t>833318</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.boat-lifestyle.com</t>
+          <t>https://idahowatersports.com</t>
         </is>
       </c>
       <c r="T2" s="3" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Electronics &gt; Audio</t>
+          <t>Electronics &gt; Audio &gt; Headphones &gt; Wireless Earbuds</t>
         </is>
       </c>
       <c r="Y2" s="2" t="n"/>
@@ -843,29 +843,29 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>targeted_search, company_website</t>
+          <t>company_website</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Hsatlastradefashion</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>HSAtlastradeFashion</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>HSAtlastradeFashion</t>
-        </is>
-      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Bottom Wear</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -926,16 +926,16 @@
       <c r="T3" s="6" t="n"/>
       <c r="U3" s="6" t="n"/>
       <c r="V3" s="6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="W3" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/sassafras-relaxed-women-black-trousers/p/itmdf31fe89be36d?pid=TROFVB5HNUN63XCS</t>
+          <t>https://www.flipkart.com/peter-england-2-piece-suit-solid-men/p/itm6705071169790?pid=SUIGFXFCWKU5NZGZ</t>
         </is>
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Bottom Wear</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="Y3" s="5" t="n"/>
@@ -943,7 +943,7 @@
       <c r="AA3" s="5" t="n"/>
       <c r="AB3" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/sassafras-relaxed-women-black-trousers/p/itmdf31fe89be36d?pid=TROFVB5HNUN63XCS</t>
+          <t>https://www.flipkart.com/peter-england-2-piece-suit-solid-men/p/itm6705071169790?pid=SUIGFXFCWKU5NZGZ</t>
         </is>
       </c>
       <c r="AC3" s="5" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AD3" s="5" t="inlineStr">
         <is>
-          <t>company_website, public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3755,19 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Proprietorship / Registered Business</t>
+          <t>B2C / Retail</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Women's Fotwear &gt; Women's Flats</t>
+          <t>Suit Trousers</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3830,16 +3830,16 @@
       <c r="T37" s="6" t="n"/>
       <c r="U37" s="6" t="n"/>
       <c r="V37" s="6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="W37" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/el-paso-women-flats/p/itm11a3186eab928?pid=SNDHFV5GCPQGZNUR</t>
+          <t>https://www.flipkart.com/indo-era-women-kurta-pant-dupatta-set/p/itm2735cc0b2568b?pid=ETHHYY36KVRDNWXG</t>
         </is>
       </c>
       <c r="X37" s="5" t="inlineStr">
         <is>
-          <t>Women's Fotwear &gt; Women's Flats</t>
+          <t>Suit Trousers</t>
         </is>
       </c>
       <c r="Y37" s="5" t="n"/>
@@ -3847,7 +3847,7 @@
       <c r="AA37" s="5" t="n"/>
       <c r="AB37" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/el-paso-women-flats/p/itm11a3186eab928?pid=SNDHFV5GCPQGZNUR</t>
+          <t>https://www.flipkart.com/indo-era-women-kurta-pant-dupatta-set/p/itm2735cc0b2568b?pid=ETHHYY36KVRDNWXG</t>
         </is>
       </c>
       <c r="AC37" s="5" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="AD37" s="5" t="inlineStr">
         <is>
-          <t>public_search, company_website</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -22184,14 +22184,14 @@
     <row r="267" ht="22" customHeight="1">
       <c r="A267" s="5" t="inlineStr">
         <is>
+          <t>Maksudenterprise</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
           <t>MAKSUDENTERPRISE</t>
         </is>
       </c>
-      <c r="B267" s="5" t="inlineStr">
-        <is>
-          <t>MAKSUDENTERPRISE</t>
-        </is>
-      </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="G267" s="5" t="n"/>
@@ -22232,16 +22232,16 @@
       <c r="T267" s="6" t="n"/>
       <c r="U267" s="6" t="n"/>
       <c r="V267" s="6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W267" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/maksud-enterprise-solid-men-waistcoat/p/itm548d8a949c322?pid=WSCGF4ESHSG3MZFR</t>
+          <t>https://www.flipkart.com/maksud-enterprise-solid-men-waistcoat/p/itm3adc5f0a02d50?pid=WSCGGFF9BHECP78U</t>
         </is>
       </c>
       <c r="X267" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="Y267" s="5" t="n"/>
@@ -22249,7 +22249,7 @@
       <c r="AA267" s="5" t="n"/>
       <c r="AB267" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/maksud-enterprise-solid-men-waistcoat/p/itm548d8a949c322?pid=WSCGF4ESHSG3MZFR</t>
+          <t>https://www.flipkart.com/maksud-enterprise-solid-men-waistcoat/p/itm3adc5f0a02d50?pid=WSCGGFF9BHECP78U</t>
         </is>
       </c>
       <c r="AC267" s="5" t="inlineStr">
@@ -22266,14 +22266,14 @@
     <row r="268" ht="22" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
+          <t>Clothifyusha</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
           <t>ClothifyUsha</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>ClothifyUsha</t>
-        </is>
-      </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -22314,7 +22314,7 @@
       <c r="T268" s="3" t="n"/>
       <c r="U268" s="3" t="n"/>
       <c r="V268" s="3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W268" s="2" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
       </c>
       <c r="X268" s="2" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="Y268" s="2" t="n"/>
@@ -22348,14 +22348,14 @@
     <row r="269" ht="22" customHeight="1">
       <c r="A269" s="5" t="inlineStr">
         <is>
+          <t>Carcolaritailnet</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
           <t>CARCOLARITAILNET</t>
         </is>
       </c>
-      <c r="B269" s="5" t="inlineStr">
-        <is>
-          <t>CARCOLARITAILNET</t>
-        </is>
-      </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="G269" s="5" t="n"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="X269" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="Y269" s="5" t="n"/>
@@ -22760,22 +22760,22 @@
     <row r="274" ht="22" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
+          <t>Rntradingco</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>RNTRADINGCO</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>RNTRADINGCO</t>
-        </is>
-      </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D274" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
+      <c r="D274" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -22785,7 +22785,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Suit Jackets</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -22835,15 +22835,17 @@
       </c>
       <c r="T274" s="3" t="n"/>
       <c r="U274" s="3" t="n"/>
-      <c r="V274" s="3" t="n"/>
+      <c r="V274" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="W274" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/paryushnam-party-wear-kids-boy-dress-suit-set-coat-pant-full-clothes-self-design-boys/p/itm46df225668c7a?pid=SUIHPNAYKVJEH6SY</t>
+          <t>https://www.flipkart.com/paryushnam-boys-festive-party-wedding-blazer-pant-set/p/itm08079d754fc42?pid=KETHQ9E6BJZYGZNQ</t>
         </is>
       </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Suit Jackets</t>
         </is>
       </c>
       <c r="Y274" s="2" t="n"/>
@@ -22851,7 +22853,7 @@
       <c r="AA274" s="2" t="n"/>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/paryushnam-party-wear-kids-boy-dress-suit-set-coat-pant-full-clothes-self-design-boys/p/itm46df225668c7a?pid=SUIHPNAYKVJEH6SY</t>
+          <t>https://www.flipkart.com/paryushnam-boys-festive-party-wedding-blazer-pant-set/p/itm08079d754fc42?pid=KETHQ9E6BJZYGZNQ</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
@@ -22861,7 +22863,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>company_website, public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -22881,9 +22883,9 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D275" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_REVIEW</t>
+      <c r="D275" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
@@ -22893,7 +22895,7 @@
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="G275" s="5" t="n"/>
@@ -22929,7 +22931,7 @@
       </c>
       <c r="X275" s="5" t="inlineStr">
         <is>
-          <t>Blazers, Waistcoats &amp; Suits</t>
+          <t>Blazers, Waistcoats &amp; Suits &gt; Suits</t>
         </is>
       </c>
       <c r="Y275" s="5" t="n"/>
@@ -22947,7 +22949,7 @@
       </c>
       <c r="AD275" s="5" t="inlineStr">
         <is>
-          <t>public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -23048,14 +23050,14 @@
     <row r="277" ht="22" customHeight="1">
       <c r="A277" s="5" t="inlineStr">
         <is>
+          <t>Menrocks</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
           <t>MenRocks</t>
         </is>
       </c>
-      <c r="B277" s="5" t="inlineStr">
-        <is>
-          <t>MenRocks</t>
-        </is>
-      </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
@@ -23073,7 +23075,7 @@
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Sports T-Shirts &amp; Jerseys</t>
         </is>
       </c>
       <c r="G277" s="5" t="n"/>
@@ -23096,16 +23098,16 @@
       <c r="T277" s="6" t="n"/>
       <c r="U277" s="6" t="n"/>
       <c r="V277" s="6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="W277" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/eyebogler-self-design-men-round-neck-black-t-shirt/p/itmf553e2385eb87?pid=TSHH8FHZXG7RR8TY</t>
+          <t>https://www.flipkart.com/eyebogler-colorblock-men-zip-neck-black-grey-t-shirt/p/itm874c7bbf24f9d?pid=TSHHNVDMEFAFXBYG</t>
         </is>
       </c>
       <c r="X277" s="5" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Sports T-Shirts &amp; Jerseys</t>
         </is>
       </c>
       <c r="Y277" s="5" t="n"/>
@@ -23113,7 +23115,7 @@
       <c r="AA277" s="5" t="n"/>
       <c r="AB277" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/eyebogler-self-design-men-round-neck-black-t-shirt/p/itmf553e2385eb87?pid=TSHH8FHZXG7RR8TY</t>
+          <t>https://www.flipkart.com/eyebogler-colorblock-men-zip-neck-black-grey-t-shirt/p/itm874c7bbf24f9d?pid=TSHHNVDMEFAFXBYG</t>
         </is>
       </c>
       <c r="AC277" s="5" t="inlineStr">
@@ -23294,22 +23296,22 @@
     <row r="280" ht="22" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
+          <t>Ninq</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
           <t>NINQ</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>NINQ</t>
-        </is>
-      </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D280" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -23319,7 +23321,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Tights</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -23350,16 +23352,16 @@
       <c r="T280" s="3" t="n"/>
       <c r="U280" s="3" t="n"/>
       <c r="V280" s="3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="W280" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/ninq-solid-men-round-neck-black-t-shirt/p/itm22792ec0f2e87?pid=TSHHFVCTUZPSAHMD</t>
+          <t>https://www.flipkart.com/ninq-solid-men-black-tights/p/itm9fd6dec67ba75?pid=TGTGXJP3E86U5RZR</t>
         </is>
       </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Tights</t>
         </is>
       </c>
       <c r="Y280" s="2" t="n"/>
@@ -23367,7 +23369,7 @@
       <c r="AA280" s="2" t="n"/>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/ninq-solid-men-round-neck-black-t-shirt/p/itm22792ec0f2e87?pid=TSHHFVCTUZPSAHMD</t>
+          <t>https://www.flipkart.com/ninq-solid-men-black-tights/p/itm9fd6dec67ba75?pid=TGTGXJP3E86U5RZR</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
@@ -23377,7 +23379,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -23502,22 +23504,22 @@
     <row r="282" ht="22" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
+          <t>Sportspal</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
           <t>SPORTSPAL</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>SPORTSPAL</t>
-        </is>
-      </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D282" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY_VERIFIED</t>
+      <c r="D282" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -23527,7 +23529,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Tights</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -23578,16 +23580,16 @@
       <c r="T282" s="3" t="n"/>
       <c r="U282" s="3" t="n"/>
       <c r="V282" s="3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="W282" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/kyk-solid-men-round-neck-black-t-shirt/p/itm8c415b7f0dcd6?pid=TSHGZEZ8H3BGPGUZ</t>
+          <t>https://www.flipkart.com/wmx-solid-men-black-tights/p/itm02a71e13fbcb0?pid=TGTGNZEHUN6RZSDH</t>
         </is>
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Tights</t>
         </is>
       </c>
       <c r="Y282" s="2" t="n"/>
@@ -23595,7 +23597,7 @@
       <c r="AA282" s="2" t="n"/>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/kyk-solid-men-round-neck-black-t-shirt/p/itm8c415b7f0dcd6?pid=TSHGZEZ8H3BGPGUZ</t>
+          <t>https://www.flipkart.com/wmx-solid-men-black-tights/p/itm02a71e13fbcb0?pid=TGTGNZEHUN6RZSDH</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
@@ -23605,29 +23607,29 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>company_website, public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
     <row r="283" ht="22" customHeight="1">
       <c r="A283" s="5" t="inlineStr">
         <is>
+          <t>Tribhuvanapparels</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
           <t>TribhuvanApparels</t>
         </is>
       </c>
-      <c r="B283" s="5" t="inlineStr">
-        <is>
-          <t>TribhuvanApparels</t>
-        </is>
-      </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D283" s="9" t="inlineStr">
-        <is>
-          <t>NEEDS_REVIEW</t>
+      <c r="D283" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
@@ -23637,7 +23639,7 @@
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Sports T-Shirts &amp; Jerseys</t>
         </is>
       </c>
       <c r="G283" s="5" t="n"/>
@@ -23684,16 +23686,16 @@
       <c r="T283" s="6" t="n"/>
       <c r="U283" s="6" t="n"/>
       <c r="V283" s="6" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="W283" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/sportz-fit-solid-men-round-neck-green-t-shirt/p/itm858c78e5a30b3?pid=TSHHHDYUJPFJSRDJ</t>
+          <t>https://www.flipkart.com/sportz-fit-solid-men-polo-neck-blue-t-shirt/p/itm627ad8bdefee6?pid=TSHHGS6JC9HWHFVR</t>
         </is>
       </c>
       <c r="X283" s="5" t="inlineStr">
         <is>
-          <t>Sportswear</t>
+          <t>Sports T-Shirts &amp; Jerseys</t>
         </is>
       </c>
       <c r="Y283" s="5" t="n"/>
@@ -23701,7 +23703,7 @@
       <c r="AA283" s="5" t="n"/>
       <c r="AB283" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/sportz-fit-solid-men-round-neck-green-t-shirt/p/itm858c78e5a30b3?pid=TSHHHDYUJPFJSRDJ</t>
+          <t>https://www.flipkart.com/sportz-fit-solid-men-polo-neck-blue-t-shirt/p/itm627ad8bdefee6?pid=TSHHGS6JC9HWHFVR</t>
         </is>
       </c>
       <c r="AC283" s="5" t="inlineStr">
@@ -23711,7 +23713,7 @@
       </c>
       <c r="AD283" s="5" t="inlineStr">
         <is>
-          <t>public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -25410,14 +25412,14 @@
     <row r="302" ht="22" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
+          <t>Sbs1Enterprises</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
           <t>SBS1ENTERPRISES</t>
         </is>
       </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>SBS1ENTERPRISES</t>
-        </is>
-      </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
@@ -25435,7 +25437,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>Ethnic Wear</t>
+          <t>Suit Trousers</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -25460,12 +25462,12 @@
       <c r="V302" s="3" t="n"/>
       <c r="W302" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/shreekshinsa-embroidered-kurta-trouser-pant-dupatta-set/p/itm784881ab05038?pid=SWDHPG53TVXBWNRC</t>
+          <t>https://www.flipkart.com/shreekshinsa-embroidered-kurta-trouser-pant-dupatta-set/p/itm784881ab05038?pid=SWDHPG535FPFRCBN</t>
         </is>
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>Ethnic Wear</t>
+          <t>Suit Trousers</t>
         </is>
       </c>
       <c r="Y302" s="2" t="n"/>
@@ -25473,7 +25475,7 @@
       <c r="AA302" s="2" t="n"/>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/shreekshinsa-embroidered-kurta-trouser-pant-dupatta-set/p/itm784881ab05038?pid=SWDHPG53TVXBWNRC</t>
+          <t>https://www.flipkart.com/shreekshinsa-embroidered-kurta-trouser-pant-dupatta-set/p/itm784881ab05038?pid=SWDHPG535FPFRCBN</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
@@ -25678,32 +25680,32 @@
     <row r="305" ht="22" customHeight="1">
       <c r="A305" s="5" t="inlineStr">
         <is>
+          <t>Ravr India</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
           <t>RAVR India</t>
         </is>
       </c>
-      <c r="B305" s="5" t="inlineStr">
-        <is>
-          <t>RAVR India</t>
-        </is>
-      </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D305" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+      <c r="D305" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>Proprietorship / Registered Business</t>
+          <t>B2C / Retail</t>
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>Innerwear</t>
+          <t>Sportswear &gt; Athletic Socks</t>
         </is>
       </c>
       <c r="G305" s="5" t="n"/>
@@ -25762,16 +25764,16 @@
       <c r="T305" s="6" t="n"/>
       <c r="U305" s="6" t="n"/>
       <c r="V305" s="6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="W305" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/swagr-men-brief/p/itm7e75f0d78747e?pid=BRFHNH3ZZNEMSRSM</t>
+          <t>https://www.flipkart.com/navy-sport-men-mid-calf-crew/p/itmef016217af0c3?pid=SOCFX6P6G2KMZDFJ</t>
         </is>
       </c>
       <c r="X305" s="5" t="inlineStr">
         <is>
-          <t>Innerwear</t>
+          <t>Sportswear &gt; Athletic Socks</t>
         </is>
       </c>
       <c r="Y305" s="5" t="n"/>
@@ -25779,7 +25781,7 @@
       <c r="AA305" s="5" t="n"/>
       <c r="AB305" s="5" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/swagr-men-brief/p/itm7e75f0d78747e?pid=BRFHNH3ZZNEMSRSM</t>
+          <t>https://www.flipkart.com/navy-sport-men-mid-calf-crew/p/itmef016217af0c3?pid=SOCFX6P6G2KMZDFJ</t>
         </is>
       </c>
       <c r="AC305" s="5" t="inlineStr">
@@ -25789,7 +25791,7 @@
       </c>
       <c r="AD305" s="5" t="inlineStr">
         <is>
-          <t>company_website, public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -32666,32 +32668,32 @@
     <row r="382" ht="22" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
+          <t>Tripr</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
           <t>TRIPR</t>
         </is>
       </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>TRIPR</t>
-        </is>
-      </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D382" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+      <c r="D382" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>Proprietorship / Registered Business</t>
+          <t>B2C / Retail</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>Tracksuits</t>
+          <t>Sweatshirts &amp; Hoodies</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
@@ -32758,12 +32760,12 @@
       </c>
       <c r="W382" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/blive-solid-men-track-suit/p/itmb7de455c84b78?pid=TKSHNEVUQF9BVSQT</t>
+          <t>https://www.flipkart.com/tripr-full-sleeve-solid-men-sweatshirt/p/itmd3bad93b1345a?pid=SWSHQKDERZUHHWBN</t>
         </is>
       </c>
       <c r="X382" s="2" t="inlineStr">
         <is>
-          <t>Tracksuits</t>
+          <t>Sweatshirts &amp; Hoodies</t>
         </is>
       </c>
       <c r="Y382" s="2" t="n"/>
@@ -32771,7 +32773,7 @@
       <c r="AA382" s="2" t="n"/>
       <c r="AB382" s="2" t="inlineStr">
         <is>
-          <t>https://www.flipkart.com/blive-solid-men-track-suit/p/itmb7de455c84b78?pid=TKSHNEVUQF9BVSQT</t>
+          <t>https://www.flipkart.com/tripr-full-sleeve-solid-men-sweatshirt/p/itmd3bad93b1345a?pid=SWSHQKDERZUHHWBN</t>
         </is>
       </c>
       <c r="AC382" s="2" t="inlineStr">
@@ -32781,7 +32783,7 @@
       </c>
       <c r="AD382" s="2" t="inlineStr">
         <is>
-          <t>company_website, public_search</t>
+          <t>search_query</t>
         </is>
       </c>
     </row>
@@ -48228,26 +48230,34 @@
     <row r="568" ht="22" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
+          <t>Fabrrinityfashion</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
           <t>FabrrinityFashion</t>
         </is>
       </c>
-      <c r="B568" s="2" t="inlineStr">
-        <is>
-          <t>FabrrinityFashion</t>
-        </is>
-      </c>
       <c r="C568" s="3" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D568" s="4" t="inlineStr">
-        <is>
-          <t>ENRICHMENT_PENDING</t>
-        </is>
-      </c>
-      <c r="E568" s="2" t="n"/>
-      <c r="F568" s="2" t="n"/>
+      <c r="D568" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Sweatshirts &amp; Hoodies</t>
+        </is>
+      </c>
       <c r="G568" s="2" t="n"/>
       <c r="H568" s="3" t="n"/>
       <c r="I568" s="2" t="n"/>
@@ -48259,7 +48269,11 @@
       <c r="O568" s="2" t="n"/>
       <c r="P568" s="2" t="n"/>
       <c r="Q568" s="3" t="n"/>
-      <c r="R568" s="2" t="n"/>
+      <c r="R568" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="S568" s="2" t="n"/>
       <c r="T568" s="3" t="n"/>
       <c r="U568" s="3" t="n"/>
@@ -48287,7 +48301,1051 @@
           <t>fulfillment_label</t>
         </is>
       </c>
-      <c r="AD568" s="2" t="n"/>
+      <c r="AD568" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="22" customHeight="1">
+      <c r="A569" s="5" t="inlineStr">
+        <is>
+          <t>TwinBirds</t>
+        </is>
+      </c>
+      <c r="B569" s="5" t="inlineStr">
+        <is>
+          <t>TwinBirds</t>
+        </is>
+      </c>
+      <c r="C569" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D569" s="7" t="inlineStr">
+        <is>
+          <t>PARTIALLY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="E569" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="n"/>
+      <c r="H569" s="6" t="n"/>
+      <c r="I569" s="5" t="inlineStr">
+        <is>
+          <t>support@twinbirds.co.in</t>
+        </is>
+      </c>
+      <c r="J569" s="6" t="n"/>
+      <c r="K569" s="6" t="n"/>
+      <c r="L569" s="6" t="n"/>
+      <c r="M569" s="5" t="inlineStr">
+        <is>
+          <t>Road, Andipalayam, Tiruppur - 641687</t>
+        </is>
+      </c>
+      <c r="N569" s="5" t="inlineStr">
+        <is>
+          <t>Road, Andipalayam, Tiruppur - 641687</t>
+        </is>
+      </c>
+      <c r="O569" s="5" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="P569" s="5" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="Q569" s="6" t="inlineStr">
+        <is>
+          <t>641687</t>
+        </is>
+      </c>
+      <c r="R569" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S569" s="5" t="inlineStr">
+        <is>
+          <t>https://twinbirds.co.in</t>
+        </is>
+      </c>
+      <c r="T569" s="6" t="n"/>
+      <c r="U569" s="6" t="n"/>
+      <c r="V569" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W569" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/twin-birds-churidar-length-ethnic-wear-legging/p/itmf3wgetjjnzv3z?pid=LJGEDUNMJRY2G2ZB</t>
+        </is>
+      </c>
+      <c r="X569" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y569" s="5" t="n"/>
+      <c r="Z569" s="5" t="n"/>
+      <c r="AA569" s="5" t="n"/>
+      <c r="AB569" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/twin-birds-churidar-length-ethnic-wear-legging/p/itmf3wgetjjnzv3z?pid=LJGEDUNMJRY2G2ZB</t>
+        </is>
+      </c>
+      <c r="AC569" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD569" s="5" t="inlineStr">
+        <is>
+          <t>company_website</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="22" customHeight="1">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>DreamFighter</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>DreamFighter</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D570" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="n"/>
+      <c r="H570" s="3" t="n"/>
+      <c r="I570" s="2" t="n"/>
+      <c r="J570" s="3" t="n"/>
+      <c r="K570" s="3" t="n"/>
+      <c r="L570" s="3" t="n"/>
+      <c r="M570" s="2" t="n"/>
+      <c r="N570" s="2" t="n"/>
+      <c r="O570" s="2" t="n"/>
+      <c r="P570" s="2" t="n"/>
+      <c r="Q570" s="3" t="n"/>
+      <c r="R570" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S570" s="2" t="n"/>
+      <c r="T570" s="3" t="n"/>
+      <c r="U570" s="3" t="n"/>
+      <c r="V570" s="3" t="n"/>
+      <c r="W570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-churidar-length-ethnic-wear-legging/p/itmdd5b4021caa10?pid=LGGG42G6W9HFMBVY</t>
+        </is>
+      </c>
+      <c r="X570" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y570" s="2" t="n"/>
+      <c r="Z570" s="2" t="n"/>
+      <c r="AA570" s="2" t="n"/>
+      <c r="AB570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-churidar-length-ethnic-wear-legging/p/itmdd5b4021caa10?pid=LGGG42G6W9HFMBVY</t>
+        </is>
+      </c>
+      <c r="AC570" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD570" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="22" customHeight="1">
+      <c r="A571" s="5" t="inlineStr">
+        <is>
+          <t>TheFitwellClothing</t>
+        </is>
+      </c>
+      <c r="B571" s="5" t="inlineStr">
+        <is>
+          <t>TheFitwellClothing</t>
+        </is>
+      </c>
+      <c r="C571" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D571" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E571" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G571" s="5" t="n"/>
+      <c r="H571" s="6" t="n"/>
+      <c r="I571" s="5" t="n"/>
+      <c r="J571" s="6" t="n"/>
+      <c r="K571" s="6" t="n"/>
+      <c r="L571" s="6" t="n"/>
+      <c r="M571" s="5" t="n"/>
+      <c r="N571" s="5" t="n"/>
+      <c r="O571" s="5" t="n"/>
+      <c r="P571" s="5" t="n"/>
+      <c r="Q571" s="6" t="n"/>
+      <c r="R571" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S571" s="5" t="n"/>
+      <c r="T571" s="6" t="n"/>
+      <c r="U571" s="6" t="n"/>
+      <c r="V571" s="6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W571" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tfc-ankle-length-western-wear-legging/p/itmc4d4820c48ee8?pid=LGGHP2R855ZRZQMM</t>
+        </is>
+      </c>
+      <c r="X571" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y571" s="5" t="n"/>
+      <c r="Z571" s="5" t="n"/>
+      <c r="AA571" s="5" t="n"/>
+      <c r="AB571" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/tfc-ankle-length-western-wear-legging/p/itmc4d4820c48ee8?pid=LGGHP2R855ZRZQMM</t>
+        </is>
+      </c>
+      <c r="AC571" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD571" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="22" customHeight="1">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>NIHMATH</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>NIHMATH</t>
+        </is>
+      </c>
+      <c r="C572" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D572" s="7" t="inlineStr">
+        <is>
+          <t>PARTIALLY_VERIFIED</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="n"/>
+      <c r="H572" s="3" t="inlineStr">
+        <is>
+          <t>9847583758</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>info@nihmathply.com</t>
+        </is>
+      </c>
+      <c r="J572" s="3" t="n"/>
+      <c r="K572" s="3" t="n"/>
+      <c r="L572" s="3" t="n"/>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>Road Kadungooth Koottilangadi PO Malappuram, Kerala India 676506 Ph: +91 9847583758 Seaport - Airport Road Kalamassery Kaipadamugal Jn Ernakulam, Kerala India 682021</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="inlineStr">
+        <is>
+          <t>Road Kadungooth Koottilangadi PO Malappuram, Kerala India 676506 Ph: +91 9847583758 Seaport - Airport Road Kalamassery Kaipadamugal Jn Ernakulam, Kerala India 682021</t>
+        </is>
+      </c>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>Kerala India</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="Q572" s="3" t="inlineStr">
+        <is>
+          <t>676506</t>
+        </is>
+      </c>
+      <c r="R572" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nihmathply.com</t>
+        </is>
+      </c>
+      <c r="T572" s="3" t="n"/>
+      <c r="U572" s="3" t="n"/>
+      <c r="V572" s="3" t="n"/>
+      <c r="W572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-western-wear-legging/p/itmcf77b353ce6af?pid=LGGHAV3BZQYJZSAZ</t>
+        </is>
+      </c>
+      <c r="X572" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y572" s="2" t="n"/>
+      <c r="Z572" s="2" t="n"/>
+      <c r="AA572" s="2" t="n"/>
+      <c r="AB572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-western-wear-legging/p/itmcf77b353ce6af?pid=LGGHAV3BZQYJZSAZ</t>
+        </is>
+      </c>
+      <c r="AC572" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD572" s="2" t="inlineStr">
+        <is>
+          <t>company_website</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="22" customHeight="1">
+      <c r="A573" s="5" t="inlineStr">
+        <is>
+          <t>shobhaexpo</t>
+        </is>
+      </c>
+      <c r="B573" s="5" t="inlineStr">
+        <is>
+          <t>shobhaexpo</t>
+        </is>
+      </c>
+      <c r="C573" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D573" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E573" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G573" s="5" t="n"/>
+      <c r="H573" s="6" t="n"/>
+      <c r="I573" s="5" t="n"/>
+      <c r="J573" s="6" t="n"/>
+      <c r="K573" s="6" t="n"/>
+      <c r="L573" s="6" t="n"/>
+      <c r="M573" s="5" t="n"/>
+      <c r="N573" s="5" t="n"/>
+      <c r="O573" s="5" t="n"/>
+      <c r="P573" s="5" t="n"/>
+      <c r="Q573" s="6" t="n"/>
+      <c r="R573" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S573" s="5" t="n"/>
+      <c r="T573" s="6" t="n"/>
+      <c r="U573" s="6" t="n"/>
+      <c r="V573" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W573" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fit-flick-ankle-length-western-wear-legging/p/itmd186d260e9fe8?pid=LGGHFP7FZ8BVQE98</t>
+        </is>
+      </c>
+      <c r="X573" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y573" s="5" t="n"/>
+      <c r="Z573" s="5" t="n"/>
+      <c r="AA573" s="5" t="n"/>
+      <c r="AB573" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/fit-flick-ankle-length-western-wear-legging/p/itmd186d260e9fe8?pid=LGGHFP7FZ8BVQE98</t>
+        </is>
+      </c>
+      <c r="AC573" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD573" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="22" customHeight="1">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>ShriBalajiTextileDanuja</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>ShriBalajiTextileDanuja</t>
+        </is>
+      </c>
+      <c r="C574" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D574" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="n"/>
+      <c r="H574" s="3" t="n"/>
+      <c r="I574" s="2" t="n"/>
+      <c r="J574" s="3" t="n"/>
+      <c r="K574" s="3" t="n"/>
+      <c r="L574" s="3" t="n"/>
+      <c r="M574" s="2" t="n"/>
+      <c r="N574" s="2" t="n"/>
+      <c r="O574" s="2" t="n"/>
+      <c r="P574" s="2" t="n"/>
+      <c r="Q574" s="3" t="n"/>
+      <c r="R574" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S574" s="2" t="n"/>
+      <c r="T574" s="3" t="n"/>
+      <c r="U574" s="3" t="n"/>
+      <c r="V574" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bigtees-ankle-length-western-wear-legging/p/itm470a4cbf37381?pid=LGGHGBH7ZEAYCFRH</t>
+        </is>
+      </c>
+      <c r="X574" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y574" s="2" t="n"/>
+      <c r="Z574" s="2" t="n"/>
+      <c r="AA574" s="2" t="n"/>
+      <c r="AB574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bigtees-ankle-length-western-wear-legging/p/itm470a4cbf37381?pid=LGGHGBH7ZEAYCFRH</t>
+        </is>
+      </c>
+      <c r="AC574" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD574" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="22" customHeight="1">
+      <c r="A575" s="5" t="inlineStr">
+        <is>
+          <t>LIEFNEEDS</t>
+        </is>
+      </c>
+      <c r="B575" s="5" t="inlineStr">
+        <is>
+          <t>LIEFNEEDS</t>
+        </is>
+      </c>
+      <c r="C575" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D575" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E575" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G575" s="5" t="n"/>
+      <c r="H575" s="6" t="n"/>
+      <c r="I575" s="5" t="n"/>
+      <c r="J575" s="6" t="n"/>
+      <c r="K575" s="6" t="n"/>
+      <c r="L575" s="6" t="n"/>
+      <c r="M575" s="5" t="n"/>
+      <c r="N575" s="5" t="n"/>
+      <c r="O575" s="5" t="n"/>
+      <c r="P575" s="5" t="n"/>
+      <c r="Q575" s="6" t="n"/>
+      <c r="R575" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S575" s="5" t="n"/>
+      <c r="T575" s="6" t="n"/>
+      <c r="U575" s="6" t="n"/>
+      <c r="V575" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W575" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-ankle-length-western-wear-legging/p/itm734bba5a2e880?pid=LGGHPHXZVDPN7WRV</t>
+        </is>
+      </c>
+      <c r="X575" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y575" s="5" t="n"/>
+      <c r="Z575" s="5" t="n"/>
+      <c r="AA575" s="5" t="n"/>
+      <c r="AB575" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/k-m-r-ankle-length-western-wear-legging/p/itm734bba5a2e880?pid=LGGHPHXZVDPN7WRV</t>
+        </is>
+      </c>
+      <c r="AC575" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD575" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="22" customHeight="1">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>JockeyIndia</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>JockeyIndia</t>
+        </is>
+      </c>
+      <c r="C576" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D576" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="n"/>
+      <c r="H576" s="3" t="n"/>
+      <c r="I576" s="2" t="n"/>
+      <c r="J576" s="3" t="n"/>
+      <c r="K576" s="3" t="n"/>
+      <c r="L576" s="3" t="n"/>
+      <c r="M576" s="2" t="n"/>
+      <c r="N576" s="2" t="n"/>
+      <c r="O576" s="2" t="n"/>
+      <c r="P576" s="2" t="n"/>
+      <c r="Q576" s="3" t="n"/>
+      <c r="R576" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S576" s="2" t="n"/>
+      <c r="T576" s="3" t="n"/>
+      <c r="U576" s="3" t="n"/>
+      <c r="V576" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jockey-ankle-length-western-wear-legging/p/itm11eb659eaad63?pid=LGGGD3ZGZCJHVUKG</t>
+        </is>
+      </c>
+      <c r="X576" s="2" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y576" s="2" t="n"/>
+      <c r="Z576" s="2" t="n"/>
+      <c r="AA576" s="2" t="n"/>
+      <c r="AB576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/jockey-ankle-length-western-wear-legging/p/itm11eb659eaad63?pid=LGGGD3ZGZCJHVUKG</t>
+        </is>
+      </c>
+      <c r="AC576" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD576" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="22" customHeight="1">
+      <c r="A577" s="5" t="inlineStr">
+        <is>
+          <t>PrakashGarments234</t>
+        </is>
+      </c>
+      <c r="B577" s="5" t="inlineStr">
+        <is>
+          <t>PrakashGarments234</t>
+        </is>
+      </c>
+      <c r="C577" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D577" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E577" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F577" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="G577" s="5" t="n"/>
+      <c r="H577" s="6" t="n"/>
+      <c r="I577" s="5" t="n"/>
+      <c r="J577" s="6" t="n"/>
+      <c r="K577" s="6" t="n"/>
+      <c r="L577" s="6" t="n"/>
+      <c r="M577" s="5" t="n"/>
+      <c r="N577" s="5" t="n"/>
+      <c r="O577" s="5" t="n"/>
+      <c r="P577" s="5" t="n"/>
+      <c r="Q577" s="6" t="n"/>
+      <c r="R577" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S577" s="5" t="n"/>
+      <c r="T577" s="6" t="n"/>
+      <c r="U577" s="6" t="n"/>
+      <c r="V577" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W577" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/loveit-ankle-length-western-wear-legging/p/itm09c3afcf33967?pid=LGGHZHTJJ8BGJXFU</t>
+        </is>
+      </c>
+      <c r="X577" s="5" t="inlineStr">
+        <is>
+          <t>Leggings</t>
+        </is>
+      </c>
+      <c r="Y577" s="5" t="n"/>
+      <c r="Z577" s="5" t="n"/>
+      <c r="AA577" s="5" t="n"/>
+      <c r="AB577" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/loveit-ankle-length-western-wear-legging/p/itm09c3afcf33967?pid=LGGHZHTJJ8BGJXFU</t>
+        </is>
+      </c>
+      <c r="AC577" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD577" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="22" customHeight="1">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Bhavay</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>BHAVAY</t>
+        </is>
+      </c>
+      <c r="C578" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D578" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="n"/>
+      <c r="H578" s="3" t="n"/>
+      <c r="I578" s="2" t="n"/>
+      <c r="J578" s="3" t="n"/>
+      <c r="K578" s="3" t="n"/>
+      <c r="L578" s="3" t="n"/>
+      <c r="M578" s="2" t="n"/>
+      <c r="N578" s="2" t="n"/>
+      <c r="O578" s="2" t="n"/>
+      <c r="P578" s="2" t="n"/>
+      <c r="Q578" s="3" t="n"/>
+      <c r="R578" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S578" s="2" t="n"/>
+      <c r="T578" s="3" t="n"/>
+      <c r="U578" s="3" t="n"/>
+      <c r="V578" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/9lkha-striped-men-three-fourths/p/itm1c204321e2c77?pid=TFHHNHJCHDC9YCGR</t>
+        </is>
+      </c>
+      <c r="X578" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y578" s="2" t="n"/>
+      <c r="Z578" s="2" t="n"/>
+      <c r="AA578" s="2" t="n"/>
+      <c r="AB578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/9lkha-striped-men-three-fourths/p/itm1c204321e2c77?pid=TFHHNHJCHDC9YCGR</t>
+        </is>
+      </c>
+      <c r="AC578" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD578" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="22" customHeight="1">
+      <c r="A579" s="5" t="inlineStr">
+        <is>
+          <t>Munnz</t>
+        </is>
+      </c>
+      <c r="B579" s="5" t="inlineStr">
+        <is>
+          <t>Munnz</t>
+        </is>
+      </c>
+      <c r="C579" s="6" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D579" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E579" s="5" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F579" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G579" s="5" t="n"/>
+      <c r="H579" s="6" t="n"/>
+      <c r="I579" s="5" t="n"/>
+      <c r="J579" s="6" t="n"/>
+      <c r="K579" s="6" t="n"/>
+      <c r="L579" s="6" t="n"/>
+      <c r="M579" s="5" t="n"/>
+      <c r="N579" s="5" t="n"/>
+      <c r="O579" s="5" t="n"/>
+      <c r="P579" s="5" t="n"/>
+      <c r="Q579" s="6" t="n"/>
+      <c r="R579" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S579" s="5" t="n"/>
+      <c r="T579" s="6" t="n"/>
+      <c r="U579" s="6" t="n"/>
+      <c r="V579" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W579" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
+        </is>
+      </c>
+      <c r="X579" s="5" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y579" s="5" t="n"/>
+      <c r="Z579" s="5" t="n"/>
+      <c r="AA579" s="5" t="n"/>
+      <c r="AB579" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/munnz-solid-men-three-fourths/p/itme83472b57b005?pid=TFHH2YB66XPKJH2G</t>
+        </is>
+      </c>
+      <c r="AC579" s="5" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD579" s="5" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="22" customHeight="1">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Bikrom Garments</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>BIKROM GARMENTS</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="D580" s="10" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>B2C / Retail</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="n"/>
+      <c r="H580" s="3" t="n"/>
+      <c r="I580" s="2" t="n"/>
+      <c r="J580" s="3" t="n"/>
+      <c r="K580" s="3" t="n"/>
+      <c r="L580" s="3" t="n"/>
+      <c r="M580" s="2" t="n"/>
+      <c r="N580" s="2" t="n"/>
+      <c r="O580" s="2" t="n"/>
+      <c r="P580" s="2" t="n"/>
+      <c r="Q580" s="3" t="n"/>
+      <c r="R580" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S580" s="2" t="n"/>
+      <c r="T580" s="3" t="n"/>
+      <c r="U580" s="3" t="n"/>
+      <c r="V580" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
+        </is>
+      </c>
+      <c r="X580" s="2" t="inlineStr">
+        <is>
+          <t>Three-Fourths</t>
+        </is>
+      </c>
+      <c r="Y580" s="2" t="n"/>
+      <c r="Z580" s="2" t="n"/>
+      <c r="AA580" s="2" t="n"/>
+      <c r="AB580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.flipkart.com/bikrom-garments-solid-men-three-fourths/p/itm9c3b3c49c3335?pid=TFHG36PT4RBE2MCS</t>
+        </is>
+      </c>
+      <c r="AC580" s="2" t="inlineStr">
+        <is>
+          <t>fulfillment_label</t>
+        </is>
+      </c>
+      <c r="AD580" s="2" t="inlineStr">
+        <is>
+          <t>search_query</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
